--- a/bom.xlsx
+++ b/bom.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="456">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="511">
   <x:si>
     <x:t>Document No</x:t>
   </x:si>
@@ -699,10 +699,28 @@
     <x:t xml:space="preserve">Flanged Small Ball Bearings Stainless Steel </x:t>
   </x:si>
   <x:si>
-    <x:t>C-SEFL608ZZ</x:t>
+    <x:t>Misumi
+[YHD]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C-SEFL608ZZ
+[BAL608ZZ-E-SUS]</x:t>
   </x:si>
   <x:si>
     <x:t>RFQ4124221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5319311</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dongguan YHD Supply Chain Management Co Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45811
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAPO26030261</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Bearing Shaft Screws </x:t>
@@ -878,6 +896,19 @@
     <x:t>RFQ4128991</x:t>
   </x:si>
   <x:si>
+    <x:t>PR5319361</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COPOLY TRADING SDN BHD</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45814
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAPO26030245</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Heavy Load Low Profile Caster Swivel </x:t>
   </x:si>
   <x:si>
@@ -997,9 +1028,6 @@
     <x:t>OMRP513-F3005-00</x:t>
   </x:si>
   <x:si>
-    <x:t>RFQ Updated</x:t>
-  </x:si>
-  <x:si>
     <x:t>HOIST</x:t>
   </x:si>
   <x:si>
@@ -1007,12 +1035,18 @@
   </x:si>
   <x:si>
     <x:t>RFQ4129102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5322791</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45485
 </x:t>
   </x:si>
   <x:si>
+    <x:t>SAPO26030317</x:t>
+  </x:si>
+  <x:si>
     <x:t>OMRP513-F2002-00</x:t>
   </x:si>
   <x:si>
@@ -1074,12 +1108,18 @@
   </x:si>
   <x:si>
     <x:t>RFQ4129132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5322431</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45525
 </x:t>
   </x:si>
   <x:si>
+    <x:t>SAPO26030313</x:t>
+  </x:si>
+  <x:si>
     <x:t>OMR513-F1002A</x:t>
   </x:si>
   <x:si>
@@ -1129,6 +1169,9 @@
   </x:si>
   <x:si>
     <x:t>OMR513-F1018A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ Updated</x:t>
   </x:si>
   <x:si>
     <x:t>OMR513-S1000A</x:t>
@@ -1171,13 +1214,32 @@
     <x:t>bearing</x:t>
   </x:si>
   <x:si>
-    <x:t>B6000ZZ</x:t>
+    <x:t xml:space="preserve">MISUMI
+[YHD]
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B6000ZZ
+[BAY6000ZZ]	
+]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4131262</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45810
+</x:t>
   </x:si>
   <x:si>
     <x:t>c clip</x:t>
   </x:si>
   <x:si>
-    <x:t>STWS10</x:t>
+    <x:t>MISUMI
+[YHD]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STWS10
+[TAS02-10]</x:t>
   </x:si>
   <x:si>
     <x:t>height sensor</x:t>
@@ -1219,19 +1281,29 @@
     <x:t>Pivot Pin</x:t>
   </x:si>
   <x:si>
-    <x:t>SHCDG6-25</x:t>
+    <x:t xml:space="preserve">SHCDG6-25
+【Y-KCD32-D6-L25】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>RFQ4129262</x:t>
   </x:si>
   <x:si>
-    <x:t>SHCDG8-20</x:t>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45808
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SHCDG8-20
+【Y-KCD32-D8-L20】	
+</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Bushing </x:t>
   </x:si>
   <x:si>
-    <x:t>MDZB6-10</x:t>
+    <x:t xml:space="preserve">MDZB6-10
+【OFV01-d6-L10】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>Photoelectric sensor</x:t>
@@ -1243,10 +1315,31 @@
     <x:t>pm-u25</x:t>
   </x:si>
   <x:si>
+    <x:t>RFQ4130812</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5319341</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fulitech Technology Co. Limited</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45744
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAPO26030286</x:t>
+  </x:si>
+  <x:si>
     <x:t>Linear Guide</x:t>
   </x:si>
   <x:si>
-    <x:t>SSEBWZ16G-110</x:t>
+    <x:t xml:space="preserve">SSEBWZ16G-110
+【IAJ01-H16-L110】	
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ Reject</x:t>
   </x:si>
   <x:si>
     <x:t>Linear Guide Bearing</x:t>
@@ -1261,37 +1354,51 @@
     <x:t>Linear Shaft</x:t>
   </x:si>
   <x:si>
-    <x:t>PSSFGZ6-50-M3-N3-SC15</x:t>
+    <x:t xml:space="preserve">PSSFGZ6-50-M3-N3-SC15
+【SCK14-D6-L50-M3-N3-S15】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>Linear Bearing</x:t>
   </x:si>
   <x:si>
-    <x:t>LMU6</x:t>
+    <x:t xml:space="preserve">LMU6
+【LMC02-d6】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>Round Wire Coil Spring</x:t>
   </x:si>
   <x:si>
-    <x:t>C-UL8-40</x:t>
+    <x:t xml:space="preserve">C-UL8-40
+【E-YUL-D8-L40】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>Bearing with Housing</x:t>
   </x:si>
   <x:si>
-    <x:t>C-BGHA698ZZ-20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCLBRU5-12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MDZB5-5</x:t>
+    <x:t xml:space="preserve">C-BGHA698ZZ-20
+【E-BHJ21-698ZZ-h20】	
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SCLBRU5-12
+【Y-KCD56-D5-L12】	
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MDZB5-5
+【OFV01-d5-L5】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>Bearing Spacer</x:t>
   </x:si>
   <x:si>
-    <x:t>E-CLBUS5-8-7</x:t>
+    <x:t xml:space="preserve">E-CLBUS5-8-7
+【BKP11-d5-D8-L7】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>pm-l25</x:t>
@@ -1300,10 +1407,14 @@
     <x:t>Retaining Rings C-Type</x:t>
   </x:si>
   <x:si>
-    <x:t>STWS12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HCDG5-10</x:t>
+    <x:t xml:space="preserve">STWS12
+【TAS02-12】	
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">HCDG5-10
+【MIC01-D5-L10】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>Reflactor</x:t>
@@ -1315,13 +1426,20 @@
     <x:t>A0-158515</x:t>
   </x:si>
   <x:si>
-    <x:t>E-CLBUS12-15-1.5</x:t>
+    <x:t>RFQ4130831</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">E-CLBUS12-15-1.5
+【BKP11-d12-D15-L1.5】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>Coupling</x:t>
   </x:si>
   <x:si>
-    <x:t>GSACL20-5-6</x:t>
+    <x:t xml:space="preserve">GSACL20-5-6
+【DEE13-D20-d5-e6】	
+</x:t>
   </x:si>
   <x:si>
     <x:t>Stepper Motor</x:t>
@@ -1333,31 +1451,64 @@
     <x:t>AM17HD6426-BR01</x:t>
   </x:si>
   <x:si>
+    <x:t>RFQ4130821</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5319351</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">VALUE SOURCES (M) SDN BHD                                   </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45735
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAPO26030285</x:t>
+  </x:si>
+  <x:si>
     <x:t>OMRG2-2104- Repeat</x:t>
   </x:si>
   <x:si>
     <x:t>RFQ4129661</x:t>
   </x:si>
   <x:si>
-    <x:t>misumi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HR30220J</x:t>
+    <x:t>PR5321001</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/46314
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAPO26030296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ Approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>misumi [YHD]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HR30220J [HR30220J-NSK ]</x:t>
   </x:si>
   <x:si>
     <x:t>RFQ4130402</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/46459
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>ball plungers</x:t>
   </x:si>
   <x:si>
-    <x:t>FBPJS12</x:t>
+    <x:t>FBPJS12 [ZAK52-M12 ]</x:t>
   </x:si>
   <x:si>
     <x:t>ball button</x:t>
   </x:si>
   <x:si>
-    <x:t>TBBT12</x:t>
+    <x:t>TBBT12 [ ZAS81-M12]</x:t>
   </x:si>
   <x:si>
     <x:t>unasis</x:t>
@@ -1366,6 +1517,9 @@
     <x:t>IZ0100XV-RL</x:t>
   </x:si>
   <x:si>
+    <x:t>RFQ4132491</x:t>
+  </x:si>
+  <x:si>
     <x:t>Safety Guide</x:t>
   </x:si>
   <x:si>
@@ -1378,6 +1532,9 @@
     <x:t>OMR-STR-F1110A</x:t>
   </x:si>
   <x:si>
+    <x:t>RFQ4130861</x:t>
+  </x:si>
+  <x:si>
     <x:t>OMR-STR-F1111A</x:t>
   </x:si>
   <x:si>
@@ -1402,6 +1559,13 @@
     <x:t>OMR-STR-S1123A</x:t>
   </x:si>
   <x:si>
+    <x:t>RFQ4130871</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45815
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>OMR-STR-F1124A</x:t>
   </x:si>
   <x:si>
@@ -1409,6 +1573,61 @@
   </x:si>
   <x:si>
     <x:t>OMR-STR-F1126A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LM guide</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hiwin
+[YHD]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HGH25CA2R850Z0C
+[HGH25CA2R850Z0C]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4130782</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45832
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Linear Bush Bearing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Misumi 
+[YHD]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C-LHFCM20
+[E-LME23-d20]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shaft Holder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBHF20
+[GFC01-D20]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Spring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WR27-100
+[YWR-D27-L80]</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SHIPPING </x:t>
+  </x:si>
+  <x:si>
+    <x:t>OMR-STR-A1200A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4131351</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHIPPING</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1797,7 +2016,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AC191"/>
+  <x:dimension ref="A1:AC198"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="30" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1818,7 +2037,7 @@
     <x:col min="15" max="15" width="11.490625" style="1" customWidth="1"/>
     <x:col min="16" max="16" width="10.350625" style="1" customWidth="1"/>
     <x:col min="17" max="17" width="11.060625" style="1" customWidth="1"/>
-    <x:col min="18" max="18" width="40.220625" style="1" customWidth="1"/>
+    <x:col min="18" max="18" width="43.820625" style="1" customWidth="1"/>
     <x:col min="19" max="19" width="51.710625" style="1" customWidth="1"/>
     <x:col min="20" max="20" width="17.810625" style="1" customWidth="1"/>
     <x:col min="21" max="21" width="14.980625" style="1" customWidth="1"/>
@@ -5814,13 +6033,13 @@
     </x:row>
     <x:row r="64" spans="1:29">
       <x:c r="A64" s="4">
-        <x:v>46039.5807428588</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B64" s="1" t="n">
         <x:v>33548</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
         <x:v>138</x:v>
@@ -5829,13 +6048,13 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I64" s="1" t="n">
         <x:v>6</x:v>
@@ -5843,17 +6062,44 @@
       <x:c r="J64" s="1" t="n">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="K64" s="4">
+        <x:v>46086.6616231481</x:v>
+      </x:c>
       <x:c r="L64" s="4">
-        <x:v>46039.5782636574</x:v>
+        <x:v>46086.6616232292</x:v>
       </x:c>
       <x:c r="M64" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="N64" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O64" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P64" s="1" t="n">
+        <x:v>1.06</x:v>
+      </x:c>
+      <x:c r="Q64" s="1" t="n">
+        <x:v>25.23966</x:v>
       </x:c>
       <x:c r="R64" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S64" s="1" t="s">
+        <x:v>227</x:v>
       </x:c>
       <x:c r="T64" s="1" t="n">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="U64" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V64" s="1" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="W64" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:29">
@@ -5870,7 +6116,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
         <x:v>191</x:v>
@@ -5879,7 +6125,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="I65" s="1" t="n">
         <x:v>2</x:v>
@@ -5941,7 +6187,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
         <x:v>191</x:v>
@@ -5950,7 +6196,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="I66" s="1" t="n">
         <x:v>1</x:v>
@@ -6012,7 +6258,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
         <x:v>191</x:v>
@@ -6021,7 +6267,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="I67" s="1" t="n">
         <x:v>2</x:v>
@@ -6083,16 +6329,16 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H68" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="I68" s="1" t="n">
         <x:v>2</x:v>
@@ -6107,13 +6353,13 @@
         <x:v>46037.4235065972</x:v>
       </x:c>
       <x:c r="M68" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="N68" s="4">
         <x:v>46037.6961916319</x:v>
       </x:c>
       <x:c r="O68" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="P68" s="1" t="n">
         <x:v>25</x:v>
@@ -6122,16 +6368,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="R68" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="S68" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="T68" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U68" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="V68" s="1" t="n">
         <x:v>2</x:v>
@@ -6154,16 +6400,16 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="I69" s="1" t="n">
         <x:v>1</x:v>
@@ -6178,13 +6424,13 @@
         <x:v>46037.4235065972</x:v>
       </x:c>
       <x:c r="M69" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="N69" s="4">
         <x:v>46037.6961916319</x:v>
       </x:c>
       <x:c r="O69" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="P69" s="1" t="n">
         <x:v>25</x:v>
@@ -6193,16 +6439,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="R69" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="S69" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="T69" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U69" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="V69" s="1" t="n">
         <x:v>1</x:v>
@@ -6225,10 +6471,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>52</x:v>
@@ -6246,13 +6492,13 @@
         <x:v>46062.4290690972</x:v>
       </x:c>
       <x:c r="M70" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="N70" s="4">
         <x:v>46062.429069213</x:v>
       </x:c>
       <x:c r="O70" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="P70" s="1" t="n">
         <x:v>920</x:v>
@@ -6264,13 +6510,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S70" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="T70" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U70" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="V70" s="1" t="n">
         <x:v>1</x:v>
@@ -6290,10 +6536,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
         <x:v>51</x:v>
@@ -6314,13 +6560,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M71" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N71" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O71" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P71" s="1" t="n">
         <x:v>450</x:v>
@@ -6332,13 +6578,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S71" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T71" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U71" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V71" s="1" t="n">
         <x:v>2</x:v>
@@ -6358,10 +6604,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
         <x:v>51</x:v>
@@ -6382,13 +6628,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M72" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N72" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O72" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P72" s="1" t="n">
         <x:v>85</x:v>
@@ -6400,13 +6646,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S72" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T72" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U72" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V72" s="1" t="n">
         <x:v>2</x:v>
@@ -6426,10 +6672,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
         <x:v>51</x:v>
@@ -6450,13 +6696,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M73" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N73" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O73" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P73" s="1" t="n">
         <x:v>40</x:v>
@@ -6468,13 +6714,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S73" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T73" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U73" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V73" s="1" t="n">
         <x:v>2</x:v>
@@ -6494,10 +6740,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
         <x:v>51</x:v>
@@ -6518,13 +6764,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M74" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N74" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O74" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P74" s="1" t="n">
         <x:v>55</x:v>
@@ -6536,13 +6782,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S74" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T74" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U74" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V74" s="1" t="n">
         <x:v>2</x:v>
@@ -6562,10 +6808,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
         <x:v>51</x:v>
@@ -6586,13 +6832,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M75" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N75" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O75" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P75" s="1" t="n">
         <x:v>40</x:v>
@@ -6604,13 +6850,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S75" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T75" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U75" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V75" s="1" t="n">
         <x:v>4</x:v>
@@ -6630,10 +6876,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
         <x:v>51</x:v>
@@ -6654,13 +6900,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M76" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N76" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O76" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P76" s="1" t="n">
         <x:v>50</x:v>
@@ -6672,13 +6918,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S76" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T76" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U76" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V76" s="1" t="n">
         <x:v>1</x:v>
@@ -6698,10 +6944,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
         <x:v>51</x:v>
@@ -6722,13 +6968,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M77" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N77" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O77" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P77" s="1" t="n">
         <x:v>30</x:v>
@@ -6740,13 +6986,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S77" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T77" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U77" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V77" s="1" t="n">
         <x:v>1</x:v>
@@ -6766,10 +7012,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
         <x:v>51</x:v>
@@ -6790,13 +7036,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M78" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N78" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O78" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P78" s="1" t="n">
         <x:v>40</x:v>
@@ -6808,13 +7054,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S78" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T78" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U78" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V78" s="1" t="n">
         <x:v>2</x:v>
@@ -6834,10 +7080,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
         <x:v>51</x:v>
@@ -6858,13 +7104,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M79" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N79" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O79" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P79" s="1" t="n">
         <x:v>70</x:v>
@@ -6876,13 +7122,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S79" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T79" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U79" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V79" s="1" t="n">
         <x:v>1</x:v>
@@ -6902,10 +7148,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
         <x:v>51</x:v>
@@ -6926,13 +7172,13 @@
         <x:v>46051.4773018519</x:v>
       </x:c>
       <x:c r="M80" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="N80" s="4">
         <x:v>46051.477631794</x:v>
       </x:c>
       <x:c r="O80" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="P80" s="1" t="n">
         <x:v>35</x:v>
@@ -6944,13 +7190,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S80" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="T80" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U80" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="V80" s="1" t="n">
         <x:v>2</x:v>
@@ -6970,10 +7216,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
         <x:v>109</x:v>
@@ -6982,7 +7228,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="I81" s="1" t="n">
         <x:v>1</x:v>
@@ -6997,13 +7243,13 @@
         <x:v>46076.6816239236</x:v>
       </x:c>
       <x:c r="M81" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="N81" s="4">
         <x:v>46076.6816248032</x:v>
       </x:c>
       <x:c r="O81" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="P81" s="1" t="n">
         <x:v>51.34</x:v>
@@ -7012,16 +7258,16 @@
         <x:v>51.34</x:v>
       </x:c>
       <x:c r="R81" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="S81" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="T81" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U81" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="V81" s="1" t="n">
         <x:v>1</x:v>
@@ -7041,10 +7287,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
         <x:v>191</x:v>
@@ -7053,7 +7299,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="I82" s="1" t="n">
         <x:v>4</x:v>
@@ -7068,13 +7314,13 @@
         <x:v>46066.6646353356</x:v>
       </x:c>
       <x:c r="M82" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="N82" s="4">
         <x:v>46066.5919248495</x:v>
       </x:c>
       <x:c r="O82" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="P82" s="1" t="n">
         <x:v>9.79</x:v>
@@ -7086,13 +7332,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S82" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="T82" s="1" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="U82" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="V82" s="1" t="n">
         <x:v>4</x:v>
@@ -7112,10 +7358,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
         <x:v>191</x:v>
@@ -7124,7 +7370,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="I83" s="1" t="n">
         <x:v>1</x:v>
@@ -7139,13 +7385,13 @@
         <x:v>46066.6646353356</x:v>
       </x:c>
       <x:c r="M83" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="N83" s="4">
         <x:v>46066.6646354514</x:v>
       </x:c>
       <x:c r="O83" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="P83" s="1" t="n">
         <x:v>11.33</x:v>
@@ -7157,13 +7403,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S83" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="T83" s="1" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="U83" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="V83" s="1" t="n">
         <x:v>1</x:v>
@@ -7174,28 +7420,28 @@
     </x:row>
     <x:row r="84" spans="1:29">
       <x:c r="A84" s="4">
-        <x:v>46080.7138722222</x:v>
+        <x:v>46090.4481799421</x:v>
       </x:c>
       <x:c r="B84" s="1" t="n">
         <x:v>35728</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="I84" s="1" t="n">
         <x:v>1</x:v>
@@ -7203,11 +7449,44 @@
       <x:c r="J84" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K84" s="4">
+        <x:v>46087.0812799769</x:v>
+      </x:c>
       <x:c r="L84" s="4">
-        <x:v>46065.9712546296</x:v>
+        <x:v>46090.4481129977</x:v>
       </x:c>
       <x:c r="M84" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="N84" s="4">
+        <x:v>46090.4481131134</x:v>
+      </x:c>
+      <x:c r="O84" s="1" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="P84" s="1" t="n">
+        <x:v>2100</x:v>
+      </x:c>
+      <x:c r="Q84" s="1" t="n">
+        <x:v>2100</x:v>
+      </x:c>
+      <x:c r="R84" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="S84" s="1" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="T84" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U84" s="1" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="V84" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W84" s="3">
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:29">
@@ -7221,10 +7500,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
         <x:v>191</x:v>
@@ -7233,7 +7512,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="I85" s="1" t="n">
         <x:v>4</x:v>
@@ -7248,13 +7527,13 @@
         <x:v>46066.6646353356</x:v>
       </x:c>
       <x:c r="M85" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="N85" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O85" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P85" s="1" t="n">
         <x:v>24.84</x:v>
@@ -7266,13 +7545,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S85" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="T85" s="1" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="U85" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V85" s="1" t="n">
         <x:v>4</x:v>
@@ -7292,10 +7571,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
         <x:v>191</x:v>
@@ -7304,7 +7583,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="I86" s="1" t="n">
         <x:v>2</x:v>
@@ -7319,13 +7598,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M86" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N86" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O86" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P86" s="1" t="n">
         <x:v>23.97</x:v>
@@ -7337,13 +7616,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S86" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T86" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U86" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V86" s="1" t="n">
         <x:v>2</x:v>
@@ -7363,10 +7642,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
         <x:v>191</x:v>
@@ -7375,7 +7654,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="I87" s="1" t="n">
         <x:v>4</x:v>
@@ -7390,13 +7669,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M87" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N87" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O87" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P87" s="1" t="n">
         <x:v>62.66</x:v>
@@ -7408,13 +7687,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S87" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T87" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U87" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V87" s="1" t="n">
         <x:v>4</x:v>
@@ -7434,10 +7713,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
         <x:v>191</x:v>
@@ -7446,7 +7725,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="I88" s="1" t="n">
         <x:v>4</x:v>
@@ -7461,13 +7740,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M88" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N88" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O88" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P88" s="1" t="n">
         <x:v>46.38</x:v>
@@ -7479,13 +7758,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S88" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T88" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U88" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V88" s="1" t="n">
         <x:v>4</x:v>
@@ -7505,10 +7784,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
         <x:v>191</x:v>
@@ -7517,7 +7796,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="I89" s="1" t="n">
         <x:v>6</x:v>
@@ -7532,13 +7811,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M89" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N89" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O89" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P89" s="1" t="n">
         <x:v>309.14</x:v>
@@ -7550,13 +7829,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S89" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T89" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U89" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V89" s="1" t="n">
         <x:v>6</x:v>
@@ -7576,7 +7855,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>217</x:v>
@@ -7588,7 +7867,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="I90" s="1" t="n">
         <x:v>4</x:v>
@@ -7603,13 +7882,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M90" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N90" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O90" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P90" s="1" t="n">
         <x:v>12.4</x:v>
@@ -7621,13 +7900,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S90" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T90" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U90" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V90" s="1" t="n">
         <x:v>4</x:v>
@@ -7647,10 +7926,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
         <x:v>191</x:v>
@@ -7659,7 +7938,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="I91" s="1" t="n">
         <x:v>1</x:v>
@@ -7674,13 +7953,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M91" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N91" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O91" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P91" s="1" t="n">
         <x:v>16.6</x:v>
@@ -7692,13 +7971,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S91" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T91" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U91" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V91" s="1" t="n">
         <x:v>1</x:v>
@@ -7718,10 +7997,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
         <x:v>191</x:v>
@@ -7730,7 +8009,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="I92" s="1" t="n">
         <x:v>1</x:v>
@@ -7745,13 +8024,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M92" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N92" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O92" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P92" s="1" t="n">
         <x:v>32.03</x:v>
@@ -7763,13 +8042,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S92" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T92" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U92" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V92" s="1" t="n">
         <x:v>1</x:v>
@@ -7789,10 +8068,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
         <x:v>191</x:v>
@@ -7801,7 +8080,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="I93" s="1" t="n">
         <x:v>2</x:v>
@@ -7816,13 +8095,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M93" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N93" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O93" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P93" s="1" t="n">
         <x:v>73.31</x:v>
@@ -7834,13 +8113,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S93" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T93" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U93" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V93" s="1" t="n">
         <x:v>2</x:v>
@@ -7860,10 +8139,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
         <x:v>191</x:v>
@@ -7872,7 +8151,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="I94" s="1" t="n">
         <x:v>2</x:v>
@@ -7887,13 +8166,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M94" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N94" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O94" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P94" s="1" t="n">
         <x:v>56.66</x:v>
@@ -7905,13 +8184,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S94" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T94" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U94" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V94" s="1" t="n">
         <x:v>2</x:v>
@@ -7931,10 +8210,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
         <x:v>191</x:v>
@@ -7943,7 +8222,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="I95" s="1" t="n">
         <x:v>1</x:v>
@@ -7958,13 +8237,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M95" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N95" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O95" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P95" s="1" t="n">
         <x:v>62.1</x:v>
@@ -7976,13 +8255,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S95" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T95" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U95" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V95" s="1" t="n">
         <x:v>1</x:v>
@@ -8002,10 +8281,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
         <x:v>191</x:v>
@@ -8014,7 +8293,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="I96" s="1" t="n">
         <x:v>1</x:v>
@@ -8029,13 +8308,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M96" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="N96" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O96" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="P96" s="1" t="n">
         <x:v>11.33</x:v>
@@ -8047,13 +8326,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S96" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="T96" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U96" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V96" s="1" t="n">
         <x:v>1</x:v>
@@ -8073,19 +8352,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="I97" s="1" t="n">
         <x:v>3</x:v>
@@ -8100,13 +8379,13 @@
         <x:v>46079.4450462963</x:v>
       </x:c>
       <x:c r="M97" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="N97" s="4">
         <x:v>46079.445046412</x:v>
       </x:c>
       <x:c r="O97" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="P97" s="1" t="n">
         <x:v>25</x:v>
@@ -8115,16 +8394,16 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="R97" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="S97" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="T97" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U97" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="V97" s="1" t="n">
         <x:v>3</x:v>
@@ -8144,10 +8423,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
         <x:v>51</x:v>
@@ -8165,7 +8444,7 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M98" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:29">
@@ -8179,10 +8458,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
         <x:v>51</x:v>
@@ -8200,7 +8479,7 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M99" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:29">
@@ -8214,10 +8493,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
         <x:v>51</x:v>
@@ -8235,7 +8514,7 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M100" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:29">
@@ -8249,10 +8528,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
         <x:v>51</x:v>
@@ -8270,7 +8549,7 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M101" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:29">
@@ -8284,10 +8563,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
         <x:v>51</x:v>
@@ -8305,24 +8584,24 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M102" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:29">
       <x:c r="A103" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B103" s="1" t="n">
         <x:v>35800</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
         <x:v>51</x:v>
@@ -8340,36 +8619,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L103" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M103" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N103" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O103" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P103" s="1" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="Q103" s="1" t="n">
+        <x:v>280</x:v>
       </x:c>
       <x:c r="R103" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S103" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T103" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U103" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V103" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W103" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:29">
       <x:c r="A104" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B104" s="1" t="n">
         <x:v>35801</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
         <x:v>51</x:v>
@@ -8387,36 +8687,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L104" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M104" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N104" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O104" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P104" s="1" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="Q104" s="1" t="n">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="R104" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S104" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T104" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U104" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V104" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W104" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:29">
       <x:c r="A105" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B105" s="1" t="n">
         <x:v>35802</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
         <x:v>51</x:v>
@@ -8434,36 +8755,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L105" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M105" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N105" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O105" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P105" s="1" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="Q105" s="1" t="n">
+        <x:v>170</x:v>
       </x:c>
       <x:c r="R105" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S105" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T105" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U105" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V105" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W105" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:29">
       <x:c r="A106" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B106" s="1" t="n">
         <x:v>35803</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
         <x:v>51</x:v>
@@ -8481,36 +8823,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L106" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M106" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N106" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O106" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P106" s="1" t="n">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="Q106" s="1" t="n">
+        <x:v>275</x:v>
       </x:c>
       <x:c r="R106" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S106" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T106" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U106" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V106" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W106" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:29">
       <x:c r="A107" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B107" s="1" t="n">
         <x:v>35804</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
         <x:v>51</x:v>
@@ -8528,36 +8891,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L107" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M107" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N107" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O107" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P107" s="1" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q107" s="1" t="n">
+        <x:v>600</x:v>
       </x:c>
       <x:c r="R107" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S107" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T107" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U107" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V107" s="1" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="W107" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:29">
       <x:c r="A108" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B108" s="1" t="n">
         <x:v>35805</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
         <x:v>51</x:v>
@@ -8575,36 +8959,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L108" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M108" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N108" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O108" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P108" s="1" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q108" s="1" t="n">
+        <x:v>150</x:v>
       </x:c>
       <x:c r="R108" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S108" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T108" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U108" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V108" s="1" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="W108" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:29">
       <x:c r="A109" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B109" s="1" t="n">
         <x:v>35806</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
         <x:v>51</x:v>
@@ -8622,36 +9027,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L109" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M109" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N109" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O109" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P109" s="1" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Q109" s="1" t="n">
+        <x:v>200</x:v>
       </x:c>
       <x:c r="R109" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S109" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T109" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U109" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V109" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W109" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:29">
       <x:c r="A110" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B110" s="1" t="n">
         <x:v>35807</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F110" s="1" t="s">
         <x:v>51</x:v>
@@ -8669,36 +9095,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L110" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M110" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N110" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O110" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P110" s="1" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q110" s="1" t="n">
+        <x:v>240</x:v>
       </x:c>
       <x:c r="R110" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S110" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T110" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U110" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V110" s="1" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="W110" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:29">
       <x:c r="A111" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B111" s="1" t="n">
         <x:v>35808</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
         <x:v>51</x:v>
@@ -8716,36 +9163,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L111" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M111" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N111" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O111" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P111" s="1" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="Q111" s="1" t="n">
+        <x:v>155</x:v>
       </x:c>
       <x:c r="R111" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S111" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T111" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U111" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V111" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W111" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:29">
       <x:c r="A112" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B112" s="1" t="n">
         <x:v>35809</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
         <x:v>51</x:v>
@@ -8763,36 +9231,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L112" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M112" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N112" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O112" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P112" s="1" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="Q112" s="1" t="n">
+        <x:v>540</x:v>
       </x:c>
       <x:c r="R112" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S112" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T112" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U112" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V112" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W112" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:29">
       <x:c r="A113" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B113" s="1" t="n">
         <x:v>35810</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F113" s="1" t="s">
         <x:v>51</x:v>
@@ -8810,36 +9299,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L113" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M113" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N113" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O113" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P113" s="1" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q113" s="1" t="n">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R113" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S113" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T113" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U113" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V113" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W113" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:29">
       <x:c r="A114" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B114" s="1" t="n">
         <x:v>35811</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="F114" s="1" t="s">
         <x:v>51</x:v>
@@ -8857,36 +9367,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L114" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M114" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N114" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O114" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P114" s="1" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q114" s="1" t="n">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R114" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S114" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T114" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U114" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V114" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W114" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:29">
       <x:c r="A115" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B115" s="1" t="n">
         <x:v>35812</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="F115" s="1" t="s">
         <x:v>51</x:v>
@@ -8904,36 +9435,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L115" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M115" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N115" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O115" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P115" s="1" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q115" s="1" t="n">
+        <x:v>160</x:v>
       </x:c>
       <x:c r="R115" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S115" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T115" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U115" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V115" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W115" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:29">
       <x:c r="A116" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B116" s="1" t="n">
         <x:v>35813</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F116" s="1" t="s">
         <x:v>51</x:v>
@@ -8951,36 +9503,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L116" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M116" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N116" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O116" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P116" s="1" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q116" s="1" t="n">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="R116" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S116" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T116" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U116" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V116" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="W116" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:29">
       <x:c r="A117" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B117" s="1" t="n">
         <x:v>35814</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="F117" s="1" t="s">
         <x:v>51</x:v>
@@ -8998,36 +9571,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L117" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M117" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N117" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O117" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P117" s="1" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="Q117" s="1" t="n">
+        <x:v>72</x:v>
       </x:c>
       <x:c r="R117" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S117" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T117" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U117" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V117" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W117" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:29">
       <x:c r="A118" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B118" s="1" t="n">
         <x:v>35815</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F118" s="1" t="s">
         <x:v>51</x:v>
@@ -9045,36 +9639,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L118" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M118" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N118" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O118" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P118" s="1" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q118" s="1" t="n">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R118" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S118" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T118" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U118" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V118" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W118" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:29">
       <x:c r="A119" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B119" s="1" t="n">
         <x:v>35816</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F119" s="1" t="s">
         <x:v>51</x:v>
@@ -9092,36 +9707,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L119" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M119" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N119" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O119" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P119" s="1" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q119" s="1" t="n">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R119" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S119" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T119" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U119" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V119" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W119" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:29">
       <x:c r="A120" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B120" s="1" t="n">
         <x:v>35817</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F120" s="1" t="s">
         <x:v>51</x:v>
@@ -9139,36 +9775,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L120" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M120" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N120" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O120" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P120" s="1" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="Q120" s="1" t="n">
+        <x:v>240</x:v>
       </x:c>
       <x:c r="R120" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S120" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T120" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U120" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V120" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W120" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:29">
       <x:c r="A121" s="4">
-        <x:v>46083.4149701389</x:v>
+        <x:v>46093.456763044</x:v>
       </x:c>
       <x:c r="B121" s="1" t="n">
         <x:v>35818</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="F121" s="1" t="s">
         <x:v>51</x:v>
@@ -9186,36 +9843,57 @@
         <x:v>46083.4149700579</x:v>
       </x:c>
       <x:c r="L121" s="4">
-        <x:v>46083.4149697917</x:v>
+        <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M121" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N121" s="4">
+        <x:v>46093.4565539005</x:v>
+      </x:c>
+      <x:c r="O121" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="P121" s="1" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="Q121" s="1" t="n">
+        <x:v>180</x:v>
       </x:c>
       <x:c r="R121" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S121" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T121" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U121" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="V121" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W121" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:29">
       <x:c r="A122" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B122" s="1" t="n">
         <x:v>35823</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E122" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F122" s="1" t="s">
         <x:v>51</x:v>
@@ -9233,36 +9911,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L122" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M122" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N122" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O122" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P122" s="1" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q122" s="1" t="n">
+        <x:v>150</x:v>
       </x:c>
       <x:c r="R122" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S122" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T122" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U122" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V122" s="1" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="W122" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:29">
       <x:c r="A123" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B123" s="1" t="n">
         <x:v>35824</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F123" s="1" t="s">
         <x:v>51</x:v>
@@ -9280,36 +9979,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L123" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M123" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N123" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O123" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P123" s="1" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="Q123" s="1" t="n">
+        <x:v>140</x:v>
       </x:c>
       <x:c r="R123" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S123" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T123" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U123" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V123" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W123" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:29">
       <x:c r="A124" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B124" s="1" t="n">
         <x:v>35825</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E124" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F124" s="1" t="s">
         <x:v>51</x:v>
@@ -9327,36 +10047,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L124" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M124" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N124" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O124" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P124" s="1" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="Q124" s="1" t="n">
+        <x:v>160</x:v>
       </x:c>
       <x:c r="R124" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S124" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T124" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U124" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V124" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W124" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:29">
       <x:c r="A125" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B125" s="1" t="n">
         <x:v>35826</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="F125" s="1" t="s">
         <x:v>51</x:v>
@@ -9374,36 +10115,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L125" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M125" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N125" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O125" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P125" s="1" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="Q125" s="1" t="n">
+        <x:v>170</x:v>
       </x:c>
       <x:c r="R125" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S125" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T125" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U125" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V125" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W125" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:29">
       <x:c r="A126" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B126" s="1" t="n">
         <x:v>35827</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F126" s="1" t="s">
         <x:v>51</x:v>
@@ -9421,36 +10183,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L126" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M126" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N126" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O126" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P126" s="1" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="Q126" s="1" t="n">
+        <x:v>480</x:v>
       </x:c>
       <x:c r="R126" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S126" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T126" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U126" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V126" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W126" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:29">
       <x:c r="A127" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B127" s="1" t="n">
         <x:v>35828</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F127" s="1" t="s">
         <x:v>51</x:v>
@@ -9468,36 +10251,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L127" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M127" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N127" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O127" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P127" s="1" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="Q127" s="1" t="n">
+        <x:v>160</x:v>
       </x:c>
       <x:c r="R127" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S127" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T127" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U127" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V127" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W127" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:29">
       <x:c r="A128" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B128" s="1" t="n">
         <x:v>35829</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="F128" s="1" t="s">
         <x:v>51</x:v>
@@ -9515,36 +10319,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L128" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M128" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N128" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O128" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P128" s="1" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Q128" s="1" t="n">
+        <x:v>400</x:v>
       </x:c>
       <x:c r="R128" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S128" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T128" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U128" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V128" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W128" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:29">
       <x:c r="A129" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B129" s="1" t="n">
         <x:v>35830</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="F129" s="1" t="s">
         <x:v>51</x:v>
@@ -9562,36 +10387,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L129" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M129" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N129" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O129" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P129" s="1" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q129" s="1" t="n">
+        <x:v>320</x:v>
       </x:c>
       <x:c r="R129" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S129" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T129" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U129" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V129" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W129" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:29">
       <x:c r="A130" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B130" s="1" t="n">
         <x:v>35831</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F130" s="1" t="s">
         <x:v>51</x:v>
@@ -9609,36 +10455,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L130" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M130" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N130" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O130" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P130" s="1" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Q130" s="1" t="n">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R130" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S130" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T130" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U130" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V130" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W130" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:29">
       <x:c r="A131" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B131" s="1" t="n">
         <x:v>35832</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="F131" s="1" t="s">
         <x:v>51</x:v>
@@ -9656,36 +10523,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L131" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M131" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N131" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O131" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P131" s="1" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q131" s="1" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="R131" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S131" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T131" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U131" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V131" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W131" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:29">
       <x:c r="A132" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B132" s="1" t="n">
         <x:v>35833</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="F132" s="1" t="s">
         <x:v>51</x:v>
@@ -9703,36 +10591,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L132" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M132" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N132" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O132" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P132" s="1" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="Q132" s="1" t="n">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R132" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S132" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T132" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U132" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V132" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W132" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:29">
       <x:c r="A133" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B133" s="1" t="n">
         <x:v>35834</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F133" s="1" t="s">
         <x:v>51</x:v>
@@ -9750,36 +10659,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L133" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M133" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N133" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O133" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P133" s="1" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="Q133" s="1" t="n">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="R133" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S133" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T133" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U133" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V133" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W133" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:29">
       <x:c r="A134" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B134" s="1" t="n">
         <x:v>35835</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="F134" s="1" t="s">
         <x:v>51</x:v>
@@ -9797,36 +10727,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L134" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M134" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N134" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O134" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P134" s="1" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="Q134" s="1" t="n">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R134" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S134" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T134" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U134" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V134" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W134" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:29">
       <x:c r="A135" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B135" s="1" t="n">
         <x:v>35836</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F135" s="1" t="s">
         <x:v>51</x:v>
@@ -9844,36 +10795,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L135" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M135" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N135" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O135" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P135" s="1" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q135" s="1" t="n">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R135" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S135" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T135" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U135" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V135" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W135" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:29">
       <x:c r="A136" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B136" s="1" t="n">
         <x:v>35837</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F136" s="1" t="s">
         <x:v>51</x:v>
@@ -9891,36 +10863,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L136" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M136" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N136" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O136" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P136" s="1" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q136" s="1" t="n">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="R136" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S136" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T136" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U136" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V136" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W136" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:29">
       <x:c r="A137" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B137" s="1" t="n">
         <x:v>35838</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F137" s="1" t="s">
         <x:v>51</x:v>
@@ -9938,36 +10931,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L137" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M137" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N137" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O137" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P137" s="1" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="Q137" s="1" t="n">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R137" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S137" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T137" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U137" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V137" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W137" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:29">
       <x:c r="A138" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B138" s="1" t="n">
         <x:v>35839</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F138" s="1" t="s">
         <x:v>51</x:v>
@@ -9985,36 +10999,57 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L138" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M138" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N138" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O138" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P138" s="1" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="Q138" s="1" t="n">
+        <x:v>320</x:v>
       </x:c>
       <x:c r="R138" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S138" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T138" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U138" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V138" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W138" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:29">
       <x:c r="A139" s="4">
-        <x:v>46083.7325411227</x:v>
+        <x:v>46092.8409738426</x:v>
       </x:c>
       <x:c r="B139" s="1" t="n">
         <x:v>35840</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F139" s="1" t="s">
         <x:v>51</x:v>
@@ -10032,19 +11067,40 @@
         <x:v>46083.732541088</x:v>
       </x:c>
       <x:c r="L139" s="4">
-        <x:v>46083.7325409722</x:v>
+        <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M139" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="N139" s="4">
+        <x:v>46092.8408331366</x:v>
+      </x:c>
+      <x:c r="O139" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="P139" s="1" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="Q139" s="1" t="n">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="R139" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="S139" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T139" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U139" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="V139" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W139" s="3">
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:29">
@@ -10055,13 +11111,13 @@
         <x:v>35841</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="F140" s="1" t="s">
         <x:v>158</x:v>
@@ -10082,13 +11138,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M140" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R140" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S140" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T140" s="1" t="n">
         <x:v>1</x:v>
@@ -10102,13 +11158,13 @@
         <x:v>35842</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F141" s="1" t="s">
         <x:v>158</x:v>
@@ -10129,13 +11185,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M141" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R141" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S141" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T141" s="1" t="n">
         <x:v>1</x:v>
@@ -10149,13 +11205,13 @@
         <x:v>35843</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F142" s="1" t="s">
         <x:v>158</x:v>
@@ -10176,13 +11232,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M142" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R142" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S142" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T142" s="1" t="n">
         <x:v>1</x:v>
@@ -10196,13 +11252,13 @@
         <x:v>35844</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="F143" s="1" t="s">
         <x:v>158</x:v>
@@ -10223,13 +11279,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M143" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R143" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S143" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T143" s="1" t="n">
         <x:v>1</x:v>
@@ -10243,13 +11299,13 @@
         <x:v>35845</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F144" s="1" t="s">
         <x:v>158</x:v>
@@ -10270,13 +11326,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M144" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R144" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S144" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T144" s="1" t="n">
         <x:v>1</x:v>
@@ -10290,13 +11346,13 @@
         <x:v>35846</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F145" s="1" t="s">
         <x:v>158</x:v>
@@ -10317,13 +11373,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M145" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R145" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S145" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T145" s="1" t="n">
         <x:v>1</x:v>
@@ -10331,7 +11387,7 @@
     </x:row>
     <x:row r="146" spans="1:29">
       <x:c r="A146" s="4">
-        <x:v>46072.6177995023</x:v>
+        <x:v>46086.6571485764</x:v>
       </x:c>
       <x:c r="B146" s="1" t="n">
         <x:v>35888</x:v>
@@ -10340,19 +11396,19 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="F146" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H146" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="I146" s="1" t="n">
         <x:v>6</x:v>
@@ -10364,33 +11420,33 @@
         <x:v>46072.617799456</x:v>
       </x:c>
       <x:c r="M146" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:29">
       <x:c r="A147" s="4">
-        <x:v>46072.6177995023</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B147" s="1" t="n">
         <x:v>35889</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F147" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H147" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="I147" s="1" t="n">
         <x:v>12</x:v>
@@ -10398,37 +11454,70 @@
       <x:c r="J147" s="1" t="n">
         <x:v>12</x:v>
       </x:c>
+      <x:c r="K147" s="4">
+        <x:v>46086.6600797107</x:v>
+      </x:c>
       <x:c r="L147" s="4">
-        <x:v>46072.617799456</x:v>
+        <x:v>46086.6600798611</x:v>
       </x:c>
       <x:c r="M147" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="N147" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O147" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P147" s="1" t="n">
+        <x:v>0.52</x:v>
+      </x:c>
+      <x:c r="Q147" s="1" t="n">
+        <x:v>24.76344</x:v>
+      </x:c>
+      <x:c r="R147" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S147" s="1" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="T147" s="1" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="U147" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V147" s="1" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="W147" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:29">
       <x:c r="A148" s="4">
-        <x:v>46072.6177995023</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B148" s="1" t="n">
         <x:v>35890</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="F148" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H148" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="I148" s="1" t="n">
         <x:v>12</x:v>
@@ -10436,16 +11525,49 @@
       <x:c r="J148" s="1" t="n">
         <x:v>12</x:v>
       </x:c>
+      <x:c r="K148" s="4">
+        <x:v>46086.6600797107</x:v>
+      </x:c>
       <x:c r="L148" s="4">
-        <x:v>46072.617799456</x:v>
+        <x:v>46086.6600798611</x:v>
       </x:c>
       <x:c r="M148" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="N148" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O148" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P148" s="1" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="Q148" s="1" t="n">
+        <x:v>27.62076</x:v>
+      </x:c>
+      <x:c r="R148" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S148" s="1" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="T148" s="1" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="U148" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V148" s="1" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="W148" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:29">
       <x:c r="A149" s="4">
-        <x:v>46072.6177995023</x:v>
+        <x:v>46086.6571485764</x:v>
       </x:c>
       <x:c r="B149" s="1" t="n">
         <x:v>35891</x:v>
@@ -10454,19 +11576,19 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F149" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H149" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="I149" s="1" t="n">
         <x:v>1</x:v>
@@ -10478,12 +11600,12 @@
         <x:v>46072.617799456</x:v>
       </x:c>
       <x:c r="M149" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:29">
       <x:c r="A150" s="4">
-        <x:v>46072.6177995023</x:v>
+        <x:v>46086.6571485764</x:v>
       </x:c>
       <x:c r="B150" s="1" t="n">
         <x:v>35893</x:v>
@@ -10492,19 +11614,19 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="F150" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H150" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="I150" s="1" t="n">
         <x:v>2</x:v>
@@ -10516,12 +11638,12 @@
         <x:v>46072.617799456</x:v>
       </x:c>
       <x:c r="M150" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:29">
       <x:c r="A151" s="4">
-        <x:v>46072.6195614583</x:v>
+        <x:v>46086.6557853356</x:v>
       </x:c>
       <x:c r="B151" s="1" t="n">
         <x:v>35894</x:v>
@@ -10530,19 +11652,19 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="F151" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H151" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="I151" s="1" t="n">
         <x:v>4</x:v>
@@ -10554,12 +11676,18 @@
         <x:v>46072.6195613773</x:v>
       </x:c>
       <x:c r="M151" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="R151" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="T151" s="1" t="n">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:29">
       <x:c r="A152" s="4">
-        <x:v>46072.6195614583</x:v>
+        <x:v>46086.6557853356</x:v>
       </x:c>
       <x:c r="B152" s="1" t="n">
         <x:v>35895</x:v>
@@ -10568,19 +11696,19 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="F152" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H152" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="I152" s="1" t="n">
         <x:v>1</x:v>
@@ -10592,12 +11720,18 @@
         <x:v>46072.6195613773</x:v>
       </x:c>
       <x:c r="M152" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="R152" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="T152" s="1" t="n">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:29">
       <x:c r="A153" s="4">
-        <x:v>46072.6195614583</x:v>
+        <x:v>46086.6557853356</x:v>
       </x:c>
       <x:c r="B153" s="1" t="n">
         <x:v>35896</x:v>
@@ -10606,19 +11740,19 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F153" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H153" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="I153" s="1" t="n">
         <x:v>1</x:v>
@@ -10630,33 +11764,39 @@
         <x:v>46072.6195613773</x:v>
       </x:c>
       <x:c r="M153" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="R153" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="T153" s="1" t="n">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:29">
       <x:c r="A154" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B154" s="1" t="n">
         <x:v>35897</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D154" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F154" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H154" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="I154" s="1" t="n">
         <x:v>4</x:v>
@@ -10664,37 +11804,70 @@
       <x:c r="J154" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="K154" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L154" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M154" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N154" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O154" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P154" s="1" t="n">
+        <x:v>4.18</x:v>
+      </x:c>
+      <x:c r="Q154" s="1" t="n">
+        <x:v>66.35332</x:v>
+      </x:c>
+      <x:c r="R154" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S154" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T154" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U154" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V154" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W154" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:29">
       <x:c r="A155" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B155" s="1" t="n">
         <x:v>35898</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D155" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F155" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H155" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="I155" s="1" t="n">
         <x:v>4</x:v>
@@ -10702,37 +11875,70 @@
       <x:c r="J155" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="K155" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L155" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M155" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N155" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O155" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P155" s="1" t="n">
+        <x:v>5.1</x:v>
+      </x:c>
+      <x:c r="Q155" s="1" t="n">
+        <x:v>80.9574</x:v>
+      </x:c>
+      <x:c r="R155" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S155" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T155" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U155" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V155" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W155" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:29">
       <x:c r="A156" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B156" s="1" t="n">
         <x:v>35899</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F156" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H156" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="I156" s="1" t="n">
         <x:v>4</x:v>
@@ -10740,37 +11946,70 @@
       <x:c r="J156" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="K156" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L156" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M156" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N156" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O156" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P156" s="1" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="Q156" s="1" t="n">
+        <x:v>3.1748</x:v>
+      </x:c>
+      <x:c r="R156" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S156" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T156" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U156" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V156" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W156" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:29">
       <x:c r="A157" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4485225694</x:v>
       </x:c>
       <x:c r="B157" s="1" t="n">
         <x:v>35900</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D157" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="F157" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H157" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="I157" s="1" t="n">
         <x:v>6</x:v>
@@ -10778,37 +12017,70 @@
       <x:c r="J157" s="1" t="n">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="K157" s="4">
+        <x:v>46087.078303206</x:v>
+      </x:c>
       <x:c r="L157" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46087.0783034375</x:v>
       </x:c>
       <x:c r="M157" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="N157" s="4">
+        <x:v>46090.4474321412</x:v>
+      </x:c>
+      <x:c r="O157" s="1" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="P157" s="1" t="n">
+        <x:v>8.5</x:v>
+      </x:c>
+      <x:c r="Q157" s="1" t="n">
+        <x:v>202.3935</x:v>
+      </x:c>
+      <x:c r="R157" s="1" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="S157" s="1" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="T157" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U157" s="1" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="V157" s="1" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="W157" s="3">
+        <x:v>46099</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:29">
       <x:c r="A158" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B158" s="1" t="n">
         <x:v>35901</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="F158" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H158" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="I158" s="1" t="n">
         <x:v>2</x:v>
@@ -10816,37 +12088,70 @@
       <x:c r="J158" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K158" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L158" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M158" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N158" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O158" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P158" s="1" t="n">
+        <x:v>35.63</x:v>
+      </x:c>
+      <x:c r="Q158" s="1" t="n">
+        <x:v>282.79531</x:v>
+      </x:c>
+      <x:c r="R158" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S158" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T158" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U158" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V158" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W158" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:29">
       <x:c r="A159" s="4">
-        <x:v>46076.6827677083</x:v>
+        <x:v>46086.6411116088</x:v>
       </x:c>
       <x:c r="B159" s="1" t="n">
         <x:v>35902</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="I159" s="1" t="n">
         <x:v>2</x:v>
@@ -10858,33 +12163,36 @@
         <x:v>46076.6827676736</x:v>
       </x:c>
       <x:c r="M159" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="R159" s="1" t="s">
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:29">
       <x:c r="A160" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B160" s="1" t="n">
         <x:v>35903</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D160" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="F160" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="I160" s="1" t="n">
         <x:v>4</x:v>
@@ -10892,37 +12200,70 @@
       <x:c r="J160" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="K160" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L160" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M160" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N160" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O160" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P160" s="1" t="n">
+        <x:v>10.11</x:v>
+      </x:c>
+      <x:c r="Q160" s="1" t="n">
+        <x:v>160.48614</x:v>
+      </x:c>
+      <x:c r="R160" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S160" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T160" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U160" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V160" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W160" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:29">
       <x:c r="A161" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B161" s="1" t="n">
         <x:v>35904</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D161" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="F161" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="I161" s="1" t="n">
         <x:v>4</x:v>
@@ -10930,37 +12271,70 @@
       <x:c r="J161" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="K161" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L161" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M161" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N161" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O161" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P161" s="1" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="Q161" s="1" t="n">
+        <x:v>13.01668</x:v>
+      </x:c>
+      <x:c r="R161" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S161" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T161" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U161" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V161" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W161" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:29">
       <x:c r="A162" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B162" s="1" t="n">
         <x:v>35905</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D162" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F162" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="I162" s="1" t="n">
         <x:v>4</x:v>
@@ -10968,37 +12342,70 @@
       <x:c r="J162" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="K162" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L162" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M162" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N162" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O162" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P162" s="1" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="Q162" s="1" t="n">
+        <x:v>2.3811</x:v>
+      </x:c>
+      <x:c r="R162" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S162" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T162" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U162" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V162" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W162" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:29">
       <x:c r="A163" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B163" s="1" t="n">
         <x:v>35906</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D163" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F163" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G163" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H163" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="I163" s="1" t="n">
         <x:v>1</x:v>
@@ -11006,37 +12413,70 @@
       <x:c r="J163" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K163" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L163" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M163" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N163" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O163" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P163" s="1" t="n">
+        <x:v>3.65</x:v>
+      </x:c>
+      <x:c r="Q163" s="1" t="n">
+        <x:v>14.485025</x:v>
+      </x:c>
+      <x:c r="R163" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S163" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T163" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U163" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V163" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W163" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:29">
       <x:c r="A164" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B164" s="1" t="n">
         <x:v>35907</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D164" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F164" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G164" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H164" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="I164" s="1" t="n">
         <x:v>2</x:v>
@@ -11044,37 +12484,70 @@
       <x:c r="J164" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K164" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L164" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M164" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N164" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O164" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P164" s="1" t="n">
+        <x:v>6.75</x:v>
+      </x:c>
+      <x:c r="Q164" s="1" t="n">
+        <x:v>53.57475</x:v>
+      </x:c>
+      <x:c r="R164" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S164" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T164" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U164" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V164" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W164" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:29">
       <x:c r="A165" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B165" s="1" t="n">
         <x:v>35908</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D165" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F165" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G165" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I165" s="1" t="n">
         <x:v>6</x:v>
@@ -11082,37 +12555,70 @@
       <x:c r="J165" s="1" t="n">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="K165" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L165" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M165" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N165" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O165" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P165" s="1" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="Q165" s="1" t="n">
+        <x:v>3.80976</x:v>
+      </x:c>
+      <x:c r="R165" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S165" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T165" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U165" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V165" s="1" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="W165" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:29">
       <x:c r="A166" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B166" s="1" t="n">
         <x:v>35909</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F166" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G166" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="I166" s="1" t="n">
         <x:v>2</x:v>
@@ -11120,37 +12626,70 @@
       <x:c r="J166" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K166" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L166" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M166" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N166" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O166" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P166" s="1" t="n">
+        <x:v>3.48</x:v>
+      </x:c>
+      <x:c r="Q166" s="1" t="n">
+        <x:v>27.62076</x:v>
+      </x:c>
+      <x:c r="R166" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S166" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T166" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U166" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V166" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W166" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:29">
       <x:c r="A167" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4485225694</x:v>
       </x:c>
       <x:c r="B167" s="1" t="n">
         <x:v>35910</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D167" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="F167" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="G167" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="I167" s="1" t="n">
         <x:v>2</x:v>
@@ -11158,37 +12697,70 @@
       <x:c r="J167" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K167" s="4">
+        <x:v>46087.078303206</x:v>
+      </x:c>
       <x:c r="L167" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46087.0783034375</x:v>
       </x:c>
       <x:c r="M167" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="N167" s="4">
+        <x:v>46090.4474321412</x:v>
+      </x:c>
+      <x:c r="O167" s="1" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="P167" s="1" t="n">
+        <x:v>8.5</x:v>
+      </x:c>
+      <x:c r="Q167" s="1" t="n">
+        <x:v>67.4645</x:v>
+      </x:c>
+      <x:c r="R167" s="1" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="S167" s="1" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="T167" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U167" s="1" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="V167" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W167" s="3">
+        <x:v>46099</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:29">
       <x:c r="A168" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B168" s="1" t="n">
         <x:v>35911</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D168" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F168" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G168" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I168" s="1" t="n">
         <x:v>8</x:v>
@@ -11196,37 +12768,70 @@
       <x:c r="J168" s="1" t="n">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="K168" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L168" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M168" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N168" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O168" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P168" s="1" t="n">
+        <x:v>0.63</x:v>
+      </x:c>
+      <x:c r="Q168" s="1" t="n">
+        <x:v>20.00124</x:v>
+      </x:c>
+      <x:c r="R168" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S168" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T168" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U168" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V168" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="W168" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:29">
       <x:c r="A169" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B169" s="1" t="n">
         <x:v>35912</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F169" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G169" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="I169" s="1" t="n">
         <x:v>2</x:v>
@@ -11234,16 +12839,49 @@
       <x:c r="J169" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K169" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L169" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M169" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N169" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O169" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P169" s="1" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="Q169" s="1" t="n">
+        <x:v>13.88975</x:v>
+      </x:c>
+      <x:c r="R169" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S169" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T169" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U169" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V169" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W169" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:29">
       <x:c r="A170" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46085.0734823264</x:v>
       </x:c>
       <x:c r="B170" s="1" t="n">
         <x:v>35913</x:v>
@@ -11255,16 +12893,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F170" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="G170" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H170" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="I170" s="1" t="n">
         <x:v>1</x:v>
@@ -11273,36 +12911,36 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L170" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46085.0733793634</x:v>
       </x:c>
       <x:c r="M170" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:29">
       <x:c r="A171" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B171" s="1" t="n">
         <x:v>35914</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D171" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F171" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G171" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H171" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="I171" s="1" t="n">
         <x:v>4</x:v>
@@ -11310,37 +12948,70 @@
       <x:c r="J171" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="K171" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L171" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M171" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N171" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O171" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P171" s="1" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="Q171" s="1" t="n">
+        <x:v>58.7338</x:v>
+      </x:c>
+      <x:c r="R171" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S171" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T171" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U171" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V171" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W171" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:29">
       <x:c r="A172" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B172" s="1" t="n">
         <x:v>35915</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="F172" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="G172" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H172" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="I172" s="1" t="n">
         <x:v>1</x:v>
@@ -11348,37 +13019,70 @@
       <x:c r="J172" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K172" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
       <x:c r="L172" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M172" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N172" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O172" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P172" s="1" t="n">
+        <x:v>5.86</x:v>
+      </x:c>
+      <x:c r="Q172" s="1" t="n">
+        <x:v>23.25541</x:v>
+      </x:c>
+      <x:c r="R172" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S172" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T172" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U172" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V172" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W172" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:29">
       <x:c r="A173" s="4">
-        <x:v>46072.6396216782</x:v>
+        <x:v>46090.447941169</x:v>
       </x:c>
       <x:c r="B173" s="1" t="n">
         <x:v>35916</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F173" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="G173" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H173" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="I173" s="1" t="n">
         <x:v>1</x:v>
@@ -11386,28 +13090,61 @@
       <x:c r="J173" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K173" s="4">
+        <x:v>46085.6136977199</x:v>
+      </x:c>
       <x:c r="L173" s="4">
-        <x:v>46072.6396216088</x:v>
+        <x:v>46090.4477212616</x:v>
       </x:c>
       <x:c r="M173" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="N173" s="4">
+        <x:v>46090.447721412</x:v>
+      </x:c>
+      <x:c r="O173" s="1" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="P173" s="1" t="n">
+        <x:v>885</x:v>
+      </x:c>
+      <x:c r="Q173" s="1" t="n">
+        <x:v>885</x:v>
+      </x:c>
+      <x:c r="R173" s="1" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="S173" s="1" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="T173" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U173" s="1" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="V173" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W173" s="3">
+        <x:v>46113</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:29">
       <x:c r="A174" s="4">
-        <x:v>46078.6608928241</x:v>
+        <x:v>46092.6276936343</x:v>
       </x:c>
       <x:c r="B174" s="1" t="n">
         <x:v>36010</x:v>
       </x:c>
       <x:c r="C174" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F174" s="1" t="s">
         <x:v>51</x:v>
@@ -11421,37 +13158,70 @@
       <x:c r="J174" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K174" s="4">
+        <x:v>46092.6231591088</x:v>
+      </x:c>
       <x:c r="L174" s="4">
-        <x:v>46076.6806459491</x:v>
+        <x:v>46092.627584375</x:v>
       </x:c>
       <x:c r="M174" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="N174" s="4">
+        <x:v>46092.6275845255</x:v>
+      </x:c>
+      <x:c r="O174" s="1" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="P174" s="1" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="Q174" s="1" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="R174" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="S174" s="1" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="T174" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U174" s="1" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="V174" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W174" s="3">
+        <x:v>46094</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:29">
       <x:c r="A175" s="4">
-        <x:v>46083.5089856829</x:v>
+        <x:v>46093.004525081</x:v>
       </x:c>
       <x:c r="B175" s="1" t="n">
         <x:v>36279</x:v>
       </x:c>
       <x:c r="C175" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="D175" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F175" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="G175" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="I175" s="1" t="n">
         <x:v>1</x:v>
@@ -11459,37 +13229,49 @@
       <x:c r="J175" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K175" s="4">
+        <x:v>46093.0045248843</x:v>
+      </x:c>
       <x:c r="L175" s="4">
-        <x:v>46083.4492662037</x:v>
+        <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M175" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="R175" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="S175" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="T175" s="1" t="n">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:29">
       <x:c r="A176" s="4">
-        <x:v>46083.5089856829</x:v>
+        <x:v>46093.004525081</x:v>
       </x:c>
       <x:c r="B176" s="1" t="n">
         <x:v>36280</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F176" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="G176" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H176" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="I176" s="1" t="n">
         <x:v>4</x:v>
@@ -11497,37 +13279,49 @@
       <x:c r="J176" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="K176" s="4">
+        <x:v>46093.0045248843</x:v>
+      </x:c>
       <x:c r="L176" s="4">
-        <x:v>46083.4492662037</x:v>
+        <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M176" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="R176" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="S176" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="T176" s="1" t="n">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:29">
       <x:c r="A177" s="4">
-        <x:v>46083.5089856829</x:v>
+        <x:v>46093.004525081</x:v>
       </x:c>
       <x:c r="B177" s="1" t="n">
         <x:v>36281</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="F177" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="G177" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H177" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="I177" s="1" t="n">
         <x:v>4</x:v>
@@ -11535,16 +13329,28 @@
       <x:c r="J177" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="K177" s="4">
+        <x:v>46093.0045248843</x:v>
+      </x:c>
       <x:c r="L177" s="4">
-        <x:v>46083.4492662037</x:v>
+        <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M177" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="R177" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="S177" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="T177" s="1" t="n">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:29">
       <x:c r="A178" s="4">
-        <x:v>46083.5089856829</x:v>
+        <x:v>46093.0051498032</x:v>
       </x:c>
       <x:c r="B178" s="1" t="n">
         <x:v>36282</x:v>
@@ -11556,16 +13362,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="F178" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="G178" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H178" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="I178" s="1" t="n">
         <x:v>1</x:v>
@@ -11574,15 +13380,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L178" s="4">
-        <x:v>46083.4492662037</x:v>
+        <x:v>46093.0051497338</x:v>
       </x:c>
       <x:c r="M178" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>476</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:29">
       <x:c r="A179" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B179" s="1" t="n">
         <x:v>36360</x:v>
@@ -11591,10 +13397,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="F179" s="1" t="s">
         <x:v>51</x:v>
@@ -11609,15 +13415,15 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L179" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M179" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:29">
       <x:c r="A180" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4166482292</x:v>
       </x:c>
       <x:c r="B180" s="1" t="n">
         <x:v>36361</x:v>
@@ -11626,10 +13432,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="F180" s="1" t="s">
         <x:v>64</x:v>
@@ -11644,15 +13450,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L180" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4128305208</x:v>
       </x:c>
       <x:c r="M180" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:29">
       <x:c r="A181" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B181" s="1" t="n">
         <x:v>36362</x:v>
@@ -11661,10 +13467,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F181" s="1" t="s">
         <x:v>51</x:v>
@@ -11679,15 +13485,15 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L181" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M181" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:29">
       <x:c r="A182" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B182" s="1" t="n">
         <x:v>36363</x:v>
@@ -11696,10 +13502,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="F182" s="1" t="s">
         <x:v>51</x:v>
@@ -11714,15 +13520,15 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L182" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M182" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:29">
       <x:c r="A183" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B183" s="1" t="n">
         <x:v>36364</x:v>
@@ -11731,10 +13537,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="F183" s="1" t="s">
         <x:v>51</x:v>
@@ -11749,15 +13555,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L183" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M183" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:29">
       <x:c r="A184" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B184" s="1" t="n">
         <x:v>36365</x:v>
@@ -11766,10 +13572,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F184" s="1" t="s">
         <x:v>51</x:v>
@@ -11784,15 +13590,15 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L184" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M184" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:29">
       <x:c r="A185" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B185" s="1" t="n">
         <x:v>36366</x:v>
@@ -11801,10 +13607,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F185" s="1" t="s">
         <x:v>51</x:v>
@@ -11819,15 +13625,15 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L185" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M185" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:29">
       <x:c r="A186" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B186" s="1" t="n">
         <x:v>36367</x:v>
@@ -11836,10 +13642,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E186" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="F186" s="1" t="s">
         <x:v>51</x:v>
@@ -11854,15 +13660,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L186" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M186" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:29">
       <x:c r="A187" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B187" s="1" t="n">
         <x:v>36368</x:v>
@@ -11871,10 +13677,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E187" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="F187" s="1" t="s">
         <x:v>51</x:v>
@@ -11889,15 +13695,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L187" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M187" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:29">
       <x:c r="A188" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46086.6875060185</x:v>
       </x:c>
       <x:c r="B188" s="1" t="n">
         <x:v>36369</x:v>
@@ -11906,10 +13712,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F188" s="1" t="s">
         <x:v>158</x:v>
@@ -11924,15 +13730,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L188" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4131163542</x:v>
       </x:c>
       <x:c r="M188" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="R188" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="S188" s="1" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="T188" s="1" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:29">
       <x:c r="A189" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B189" s="1" t="n">
         <x:v>36370</x:v>
@@ -11941,10 +13756,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F189" s="1" t="s">
         <x:v>51</x:v>
@@ -11959,15 +13774,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L189" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M189" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:29">
       <x:c r="A190" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B190" s="1" t="n">
         <x:v>36371</x:v>
@@ -11976,10 +13791,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F190" s="1" t="s">
         <x:v>51</x:v>
@@ -11994,15 +13809,15 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L190" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M190" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:29">
       <x:c r="A191" s="4">
-        <x:v>46084.7959738426</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B191" s="1" t="n">
         <x:v>36372</x:v>
@@ -12011,10 +13826,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F191" s="1" t="s">
         <x:v>51</x:v>
@@ -12029,10 +13844,447 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L191" s="4">
-        <x:v>46084.7959737616</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M191" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:29">
+      <x:c r="A192" s="4">
+        <x:v>46090.4467435532</x:v>
+      </x:c>
+      <x:c r="B192" s="1" t="n">
+        <x:v>36373</x:v>
+      </x:c>
+      <x:c r="C192" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D192" s="1" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="E192" s="1" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="F192" s="1" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="G192" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H192" s="1" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="I192" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J192" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K192" s="4">
+        <x:v>46086.7622765857</x:v>
+      </x:c>
+      <x:c r="L192" s="4">
+        <x:v>46086.7622771991</x:v>
+      </x:c>
+      <x:c r="M192" s="1" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="N192" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O192" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P192" s="1" t="n">
+        <x:v>88.87</x:v>
+      </x:c>
+      <x:c r="Q192" s="1" t="n">
+        <x:v>705.36119</x:v>
+      </x:c>
+      <x:c r="R192" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S192" s="1" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="T192" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U192" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V192" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W192" s="3">
+        <x:v>46095</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:29">
+      <x:c r="A193" s="4">
+        <x:v>46090.4467435532</x:v>
+      </x:c>
+      <x:c r="B193" s="1" t="n">
+        <x:v>36374</x:v>
+      </x:c>
+      <x:c r="C193" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D193" s="1" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="E193" s="1" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="F193" s="1" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="G193" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H193" s="1" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="I193" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J193" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K193" s="4">
+        <x:v>46086.7622765857</x:v>
+      </x:c>
+      <x:c r="L193" s="4">
+        <x:v>46086.7622771991</x:v>
+      </x:c>
+      <x:c r="M193" s="1" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="N193" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O193" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P193" s="1" t="n">
+        <x:v>2.51</x:v>
+      </x:c>
+      <x:c r="Q193" s="1" t="n">
+        <x:v>19.92187</x:v>
+      </x:c>
+      <x:c r="R193" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S193" s="1" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="T193" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U193" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V193" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W193" s="3">
+        <x:v>46095</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:29">
+      <x:c r="A194" s="4">
+        <x:v>46090.4467435532</x:v>
+      </x:c>
+      <x:c r="B194" s="1" t="n">
+        <x:v>36375</x:v>
+      </x:c>
+      <x:c r="C194" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D194" s="1" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="E194" s="1" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="F194" s="1" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G194" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H194" s="1" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="I194" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J194" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K194" s="4">
+        <x:v>46086.7622765857</x:v>
+      </x:c>
+      <x:c r="L194" s="4">
+        <x:v>46086.7622771991</x:v>
+      </x:c>
+      <x:c r="M194" s="1" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="N194" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O194" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P194" s="1" t="n">
+        <x:v>5.72</x:v>
+      </x:c>
+      <x:c r="Q194" s="1" t="n">
+        <x:v>45.39964</x:v>
+      </x:c>
+      <x:c r="R194" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S194" s="1" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="T194" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U194" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V194" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W194" s="3">
+        <x:v>46095</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:29">
+      <x:c r="A195" s="4">
+        <x:v>46090.4467435532</x:v>
+      </x:c>
+      <x:c r="B195" s="1" t="n">
+        <x:v>36376</x:v>
+      </x:c>
+      <x:c r="C195" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D195" s="1" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="E195" s="1" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="F195" s="1" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G195" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H195" s="1" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="I195" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J195" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K195" s="4">
+        <x:v>46086.7622765857</x:v>
+      </x:c>
+      <x:c r="L195" s="4">
+        <x:v>46086.7622771991</x:v>
+      </x:c>
+      <x:c r="M195" s="1" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="N195" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O195" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P195" s="1" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="Q195" s="1" t="n">
+        <x:v>7.1433</x:v>
+      </x:c>
+      <x:c r="R195" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S195" s="1" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="T195" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U195" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V195" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W195" s="3">
+        <x:v>46095</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:29">
+      <x:c r="A196" s="4">
+        <x:v>46090.4467435532</x:v>
+      </x:c>
+      <x:c r="B196" s="1" t="n">
+        <x:v>36508</x:v>
+      </x:c>
+      <x:c r="C196" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E196" s="1" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="G196" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="J196" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K196" s="4">
+        <x:v>46086.6518195255</x:v>
+      </x:c>
+      <x:c r="L196" s="4">
+        <x:v>46086.6518199421</x:v>
+      </x:c>
+      <x:c r="M196" s="1" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="N196" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O196" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P196" s="1" t="n">
+        <x:v>52.64</x:v>
+      </x:c>
+      <x:c r="Q196" s="1" t="n">
+        <x:v>208.90184</x:v>
+      </x:c>
+      <x:c r="R196" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S196" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="T196" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U196" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V196" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W196" s="3">
+        <x:v>46095</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:29">
+      <x:c r="A197" s="4">
+        <x:v>46087.3857842245</x:v>
+      </x:c>
+      <x:c r="B197" s="1" t="n">
+        <x:v>36516</x:v>
+      </x:c>
+      <x:c r="C197" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D197" s="1" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="E197" s="1" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="F197" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G197" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I197" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J197" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L197" s="4">
+        <x:v>46086.7566555556</x:v>
+      </x:c>
+      <x:c r="M197" s="1" t="s">
+        <x:v>509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:29">
+      <x:c r="A198" s="4">
+        <x:v>46090.4467435532</x:v>
+      </x:c>
+      <x:c r="B198" s="1" t="n">
+        <x:v>36518</x:v>
+      </x:c>
+      <x:c r="C198" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E198" s="1" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="G198" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="J198" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K198" s="4">
+        <x:v>46086.7622765857</x:v>
+      </x:c>
+      <x:c r="L198" s="4">
+        <x:v>46086.7622771991</x:v>
+      </x:c>
+      <x:c r="M198" s="1" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="N198" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O198" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P198" s="1" t="n">
+        <x:v>92.08</x:v>
+      </x:c>
+      <x:c r="Q198" s="1" t="n">
+        <x:v>365.41948</x:v>
+      </x:c>
+      <x:c r="R198" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S198" s="1" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="T198" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U198" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V198" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W198" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/bom.xlsx
+++ b/bom.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="511">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
   <x:si>
     <x:t>Document No</x:t>
   </x:si>
@@ -396,7 +396,7 @@
     <x:t>SAPO26010110</x:t>
   </x:si>
   <x:si>
-    <x:t>HOIST Module</x:t>
+    <x:t>HOIST</x:t>
   </x:si>
   <x:si>
     <x:t>F1 20MM wide Elatech Italy Open-End Black PU/Polyurethane Steel Cord Flat Belt</x:t>
@@ -1026,9 +1026,6 @@
   </x:si>
   <x:si>
     <x:t>OMRP513-F3005-00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOIST</x:t>
   </x:si>
   <x:si>
     <x:t>OMRP513-F2001-00</x:t>
@@ -1245,6 +1242,9 @@
     <x:t>height sensor</x:t>
   </x:si>
   <x:si>
+    <x:t>Banner</x:t>
+  </x:si>
+  <x:si>
     <x:t>A0-139452_EP01</x:t>
   </x:si>
   <x:si>
@@ -1263,10 +1263,20 @@
     <x:t>C-SX2RL24-L_b</x:t>
   </x:si>
   <x:si>
+    <x:t>RFQ4134551</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ Reject</x:t>
+  </x:si>
+  <x:si>
+    <x:t>clamp plate</x:t>
+  </x:si>
+  <x:si>
     <x:t>RFQ4129252</x:t>
   </x:si>
   <x:si>
-    <x:t>clamp plate</x:t>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45809
+</x:t>
   </x:si>
   <x:si>
     <x:t>motor</x:t>
@@ -1276,6 +1286,22 @@
   </x:si>
   <x:si>
     <x:t>PVD-PX110-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4133271</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5327031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fulitech Technology Co. Limited</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/46660
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAPO26030523</x:t>
   </x:si>
   <x:si>
     <x:t>Pivot Pin</x:t>
@@ -1321,9 +1347,6 @@
     <x:t>PR5319341</x:t>
   </x:si>
   <x:si>
-    <x:t>Fulitech Technology Co. Limited</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45744
 </x:t>
   </x:si>
@@ -1339,9 +1362,6 @@
 </x:t>
   </x:si>
   <x:si>
-    <x:t>RFQ Reject</x:t>
-  </x:si>
-  <x:si>
     <x:t>Linear Guide Bearing</x:t>
   </x:si>
   <x:si>
@@ -1483,9 +1503,6 @@
     <x:t>SAPO26030296</x:t>
   </x:si>
   <x:si>
-    <x:t>RFQ Approved</x:t>
-  </x:si>
-  <x:si>
     <x:t>misumi [YHD]</x:t>
   </x:si>
   <x:si>
@@ -1493,12 +1510,18 @@
   </x:si>
   <x:si>
     <x:t>RFQ4130402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5327071</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/46459
 </x:t>
   </x:si>
   <x:si>
+    <x:t>SAPO26030524</x:t>
+  </x:si>
+  <x:si>
     <x:t>ball plungers</x:t>
   </x:si>
   <x:si>
@@ -1560,12 +1583,18 @@
   </x:si>
   <x:si>
     <x:t>RFQ4130871</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5328791</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45815
 </x:t>
   </x:si>
   <x:si>
+    <x:t>SAPO26030607</x:t>
+  </x:si>
+  <x:si>
     <x:t>OMR-STR-F1124A</x:t>
   </x:si>
   <x:si>
@@ -1628,6 +1657,33 @@
   </x:si>
   <x:si>
     <x:t>SHIPPING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Track</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OMR-2701A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4133302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OMR-2702A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OMR-2705A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OMR-2706A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OMR-2703A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4133662</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OMR-2704A</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2016,7 +2072,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AC198"/>
+  <x:dimension ref="A1:AC204"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="30" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3505,7 +3561,7 @@
     </x:row>
     <x:row r="27" spans="1:29">
       <x:c r="A27" s="4">
-        <x:v>46029.6167459838</x:v>
+        <x:v>46113.7096591435</x:v>
       </x:c>
       <x:c r="B27" s="1" t="n">
         <x:v>32341</x:v>
@@ -8598,10 +8654,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E103" s="1" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="E103" s="1" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
         <x:v>51</x:v>
@@ -8622,13 +8678,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M103" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N103" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O103" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P103" s="1" t="n">
         <x:v>70</x:v>
@@ -8640,13 +8696,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S103" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T103" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U103" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T103" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U103" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V103" s="1" t="n">
         <x:v>4</x:v>
@@ -8666,10 +8722,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
         <x:v>51</x:v>
@@ -8690,13 +8746,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M104" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N104" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O104" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P104" s="1" t="n">
         <x:v>35</x:v>
@@ -8708,13 +8764,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S104" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T104" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U104" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T104" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U104" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V104" s="1" t="n">
         <x:v>1</x:v>
@@ -8734,10 +8790,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
         <x:v>51</x:v>
@@ -8758,13 +8814,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M105" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N105" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O105" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P105" s="1" t="n">
         <x:v>85</x:v>
@@ -8776,13 +8832,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S105" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T105" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U105" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T105" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U105" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V105" s="1" t="n">
         <x:v>2</x:v>
@@ -8802,10 +8858,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
         <x:v>51</x:v>
@@ -8826,13 +8882,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M106" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N106" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O106" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P106" s="1" t="n">
         <x:v>275</x:v>
@@ -8844,13 +8900,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S106" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T106" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U106" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T106" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U106" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V106" s="1" t="n">
         <x:v>1</x:v>
@@ -8870,10 +8926,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
         <x:v>51</x:v>
@@ -8894,13 +8950,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M107" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N107" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O107" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P107" s="1" t="n">
         <x:v>50</x:v>
@@ -8912,13 +8968,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S107" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T107" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U107" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T107" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U107" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V107" s="1" t="n">
         <x:v>12</x:v>
@@ -8938,10 +8994,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
         <x:v>51</x:v>
@@ -8962,13 +9018,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M108" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N108" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O108" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P108" s="1" t="n">
         <x:v>25</x:v>
@@ -8980,13 +9036,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S108" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T108" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U108" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T108" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U108" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V108" s="1" t="n">
         <x:v>6</x:v>
@@ -9006,10 +9062,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
         <x:v>51</x:v>
@@ -9030,13 +9086,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M109" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N109" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O109" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P109" s="1" t="n">
         <x:v>100</x:v>
@@ -9048,13 +9104,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S109" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T109" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U109" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T109" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U109" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V109" s="1" t="n">
         <x:v>2</x:v>
@@ -9074,10 +9130,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F110" s="1" t="s">
         <x:v>51</x:v>
@@ -9098,13 +9154,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M110" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N110" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O110" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P110" s="1" t="n">
         <x:v>20</x:v>
@@ -9116,13 +9172,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S110" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T110" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U110" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T110" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U110" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V110" s="1" t="n">
         <x:v>12</x:v>
@@ -9142,10 +9198,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
         <x:v>51</x:v>
@@ -9166,13 +9222,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M111" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N111" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O111" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P111" s="1" t="n">
         <x:v>155</x:v>
@@ -9184,13 +9240,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S111" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T111" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U111" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T111" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U111" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V111" s="1" t="n">
         <x:v>1</x:v>
@@ -9210,10 +9266,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
         <x:v>51</x:v>
@@ -9234,13 +9290,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M112" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N112" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O112" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P112" s="1" t="n">
         <x:v>135</x:v>
@@ -9252,13 +9308,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S112" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T112" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U112" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T112" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U112" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V112" s="1" t="n">
         <x:v>4</x:v>
@@ -9278,10 +9334,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="F113" s="1" t="s">
         <x:v>51</x:v>
@@ -9302,13 +9358,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M113" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N113" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O113" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P113" s="1" t="n">
         <x:v>25</x:v>
@@ -9320,13 +9376,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S113" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T113" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U113" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T113" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U113" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V113" s="1" t="n">
         <x:v>2</x:v>
@@ -9346,10 +9402,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F114" s="1" t="s">
         <x:v>51</x:v>
@@ -9370,13 +9426,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M114" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N114" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O114" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P114" s="1" t="n">
         <x:v>20</x:v>
@@ -9388,13 +9444,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S114" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T114" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U114" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T114" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U114" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V114" s="1" t="n">
         <x:v>2</x:v>
@@ -9414,10 +9470,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="F115" s="1" t="s">
         <x:v>51</x:v>
@@ -9438,13 +9494,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M115" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N115" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O115" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P115" s="1" t="n">
         <x:v>80</x:v>
@@ -9456,13 +9512,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S115" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T115" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U115" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T115" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U115" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V115" s="1" t="n">
         <x:v>2</x:v>
@@ -9482,10 +9538,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="F116" s="1" t="s">
         <x:v>51</x:v>
@@ -9506,13 +9562,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M116" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N116" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O116" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P116" s="1" t="n">
         <x:v>15</x:v>
@@ -9524,13 +9580,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S116" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T116" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U116" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T116" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U116" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V116" s="1" t="n">
         <x:v>8</x:v>
@@ -9550,10 +9606,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F117" s="1" t="s">
         <x:v>51</x:v>
@@ -9574,13 +9630,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M117" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N117" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O117" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P117" s="1" t="n">
         <x:v>18</x:v>
@@ -9592,13 +9648,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S117" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T117" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U117" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T117" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U117" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V117" s="1" t="n">
         <x:v>4</x:v>
@@ -9618,10 +9674,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="F118" s="1" t="s">
         <x:v>51</x:v>
@@ -9642,13 +9698,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M118" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N118" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O118" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P118" s="1" t="n">
         <x:v>20</x:v>
@@ -9660,13 +9716,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S118" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T118" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U118" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T118" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U118" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V118" s="1" t="n">
         <x:v>2</x:v>
@@ -9686,10 +9742,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F119" s="1" t="s">
         <x:v>51</x:v>
@@ -9710,13 +9766,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M119" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N119" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O119" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P119" s="1" t="n">
         <x:v>20</x:v>
@@ -9728,13 +9784,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S119" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T119" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U119" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T119" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U119" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V119" s="1" t="n">
         <x:v>2</x:v>
@@ -9754,10 +9810,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F120" s="1" t="s">
         <x:v>51</x:v>
@@ -9778,13 +9834,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M120" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N120" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O120" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P120" s="1" t="n">
         <x:v>60</x:v>
@@ -9796,13 +9852,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S120" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T120" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U120" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T120" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U120" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V120" s="1" t="n">
         <x:v>4</x:v>
@@ -9822,10 +9878,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F121" s="1" t="s">
         <x:v>51</x:v>
@@ -9846,13 +9902,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M121" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="N121" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O121" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="P121" s="1" t="n">
         <x:v>45</x:v>
@@ -9864,13 +9920,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S121" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="T121" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U121" s="1" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="T121" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U121" s="1" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="V121" s="1" t="n">
         <x:v>4</x:v>
@@ -9890,10 +9946,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="E122" s="1" t="s">
         <x:v>352</x:v>
-      </x:c>
-      <x:c r="E122" s="1" t="s">
-        <x:v>353</x:v>
       </x:c>
       <x:c r="F122" s="1" t="s">
         <x:v>51</x:v>
@@ -9914,13 +9970,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M122" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N122" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O122" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P122" s="1" t="n">
         <x:v>25</x:v>
@@ -9932,13 +9988,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S122" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T122" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U122" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T122" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U122" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V122" s="1" t="n">
         <x:v>6</x:v>
@@ -9958,10 +10014,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="F123" s="1" t="s">
         <x:v>51</x:v>
@@ -9982,13 +10038,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M123" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N123" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O123" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P123" s="1" t="n">
         <x:v>70</x:v>
@@ -10000,13 +10056,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S123" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T123" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U123" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T123" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U123" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V123" s="1" t="n">
         <x:v>2</x:v>
@@ -10026,10 +10082,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E124" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F124" s="1" t="s">
         <x:v>51</x:v>
@@ -10050,13 +10106,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M124" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N124" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O124" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P124" s="1" t="n">
         <x:v>40</x:v>
@@ -10068,13 +10124,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S124" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T124" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U124" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T124" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U124" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V124" s="1" t="n">
         <x:v>4</x:v>
@@ -10094,10 +10150,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F125" s="1" t="s">
         <x:v>51</x:v>
@@ -10118,13 +10174,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M125" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N125" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O125" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P125" s="1" t="n">
         <x:v>85</x:v>
@@ -10136,13 +10192,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S125" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T125" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U125" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T125" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U125" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V125" s="1" t="n">
         <x:v>2</x:v>
@@ -10162,10 +10218,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="F126" s="1" t="s">
         <x:v>51</x:v>
@@ -10186,13 +10242,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M126" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N126" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O126" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P126" s="1" t="n">
         <x:v>120</x:v>
@@ -10204,13 +10260,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S126" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T126" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U126" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T126" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U126" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V126" s="1" t="n">
         <x:v>4</x:v>
@@ -10230,10 +10286,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F127" s="1" t="s">
         <x:v>51</x:v>
@@ -10254,13 +10310,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M127" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N127" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O127" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P127" s="1" t="n">
         <x:v>40</x:v>
@@ -10272,13 +10328,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S127" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T127" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U127" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T127" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U127" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V127" s="1" t="n">
         <x:v>4</x:v>
@@ -10298,10 +10354,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F128" s="1" t="s">
         <x:v>51</x:v>
@@ -10322,13 +10378,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M128" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N128" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O128" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P128" s="1" t="n">
         <x:v>100</x:v>
@@ -10340,13 +10396,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S128" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T128" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U128" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T128" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U128" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V128" s="1" t="n">
         <x:v>4</x:v>
@@ -10366,10 +10422,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="F129" s="1" t="s">
         <x:v>51</x:v>
@@ -10390,13 +10446,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M129" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N129" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O129" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P129" s="1" t="n">
         <x:v>80</x:v>
@@ -10408,13 +10464,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S129" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T129" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U129" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T129" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U129" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V129" s="1" t="n">
         <x:v>4</x:v>
@@ -10434,10 +10490,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="F130" s="1" t="s">
         <x:v>51</x:v>
@@ -10458,13 +10514,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M130" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N130" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O130" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P130" s="1" t="n">
         <x:v>25</x:v>
@@ -10476,13 +10532,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S130" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T130" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U130" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T130" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U130" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V130" s="1" t="n">
         <x:v>2</x:v>
@@ -10502,10 +10558,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F131" s="1" t="s">
         <x:v>51</x:v>
@@ -10526,13 +10582,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M131" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N131" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O131" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P131" s="1" t="n">
         <x:v>50</x:v>
@@ -10544,13 +10600,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S131" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T131" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U131" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T131" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U131" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V131" s="1" t="n">
         <x:v>2</x:v>
@@ -10570,10 +10626,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="F132" s="1" t="s">
         <x:v>51</x:v>
@@ -10594,13 +10650,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M132" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N132" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O132" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P132" s="1" t="n">
         <x:v>40</x:v>
@@ -10612,13 +10668,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S132" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T132" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U132" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T132" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U132" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V132" s="1" t="n">
         <x:v>2</x:v>
@@ -10638,10 +10694,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="F133" s="1" t="s">
         <x:v>51</x:v>
@@ -10662,13 +10718,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M133" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N133" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O133" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P133" s="1" t="n">
         <x:v>65</x:v>
@@ -10680,13 +10736,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S133" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T133" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U133" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T133" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U133" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V133" s="1" t="n">
         <x:v>1</x:v>
@@ -10706,10 +10762,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F134" s="1" t="s">
         <x:v>51</x:v>
@@ -10730,13 +10786,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M134" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N134" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O134" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P134" s="1" t="n">
         <x:v>45</x:v>
@@ -10748,13 +10804,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S134" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T134" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U134" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T134" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U134" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V134" s="1" t="n">
         <x:v>1</x:v>
@@ -10774,10 +10830,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="F135" s="1" t="s">
         <x:v>51</x:v>
@@ -10798,13 +10854,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M135" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N135" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O135" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P135" s="1" t="n">
         <x:v>17</x:v>
@@ -10816,13 +10872,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S135" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T135" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U135" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T135" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U135" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V135" s="1" t="n">
         <x:v>1</x:v>
@@ -10842,10 +10898,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F136" s="1" t="s">
         <x:v>51</x:v>
@@ -10866,13 +10922,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M136" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N136" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O136" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P136" s="1" t="n">
         <x:v>30</x:v>
@@ -10884,13 +10940,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S136" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T136" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U136" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T136" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U136" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V136" s="1" t="n">
         <x:v>2</x:v>
@@ -10910,10 +10966,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F137" s="1" t="s">
         <x:v>51</x:v>
@@ -10934,13 +10990,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M137" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N137" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O137" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P137" s="1" t="n">
         <x:v>40</x:v>
@@ -10952,13 +11008,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S137" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T137" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U137" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T137" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U137" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V137" s="1" t="n">
         <x:v>1</x:v>
@@ -10978,10 +11034,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F138" s="1" t="s">
         <x:v>51</x:v>
@@ -11002,13 +11058,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M138" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N138" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O138" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P138" s="1" t="n">
         <x:v>320</x:v>
@@ -11020,13 +11076,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S138" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T138" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U138" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T138" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U138" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V138" s="1" t="n">
         <x:v>1</x:v>
@@ -11046,10 +11102,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F139" s="1" t="s">
         <x:v>51</x:v>
@@ -11070,13 +11126,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M139" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="N139" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O139" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P139" s="1" t="n">
         <x:v>18</x:v>
@@ -11088,13 +11144,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S139" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="T139" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U139" s="1" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="T139" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U139" s="1" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="V139" s="1" t="n">
         <x:v>1</x:v>
@@ -11111,13 +11167,13 @@
         <x:v>35841</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="D140" s="1" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="E140" s="1" t="s">
         <x:v>375</x:v>
-      </x:c>
-      <x:c r="D140" s="1" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="E140" s="1" t="s">
-        <x:v>376</x:v>
       </x:c>
       <x:c r="F140" s="1" t="s">
         <x:v>158</x:v>
@@ -11138,13 +11194,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M140" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="R140" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S140" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="T140" s="1" t="n">
         <x:v>1</x:v>
@@ -11158,13 +11214,13 @@
         <x:v>35842</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F141" s="1" t="s">
         <x:v>158</x:v>
@@ -11185,13 +11241,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M141" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="R141" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S141" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="T141" s="1" t="n">
         <x:v>1</x:v>
@@ -11205,13 +11261,13 @@
         <x:v>35843</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F142" s="1" t="s">
         <x:v>158</x:v>
@@ -11232,13 +11288,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M142" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="R142" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S142" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="T142" s="1" t="n">
         <x:v>1</x:v>
@@ -11252,13 +11308,13 @@
         <x:v>35844</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F143" s="1" t="s">
         <x:v>158</x:v>
@@ -11279,13 +11335,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M143" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="R143" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S143" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="T143" s="1" t="n">
         <x:v>1</x:v>
@@ -11299,13 +11355,13 @@
         <x:v>35845</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="F144" s="1" t="s">
         <x:v>158</x:v>
@@ -11326,13 +11382,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M144" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="R144" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S144" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="T144" s="1" t="n">
         <x:v>1</x:v>
@@ -11346,13 +11402,13 @@
         <x:v>35846</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F145" s="1" t="s">
         <x:v>158</x:v>
@@ -11373,13 +11429,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M145" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="R145" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S145" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="T145" s="1" t="n">
         <x:v>1</x:v>
@@ -11387,7 +11443,7 @@
     </x:row>
     <x:row r="146" spans="1:29">
       <x:c r="A146" s="4">
-        <x:v>46086.6571485764</x:v>
+        <x:v>46111.4966081019</x:v>
       </x:c>
       <x:c r="B146" s="1" t="n">
         <x:v>35888</x:v>
@@ -11396,19 +11452,19 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="F146" s="1" t="s">
         <x:v>384</x:v>
-      </x:c>
-      <x:c r="F146" s="1" t="s">
-        <x:v>385</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H146" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="I146" s="1" t="n">
         <x:v>6</x:v>
@@ -11420,7 +11476,7 @@
         <x:v>46072.617799456</x:v>
       </x:c>
       <x:c r="M146" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:29">
@@ -11434,19 +11490,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D147" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="F147" s="1" t="s">
         <x:v>388</x:v>
-      </x:c>
-      <x:c r="F147" s="1" t="s">
-        <x:v>389</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H147" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="I147" s="1" t="n">
         <x:v>12</x:v>
@@ -11461,7 +11517,7 @@
         <x:v>46086.6600798611</x:v>
       </x:c>
       <x:c r="M147" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="N147" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11479,7 +11535,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S147" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="T147" s="1" t="n">
         <x:v>23</x:v>
@@ -11505,19 +11561,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D148" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="F148" s="1" t="s">
         <x:v>393</x:v>
-      </x:c>
-      <x:c r="F148" s="1" t="s">
-        <x:v>394</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H148" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="I148" s="1" t="n">
         <x:v>12</x:v>
@@ -11532,7 +11588,7 @@
         <x:v>46086.6600798611</x:v>
       </x:c>
       <x:c r="M148" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="N148" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11550,7 +11606,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S148" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="T148" s="1" t="n">
         <x:v>23</x:v>
@@ -11567,7 +11623,7 @@
     </x:row>
     <x:row r="149" spans="1:29">
       <x:c r="A149" s="4">
-        <x:v>46086.6571485764</x:v>
+        <x:v>46111.4966081019</x:v>
       </x:c>
       <x:c r="B149" s="1" t="n">
         <x:v>35891</x:v>
@@ -11576,10 +11632,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="F149" s="1" t="s">
         <x:v>396</x:v>
@@ -11600,12 +11656,12 @@
         <x:v>46072.617799456</x:v>
       </x:c>
       <x:c r="M149" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:29">
       <x:c r="A150" s="4">
-        <x:v>46086.6571485764</x:v>
+        <x:v>46111.4966081019</x:v>
       </x:c>
       <x:c r="B150" s="1" t="n">
         <x:v>35893</x:v>
@@ -11614,7 +11670,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
         <x:v>398</x:v>
@@ -11638,12 +11694,12 @@
         <x:v>46072.617799456</x:v>
       </x:c>
       <x:c r="M150" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:29">
       <x:c r="A151" s="4">
-        <x:v>46086.6557853356</x:v>
+        <x:v>46111.4595082523</x:v>
       </x:c>
       <x:c r="B151" s="1" t="n">
         <x:v>35894</x:v>
@@ -11658,7 +11714,7 @@
         <x:v>401</x:v>
       </x:c>
       <x:c r="F151" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
         <x:v>127</x:v>
@@ -11673,36 +11729,30 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L151" s="4">
-        <x:v>46072.6195613773</x:v>
+        <x:v>46107.609743669</x:v>
       </x:c>
       <x:c r="M151" s="1" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="R151" s="1" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="T151" s="1" t="n">
-        <x:v>21</x:v>
-      </x:c>
     </x:row>
     <x:row r="152" spans="1:29">
       <x:c r="A152" s="4">
-        <x:v>46086.6557853356</x:v>
+        <x:v>46099.715571794</x:v>
       </x:c>
       <x:c r="B152" s="1" t="n">
         <x:v>35895</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
         <x:v>321</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="F152" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
         <x:v>127</x:v>
@@ -11716,14 +11766,20 @@
       <x:c r="J152" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K152" s="4">
+        <x:v>46099.7155716435</x:v>
+      </x:c>
       <x:c r="L152" s="4">
-        <x:v>46072.6195613773</x:v>
+        <x:v>46099.7155717245</x:v>
       </x:c>
       <x:c r="M152" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="R152" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S152" s="1" t="s">
+        <x:v>407</x:v>
       </x:c>
       <x:c r="T152" s="1" t="n">
         <x:v>21</x:v>
@@ -11731,28 +11787,28 @@
     </x:row>
     <x:row r="153" spans="1:29">
       <x:c r="A153" s="4">
-        <x:v>46086.6557853356</x:v>
+        <x:v>46107.610496794</x:v>
       </x:c>
       <x:c r="B153" s="1" t="n">
         <x:v>35896</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
         <x:v>321</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F153" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H153" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="I153" s="1" t="n">
         <x:v>1</x:v>
@@ -11760,17 +11816,44 @@
       <x:c r="J153" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K153" s="4">
+        <x:v>46098.4855049769</x:v>
+      </x:c>
       <x:c r="L153" s="4">
-        <x:v>46072.6195613773</x:v>
+        <x:v>46107.6101008102</x:v>
       </x:c>
       <x:c r="M153" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="N153" s="4">
+        <x:v>46107.6101011227</x:v>
+      </x:c>
+      <x:c r="O153" s="1" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="P153" s="1" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="Q153" s="1" t="n">
+        <x:v>1318.185</x:v>
       </x:c>
       <x:c r="R153" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="S153" s="1" t="s">
+        <x:v>414</x:v>
       </x:c>
       <x:c r="T153" s="1" t="n">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U153" s="1" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="V153" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W153" s="3">
+        <x:v>46115</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:29">
@@ -11787,16 +11870,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F154" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H154" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="I154" s="1" t="n">
         <x:v>4</x:v>
@@ -11811,7 +11894,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M154" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N154" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11829,7 +11912,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S154" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T154" s="1" t="n">
         <x:v>10</x:v>
@@ -11858,16 +11941,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F155" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H155" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="I155" s="1" t="n">
         <x:v>4</x:v>
@@ -11882,7 +11965,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M155" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N155" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11900,7 +11983,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S155" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T155" s="1" t="n">
         <x:v>10</x:v>
@@ -11929,16 +12012,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F156" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H156" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="I156" s="1" t="n">
         <x:v>4</x:v>
@@ -11953,7 +12036,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M156" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N156" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11971,7 +12054,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S156" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T156" s="1" t="n">
         <x:v>10</x:v>
@@ -12000,16 +12083,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="F157" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H157" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="I157" s="1" t="n">
         <x:v>6</x:v>
@@ -12024,13 +12107,13 @@
         <x:v>46087.0783034375</x:v>
       </x:c>
       <x:c r="M157" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="N157" s="4">
         <x:v>46090.4474321412</x:v>
       </x:c>
       <x:c r="O157" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="P157" s="1" t="n">
         <x:v>8.5</x:v>
@@ -12039,16 +12122,16 @@
         <x:v>202.3935</x:v>
       </x:c>
       <x:c r="R157" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="S157" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T157" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U157" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="V157" s="1" t="n">
         <x:v>6</x:v>
@@ -12071,16 +12154,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F158" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H158" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="I158" s="1" t="n">
         <x:v>2</x:v>
@@ -12095,7 +12178,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M158" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N158" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12113,7 +12196,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S158" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T158" s="1" t="n">
         <x:v>10</x:v>
@@ -12136,22 +12219,22 @@
         <x:v>35902</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="I159" s="1" t="n">
         <x:v>2</x:v>
@@ -12163,7 +12246,7 @@
         <x:v>46076.6827676736</x:v>
       </x:c>
       <x:c r="M159" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="R159" s="1" t="s">
         <x:v>195</x:v>
@@ -12183,16 +12266,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="F160" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="I160" s="1" t="n">
         <x:v>4</x:v>
@@ -12207,7 +12290,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M160" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N160" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12225,7 +12308,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S160" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T160" s="1" t="n">
         <x:v>10</x:v>
@@ -12254,16 +12337,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="F161" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I161" s="1" t="n">
         <x:v>4</x:v>
@@ -12278,7 +12361,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M161" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N161" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12296,7 +12379,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S161" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T161" s="1" t="n">
         <x:v>10</x:v>
@@ -12325,16 +12408,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F162" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="I162" s="1" t="n">
         <x:v>4</x:v>
@@ -12349,7 +12432,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M162" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N162" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12367,7 +12450,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S162" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T162" s="1" t="n">
         <x:v>10</x:v>
@@ -12396,16 +12479,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="F163" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G163" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H163" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="I163" s="1" t="n">
         <x:v>1</x:v>
@@ -12420,7 +12503,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M163" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N163" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12438,7 +12521,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S163" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T163" s="1" t="n">
         <x:v>10</x:v>
@@ -12467,16 +12550,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F164" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G164" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H164" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I164" s="1" t="n">
         <x:v>2</x:v>
@@ -12491,7 +12574,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M164" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N164" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12509,7 +12592,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S164" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T164" s="1" t="n">
         <x:v>10</x:v>
@@ -12538,16 +12621,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="F165" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G165" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="I165" s="1" t="n">
         <x:v>6</x:v>
@@ -12562,7 +12645,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M165" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N165" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12580,7 +12663,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S165" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T165" s="1" t="n">
         <x:v>10</x:v>
@@ -12609,16 +12692,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F166" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G166" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="I166" s="1" t="n">
         <x:v>2</x:v>
@@ -12633,7 +12716,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M166" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N166" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12651,7 +12734,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S166" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T166" s="1" t="n">
         <x:v>10</x:v>
@@ -12680,16 +12763,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="F167" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="G167" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="I167" s="1" t="n">
         <x:v>2</x:v>
@@ -12704,13 +12787,13 @@
         <x:v>46087.0783034375</x:v>
       </x:c>
       <x:c r="M167" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="N167" s="4">
         <x:v>46090.4474321412</x:v>
       </x:c>
       <x:c r="O167" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="P167" s="1" t="n">
         <x:v>8.5</x:v>
@@ -12719,16 +12802,16 @@
         <x:v>67.4645</x:v>
       </x:c>
       <x:c r="R167" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="S167" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T167" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U167" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="V167" s="1" t="n">
         <x:v>2</x:v>
@@ -12751,16 +12834,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="F168" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G168" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="I168" s="1" t="n">
         <x:v>8</x:v>
@@ -12775,7 +12858,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M168" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N168" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12793,7 +12876,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S168" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T168" s="1" t="n">
         <x:v>10</x:v>
@@ -12822,16 +12905,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F169" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G169" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="I169" s="1" t="n">
         <x:v>2</x:v>
@@ -12846,7 +12929,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M169" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N169" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12864,7 +12947,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S169" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T169" s="1" t="n">
         <x:v>10</x:v>
@@ -12881,7 +12964,7 @@
     </x:row>
     <x:row r="170" spans="1:29">
       <x:c r="A170" s="4">
-        <x:v>46085.0734823264</x:v>
+        <x:v>46111.7199709144</x:v>
       </x:c>
       <x:c r="B170" s="1" t="n">
         <x:v>35913</x:v>
@@ -12893,16 +12976,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="F170" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="G170" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H170" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="I170" s="1" t="n">
         <x:v>1</x:v>
@@ -12911,10 +12994,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L170" s="4">
-        <x:v>46085.0733793634</x:v>
+        <x:v>46111.7199707986</x:v>
       </x:c>
       <x:c r="M170" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>454</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:29">
@@ -12931,16 +13014,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F171" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G171" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H171" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="I171" s="1" t="n">
         <x:v>4</x:v>
@@ -12955,7 +13038,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M171" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N171" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12973,7 +13056,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S171" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T171" s="1" t="n">
         <x:v>10</x:v>
@@ -13002,16 +13085,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="F172" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G172" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H172" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="I172" s="1" t="n">
         <x:v>1</x:v>
@@ -13026,7 +13109,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M172" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N172" s="4">
         <x:v>46090.4456414005</x:v>
@@ -13044,7 +13127,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S172" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T172" s="1" t="n">
         <x:v>10</x:v>
@@ -13073,16 +13156,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F173" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="G173" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H173" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="I173" s="1" t="n">
         <x:v>1</x:v>
@@ -13097,13 +13180,13 @@
         <x:v>46090.4477212616</x:v>
       </x:c>
       <x:c r="M173" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="N173" s="4">
         <x:v>46090.447721412</x:v>
       </x:c>
       <x:c r="O173" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="P173" s="1" t="n">
         <x:v>885</x:v>
@@ -13112,16 +13195,16 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="R173" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="S173" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="T173" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U173" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="V173" s="1" t="n">
         <x:v>1</x:v>
@@ -13144,7 +13227,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="F174" s="1" t="s">
         <x:v>51</x:v>
@@ -13165,13 +13248,13 @@
         <x:v>46092.627584375</x:v>
       </x:c>
       <x:c r="M174" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="N174" s="4">
         <x:v>46092.6275845255</x:v>
       </x:c>
       <x:c r="O174" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="P174" s="1" t="n">
         <x:v>66</x:v>
@@ -13183,13 +13266,13 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="S174" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="T174" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U174" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="V174" s="1" t="n">
         <x:v>2</x:v>
@@ -13200,28 +13283,28 @@
     </x:row>
     <x:row r="175" spans="1:29">
       <x:c r="A175" s="4">
-        <x:v>46093.004525081</x:v>
+        <x:v>46107.6118467593</x:v>
       </x:c>
       <x:c r="B175" s="1" t="n">
         <x:v>36279</x:v>
       </x:c>
       <x:c r="C175" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D175" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F175" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G175" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="I175" s="1" t="n">
         <x:v>1</x:v>
@@ -13236,42 +13319,63 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M175" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="N175" s="4">
+        <x:v>46107.6111298611</x:v>
+      </x:c>
+      <x:c r="O175" s="1" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="P175" s="1" t="n">
+        <x:v>137.84</x:v>
+      </x:c>
+      <x:c r="Q175" s="1" t="n">
+        <x:v>137.84</x:v>
       </x:c>
       <x:c r="R175" s="1" t="s">
         <x:v>195</x:v>
       </x:c>
       <x:c r="S175" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="T175" s="1" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U175" s="1" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="V175" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W175" s="3">
+        <x:v>46115</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:29">
       <x:c r="A176" s="4">
-        <x:v>46093.004525081</x:v>
+        <x:v>46107.6118467593</x:v>
       </x:c>
       <x:c r="B176" s="1" t="n">
         <x:v>36280</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D176" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="F176" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G176" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H176" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="I176" s="1" t="n">
         <x:v>4</x:v>
@@ -13286,42 +13390,63 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M176" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="N176" s="4">
+        <x:v>46107.6111298611</x:v>
+      </x:c>
+      <x:c r="O176" s="1" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="P176" s="1" t="n">
+        <x:v>1.02</x:v>
+      </x:c>
+      <x:c r="Q176" s="1" t="n">
+        <x:v>4.08</x:v>
       </x:c>
       <x:c r="R176" s="1" t="s">
         <x:v>195</x:v>
       </x:c>
       <x:c r="S176" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="T176" s="1" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U176" s="1" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="V176" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W176" s="3">
+        <x:v>46115</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:29">
       <x:c r="A177" s="4">
-        <x:v>46093.004525081</x:v>
+        <x:v>46107.6118467593</x:v>
       </x:c>
       <x:c r="B177" s="1" t="n">
         <x:v>36281</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="F177" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G177" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H177" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="I177" s="1" t="n">
         <x:v>4</x:v>
@@ -13336,21 +13461,42 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M177" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="N177" s="4">
+        <x:v>46107.6111298611</x:v>
+      </x:c>
+      <x:c r="O177" s="1" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="P177" s="1" t="n">
+        <x:v>2.37</x:v>
+      </x:c>
+      <x:c r="Q177" s="1" t="n">
+        <x:v>9.48</x:v>
       </x:c>
       <x:c r="R177" s="1" t="s">
         <x:v>195</x:v>
       </x:c>
       <x:c r="S177" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="T177" s="1" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U177" s="1" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="V177" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W177" s="3">
+        <x:v>46115</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:29">
       <x:c r="A178" s="4">
-        <x:v>46093.0051498032</x:v>
+        <x:v>46097.6308056366</x:v>
       </x:c>
       <x:c r="B178" s="1" t="n">
         <x:v>36282</x:v>
@@ -13362,16 +13508,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F178" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="G178" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H178" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="I178" s="1" t="n">
         <x:v>1</x:v>
@@ -13383,7 +13529,7 @@
         <x:v>46093.0051497338</x:v>
       </x:c>
       <x:c r="M178" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>483</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:29">
@@ -13397,10 +13543,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="F179" s="1" t="s">
         <x:v>51</x:v>
@@ -13418,7 +13564,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M179" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:29">
@@ -13432,10 +13578,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="F180" s="1" t="s">
         <x:v>64</x:v>
@@ -13453,7 +13599,7 @@
         <x:v>46085.4128305208</x:v>
       </x:c>
       <x:c r="M180" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>488</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:29">
@@ -13467,10 +13613,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F181" s="1" t="s">
         <x:v>51</x:v>
@@ -13488,7 +13634,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M181" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:29">
@@ -13502,10 +13648,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="F182" s="1" t="s">
         <x:v>51</x:v>
@@ -13523,7 +13669,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M182" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:29">
@@ -13537,10 +13683,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="F183" s="1" t="s">
         <x:v>51</x:v>
@@ -13558,7 +13704,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M183" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:29">
@@ -13572,10 +13718,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F184" s="1" t="s">
         <x:v>51</x:v>
@@ -13593,7 +13739,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M184" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:29">
@@ -13607,10 +13753,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F185" s="1" t="s">
         <x:v>51</x:v>
@@ -13628,7 +13774,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M185" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:29">
@@ -13642,10 +13788,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E186" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F186" s="1" t="s">
         <x:v>51</x:v>
@@ -13663,7 +13809,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M186" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:29">
@@ -13677,10 +13823,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E187" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="F187" s="1" t="s">
         <x:v>51</x:v>
@@ -13698,24 +13844,24 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M187" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:29">
       <x:c r="A188" s="4">
-        <x:v>46086.6875060185</x:v>
+        <x:v>46111.7202197917</x:v>
       </x:c>
       <x:c r="B188" s="1" t="n">
         <x:v>36369</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="F188" s="1" t="s">
         <x:v>158</x:v>
@@ -13729,20 +13875,44 @@
       <x:c r="J188" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K188" s="4">
+        <x:v>46111.6479773495</x:v>
+      </x:c>
       <x:c r="L188" s="4">
-        <x:v>46085.4131163542</x:v>
+        <x:v>46111.7201420139</x:v>
       </x:c>
       <x:c r="M188" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="N188" s="4">
+        <x:v>46111.7201421644</x:v>
+      </x:c>
+      <x:c r="O188" s="1" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="P188" s="1" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q188" s="1" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="R188" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S188" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="T188" s="1" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="U188" s="1" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="V188" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W188" s="3">
+        <x:v>46126</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:29">
@@ -13756,10 +13926,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="F189" s="1" t="s">
         <x:v>51</x:v>
@@ -13777,7 +13947,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M189" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:29">
@@ -13791,10 +13961,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="F190" s="1" t="s">
         <x:v>51</x:v>
@@ -13812,7 +13982,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M190" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:29">
@@ -13826,10 +13996,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="F191" s="1" t="s">
         <x:v>51</x:v>
@@ -13847,7 +14017,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M191" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:29">
@@ -13861,19 +14031,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="F192" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="G192" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H192" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="I192" s="1" t="n">
         <x:v>2</x:v>
@@ -13888,7 +14058,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M192" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="N192" s="4">
         <x:v>46090.4456414005</x:v>
@@ -13906,7 +14076,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S192" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="T192" s="1" t="n">
         <x:v>1</x:v>
@@ -13932,19 +14102,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>500</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="F193" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="G193" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H193" s="1" t="s">
-        <x:v>502</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="I193" s="1" t="n">
         <x:v>2</x:v>
@@ -13959,7 +14129,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M193" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="N193" s="4">
         <x:v>46090.4456414005</x:v>
@@ -13977,7 +14147,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S193" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="T193" s="1" t="n">
         <x:v>1</x:v>
@@ -14003,10 +14173,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
-        <x:v>503</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="F194" s="1" t="s">
         <x:v>222</x:v>
@@ -14015,7 +14185,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H194" s="1" t="s">
-        <x:v>504</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="I194" s="1" t="n">
         <x:v>2</x:v>
@@ -14030,7 +14200,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M194" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="N194" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14048,7 +14218,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S194" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="T194" s="1" t="n">
         <x:v>1</x:v>
@@ -14074,10 +14244,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E195" s="1" t="s">
-        <x:v>505</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="F195" s="1" t="s">
         <x:v>222</x:v>
@@ -14086,7 +14256,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H195" s="1" t="s">
-        <x:v>506</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="I195" s="1" t="n">
         <x:v>2</x:v>
@@ -14101,7 +14271,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M195" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="N195" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14119,7 +14289,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S195" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="T195" s="1" t="n">
         <x:v>1</x:v>
@@ -14145,7 +14315,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="G196" s="1" t="s">
         <x:v>127</x:v>
@@ -14160,7 +14330,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M196" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="N196" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14178,7 +14348,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S196" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="T196" s="1" t="n">
         <x:v>10</x:v>
@@ -14204,10 +14374,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D197" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E197" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F197" s="1" t="s">
         <x:v>64</x:v>
@@ -14225,7 +14395,7 @@
         <x:v>46086.7566555556</x:v>
       </x:c>
       <x:c r="M197" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>518</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:29">
@@ -14239,7 +14409,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E198" s="1" t="s">
-        <x:v>510</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="G198" s="1" t="s">
         <x:v>127</x:v>
@@ -14254,7 +14424,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M198" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="N198" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14272,7 +14442,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S198" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="T198" s="1" t="n">
         <x:v>1</x:v>
@@ -14285,6 +14455,216 @@
       </x:c>
       <x:c r="W198" s="3">
         <x:v>46095</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:29">
+      <x:c r="A199" s="4">
+        <x:v>46100.4842279745</x:v>
+      </x:c>
+      <x:c r="B199" s="1" t="n">
+        <x:v>37261</x:v>
+      </x:c>
+      <x:c r="C199" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D199" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E199" s="1" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="F199" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G199" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I199" s="1" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J199" s="1" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L199" s="4">
+        <x:v>46098.5238698727</x:v>
+      </x:c>
+      <x:c r="M199" s="1" t="s">
+        <x:v>522</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:29">
+      <x:c r="A200" s="4">
+        <x:v>46100.4842279745</x:v>
+      </x:c>
+      <x:c r="B200" s="1" t="n">
+        <x:v>37262</x:v>
+      </x:c>
+      <x:c r="C200" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D200" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E200" s="1" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="F200" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G200" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I200" s="1" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J200" s="1" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L200" s="4">
+        <x:v>46098.5238698727</x:v>
+      </x:c>
+      <x:c r="M200" s="1" t="s">
+        <x:v>522</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:29">
+      <x:c r="A201" s="4">
+        <x:v>46100.4842279745</x:v>
+      </x:c>
+      <x:c r="B201" s="1" t="n">
+        <x:v>37265</x:v>
+      </x:c>
+      <x:c r="C201" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D201" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E201" s="1" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="F201" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G201" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I201" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J201" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L201" s="4">
+        <x:v>46098.5238698727</x:v>
+      </x:c>
+      <x:c r="M201" s="1" t="s">
+        <x:v>522</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:29">
+      <x:c r="A202" s="4">
+        <x:v>46100.4842279745</x:v>
+      </x:c>
+      <x:c r="B202" s="1" t="n">
+        <x:v>37266</x:v>
+      </x:c>
+      <x:c r="C202" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D202" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E202" s="1" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="F202" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G202" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I202" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J202" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L202" s="4">
+        <x:v>46098.5238698727</x:v>
+      </x:c>
+      <x:c r="M202" s="1" t="s">
+        <x:v>522</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:29">
+      <x:c r="A203" s="4">
+        <x:v>46100.4847336806</x:v>
+      </x:c>
+      <x:c r="B203" s="1" t="n">
+        <x:v>37412</x:v>
+      </x:c>
+      <x:c r="C203" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D203" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E203" s="1" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="F203" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G203" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I203" s="1" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J203" s="1" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L203" s="4">
+        <x:v>46100.4729106481</x:v>
+      </x:c>
+      <x:c r="M203" s="1" t="s">
+        <x:v>527</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:29">
+      <x:c r="A204" s="4">
+        <x:v>46100.4847336806</x:v>
+      </x:c>
+      <x:c r="B204" s="1" t="n">
+        <x:v>37413</x:v>
+      </x:c>
+      <x:c r="C204" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D204" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E204" s="1" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="F204" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G204" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I204" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J204" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L204" s="4">
+        <x:v>46100.4729106481</x:v>
+      </x:c>
+      <x:c r="M204" s="1" t="s">
+        <x:v>527</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/bom.xlsx
+++ b/bom.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="530">
   <x:si>
     <x:t>Document No</x:t>
   </x:si>
@@ -1266,7 +1266,7 @@
     <x:t>RFQ4134551</x:t>
   </x:si>
   <x:si>
-    <x:t>RFQ Reject</x:t>
+    <x:t>RFQ Approved</x:t>
   </x:si>
   <x:si>
     <x:t>clamp plate</x:t>
@@ -1360,6 +1360,9 @@
     <x:t xml:space="preserve">SSEBWZ16G-110
 【IAJ01-H16-L110】	
 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ Reject</x:t>
   </x:si>
   <x:si>
     <x:t>Linear Guide Bearing</x:t>
@@ -11737,7 +11740,7 @@
     </x:row>
     <x:row r="152" spans="1:29">
       <x:c r="A152" s="4">
-        <x:v>46099.715571794</x:v>
+        <x:v>46114.6190235764</x:v>
       </x:c>
       <x:c r="B152" s="1" t="n">
         <x:v>35895</x:v>
@@ -11767,10 +11770,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K152" s="4">
-        <x:v>46099.7155716435</x:v>
+        <x:v>46114.6190233796</x:v>
       </x:c>
       <x:c r="L152" s="4">
-        <x:v>46099.7155717245</x:v>
+        <x:v>46114.6190234954</x:v>
       </x:c>
       <x:c r="M152" s="1" t="s">
         <x:v>406</x:v>
@@ -12219,13 +12222,13 @@
         <x:v>35902</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
         <x:v>384</x:v>
@@ -12234,7 +12237,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="I159" s="1" t="n">
         <x:v>2</x:v>
@@ -12246,7 +12249,7 @@
         <x:v>46076.6827676736</x:v>
       </x:c>
       <x:c r="M159" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="R159" s="1" t="s">
         <x:v>195</x:v>
@@ -12266,7 +12269,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F160" s="1" t="s">
         <x:v>393</x:v>
@@ -12275,7 +12278,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="I160" s="1" t="n">
         <x:v>4</x:v>
@@ -12337,7 +12340,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="F161" s="1" t="s">
         <x:v>393</x:v>
@@ -12346,7 +12349,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="I161" s="1" t="n">
         <x:v>4</x:v>
@@ -12408,7 +12411,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F162" s="1" t="s">
         <x:v>393</x:v>
@@ -12417,7 +12420,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="I162" s="1" t="n">
         <x:v>4</x:v>
@@ -12479,7 +12482,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F163" s="1" t="s">
         <x:v>393</x:v>
@@ -12488,7 +12491,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H163" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I163" s="1" t="n">
         <x:v>1</x:v>
@@ -12559,7 +12562,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H164" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="I164" s="1" t="n">
         <x:v>2</x:v>
@@ -12630,7 +12633,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="I165" s="1" t="n">
         <x:v>6</x:v>
@@ -12692,7 +12695,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F166" s="1" t="s">
         <x:v>393</x:v>
@@ -12701,7 +12704,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="I166" s="1" t="n">
         <x:v>2</x:v>
@@ -12772,7 +12775,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="I167" s="1" t="n">
         <x:v>2</x:v>
@@ -12834,7 +12837,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F168" s="1" t="s">
         <x:v>393</x:v>
@@ -12843,7 +12846,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="I168" s="1" t="n">
         <x:v>8</x:v>
@@ -12914,7 +12917,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="I169" s="1" t="n">
         <x:v>2</x:v>
@@ -12976,16 +12979,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F170" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="G170" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H170" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="I170" s="1" t="n">
         <x:v>1</x:v>
@@ -12997,7 +13000,7 @@
         <x:v>46111.7199707986</x:v>
       </x:c>
       <x:c r="M170" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:29">
@@ -13014,7 +13017,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F171" s="1" t="s">
         <x:v>393</x:v>
@@ -13023,7 +13026,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H171" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="I171" s="1" t="n">
         <x:v>4</x:v>
@@ -13085,7 +13088,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="F172" s="1" t="s">
         <x:v>393</x:v>
@@ -13094,7 +13097,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H172" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="I172" s="1" t="n">
         <x:v>1</x:v>
@@ -13156,16 +13159,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="F173" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="G173" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H173" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="I173" s="1" t="n">
         <x:v>1</x:v>
@@ -13180,13 +13183,13 @@
         <x:v>46090.4477212616</x:v>
       </x:c>
       <x:c r="M173" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="N173" s="4">
         <x:v>46090.447721412</x:v>
       </x:c>
       <x:c r="O173" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="P173" s="1" t="n">
         <x:v>885</x:v>
@@ -13195,16 +13198,16 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="R173" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="S173" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="T173" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U173" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="V173" s="1" t="n">
         <x:v>1</x:v>
@@ -13227,7 +13230,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="F174" s="1" t="s">
         <x:v>51</x:v>
@@ -13248,13 +13251,13 @@
         <x:v>46092.627584375</x:v>
       </x:c>
       <x:c r="M174" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="N174" s="4">
         <x:v>46092.6275845255</x:v>
       </x:c>
       <x:c r="O174" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="P174" s="1" t="n">
         <x:v>66</x:v>
@@ -13266,13 +13269,13 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="S174" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="T174" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U174" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="V174" s="1" t="n">
         <x:v>2</x:v>
@@ -13298,13 +13301,13 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="F175" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="G175" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="I175" s="1" t="n">
         <x:v>1</x:v>
@@ -13319,13 +13322,13 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M175" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="N175" s="4">
         <x:v>46107.6111298611</x:v>
       </x:c>
       <x:c r="O175" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="P175" s="1" t="n">
         <x:v>137.84</x:v>
@@ -13337,13 +13340,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S175" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="T175" s="1" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="U175" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="V175" s="1" t="n">
         <x:v>1</x:v>
@@ -13366,16 +13369,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="F176" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="G176" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H176" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="I176" s="1" t="n">
         <x:v>4</x:v>
@@ -13390,13 +13393,13 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M176" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="N176" s="4">
         <x:v>46107.6111298611</x:v>
       </x:c>
       <x:c r="O176" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="P176" s="1" t="n">
         <x:v>1.02</x:v>
@@ -13408,13 +13411,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S176" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="T176" s="1" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="U176" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="V176" s="1" t="n">
         <x:v>4</x:v>
@@ -13437,16 +13440,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="F177" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="G177" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H177" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="I177" s="1" t="n">
         <x:v>4</x:v>
@@ -13461,13 +13464,13 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M177" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="N177" s="4">
         <x:v>46107.6111298611</x:v>
       </x:c>
       <x:c r="O177" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="P177" s="1" t="n">
         <x:v>2.37</x:v>
@@ -13479,13 +13482,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S177" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="T177" s="1" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="U177" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="V177" s="1" t="n">
         <x:v>4</x:v>
@@ -13511,13 +13514,13 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="F178" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="G178" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H178" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="I178" s="1" t="n">
         <x:v>1</x:v>
@@ -13529,7 +13532,7 @@
         <x:v>46093.0051497338</x:v>
       </x:c>
       <x:c r="M178" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:29">
@@ -13543,10 +13546,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F179" s="1" t="s">
         <x:v>51</x:v>
@@ -13564,7 +13567,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M179" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:29">
@@ -13578,10 +13581,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="F180" s="1" t="s">
         <x:v>64</x:v>
@@ -13599,7 +13602,7 @@
         <x:v>46085.4128305208</x:v>
       </x:c>
       <x:c r="M180" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:29">
@@ -13613,10 +13616,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="F181" s="1" t="s">
         <x:v>51</x:v>
@@ -13634,7 +13637,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M181" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:29">
@@ -13648,10 +13651,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="F182" s="1" t="s">
         <x:v>51</x:v>
@@ -13669,7 +13672,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M182" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:29">
@@ -13683,10 +13686,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F183" s="1" t="s">
         <x:v>51</x:v>
@@ -13704,7 +13707,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M183" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:29">
@@ -13718,10 +13721,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F184" s="1" t="s">
         <x:v>51</x:v>
@@ -13739,7 +13742,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M184" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:29">
@@ -13753,10 +13756,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F185" s="1" t="s">
         <x:v>51</x:v>
@@ -13774,7 +13777,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M185" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:29">
@@ -13788,10 +13791,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E186" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="F186" s="1" t="s">
         <x:v>51</x:v>
@@ -13809,7 +13812,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M186" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:29">
@@ -13823,10 +13826,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E187" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="F187" s="1" t="s">
         <x:v>51</x:v>
@@ -13844,7 +13847,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M187" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:29">
@@ -13858,10 +13861,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="F188" s="1" t="s">
         <x:v>158</x:v>
@@ -13882,13 +13885,13 @@
         <x:v>46111.7201420139</x:v>
       </x:c>
       <x:c r="M188" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="N188" s="4">
         <x:v>46111.7201421644</x:v>
       </x:c>
       <x:c r="O188" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="P188" s="1" t="n">
         <x:v>50</x:v>
@@ -13900,13 +13903,13 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="S188" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="T188" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U188" s="1" t="s">
-        <x:v>500</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="V188" s="1" t="n">
         <x:v>2</x:v>
@@ -13926,10 +13929,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="F189" s="1" t="s">
         <x:v>51</x:v>
@@ -13947,7 +13950,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M189" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:29">
@@ -13961,10 +13964,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>502</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="F190" s="1" t="s">
         <x:v>51</x:v>
@@ -13982,7 +13985,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M190" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:29">
@@ -13996,10 +13999,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>503</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="F191" s="1" t="s">
         <x:v>51</x:v>
@@ -14017,7 +14020,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M191" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:29">
@@ -14031,19 +14034,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
-        <x:v>504</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F192" s="1" t="s">
-        <x:v>505</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="G192" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H192" s="1" t="s">
-        <x:v>506</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="I192" s="1" t="n">
         <x:v>2</x:v>
@@ -14058,7 +14061,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M192" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="N192" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14076,7 +14079,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S192" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="T192" s="1" t="n">
         <x:v>1</x:v>
@@ -14102,19 +14105,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="F193" s="1" t="s">
-        <x:v>510</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="G193" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H193" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="I193" s="1" t="n">
         <x:v>2</x:v>
@@ -14129,7 +14132,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M193" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="N193" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14147,7 +14150,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S193" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="T193" s="1" t="n">
         <x:v>1</x:v>
@@ -14173,10 +14176,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="F194" s="1" t="s">
         <x:v>222</x:v>
@@ -14185,7 +14188,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H194" s="1" t="s">
-        <x:v>513</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="I194" s="1" t="n">
         <x:v>2</x:v>
@@ -14200,7 +14203,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M194" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="N194" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14218,7 +14221,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S194" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="T194" s="1" t="n">
         <x:v>1</x:v>
@@ -14244,10 +14247,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D195" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E195" s="1" t="s">
-        <x:v>514</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="F195" s="1" t="s">
         <x:v>222</x:v>
@@ -14256,7 +14259,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H195" s="1" t="s">
-        <x:v>515</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="I195" s="1" t="n">
         <x:v>2</x:v>
@@ -14271,7 +14274,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M195" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="N195" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14289,7 +14292,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S195" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="T195" s="1" t="n">
         <x:v>1</x:v>
@@ -14315,7 +14318,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="G196" s="1" t="s">
         <x:v>127</x:v>
@@ -14374,10 +14377,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D197" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E197" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F197" s="1" t="s">
         <x:v>64</x:v>
@@ -14395,7 +14398,7 @@
         <x:v>46086.7566555556</x:v>
       </x:c>
       <x:c r="M197" s="1" t="s">
-        <x:v>518</x:v>
+        <x:v>519</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:29">
@@ -14409,7 +14412,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E198" s="1" t="s">
-        <x:v>519</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="G198" s="1" t="s">
         <x:v>127</x:v>
@@ -14424,7 +14427,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M198" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="N198" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14442,7 +14445,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S198" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="T198" s="1" t="n">
         <x:v>1</x:v>
@@ -14468,10 +14471,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D199" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="E199" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="F199" s="1" t="s">
         <x:v>64</x:v>
@@ -14489,7 +14492,7 @@
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M199" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>523</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:29">
@@ -14503,10 +14506,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="E200" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="F200" s="1" t="s">
         <x:v>64</x:v>
@@ -14524,7 +14527,7 @@
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M200" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>523</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:29">
@@ -14538,10 +14541,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="F201" s="1" t="s">
         <x:v>64</x:v>
@@ -14559,7 +14562,7 @@
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M201" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>523</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:29">
@@ -14573,10 +14576,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D202" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="E202" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="F202" s="1" t="s">
         <x:v>64</x:v>
@@ -14594,7 +14597,7 @@
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M202" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>523</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:29">
@@ -14608,10 +14611,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D203" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="F203" s="1" t="s">
         <x:v>51</x:v>
@@ -14629,7 +14632,7 @@
         <x:v>46100.4729106481</x:v>
       </x:c>
       <x:c r="M203" s="1" t="s">
-        <x:v>527</x:v>
+        <x:v>528</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:29">
@@ -14643,10 +14646,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D204" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="E204" s="1" t="s">
-        <x:v>528</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F204" s="1" t="s">
         <x:v>51</x:v>
@@ -14664,7 +14667,7 @@
         <x:v>46100.4729106481</x:v>
       </x:c>
       <x:c r="M204" s="1" t="s">
-        <x:v>527</x:v>
+        <x:v>528</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/bom.xlsx
+++ b/bom.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="530">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="533">
   <x:si>
     <x:t>Document No</x:t>
   </x:si>
@@ -1196,6 +1196,9 @@
     <x:t>OMR513-S1005A</x:t>
   </x:si>
   <x:si>
+    <x:t>PR Sent</x:t>
+  </x:si>
+  <x:si>
     <x:t>string wheel</x:t>
   </x:si>
   <x:si>
@@ -1205,7 +1208,14 @@
     <x:t>HBGP40-21</x:t>
   </x:si>
   <x:si>
-    <x:t>RFQ4129242</x:t>
+    <x:t>RFQ4136271</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5331101</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/47659
+</x:t>
   </x:si>
   <x:si>
     <x:t>bearing</x:t>
@@ -1248,6 +1258,9 @@
     <x:t>A0-139452_EP01</x:t>
   </x:si>
   <x:si>
+    <x:t>RFQ4129242</x:t>
+  </x:si>
+  <x:si>
     <x:t>slipring</x:t>
   </x:si>
   <x:si>
@@ -1257,26 +1270,23 @@
     <x:t>LPC-06A</x:t>
   </x:si>
   <x:si>
-    <x:t>slider bearing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C-SX2RL24-L_b</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RFQ4134551</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RFQ Approved</x:t>
+    <x:t>RFQ4136261</x:t>
   </x:si>
   <x:si>
     <x:t>clamp plate</x:t>
   </x:si>
   <x:si>
     <x:t>RFQ4129252</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5330771</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/45809
 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAPO26040033</x:t>
   </x:si>
   <x:si>
     <x:t>motor</x:t>
@@ -2075,7 +2085,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AC204"/>
+  <x:dimension ref="A1:AC203"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="30" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -7394,7 +7404,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="T82" s="1" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U82" s="1" t="s">
         <x:v>278</x:v>
@@ -7465,7 +7475,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="T83" s="1" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U83" s="1" t="s">
         <x:v>278</x:v>
@@ -7607,7 +7617,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="T85" s="1" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U85" s="1" t="s">
         <x:v>292</x:v>
@@ -11446,28 +11456,28 @@
     </x:row>
     <x:row r="146" spans="1:29">
       <x:c r="A146" s="4">
-        <x:v>46111.4966081019</x:v>
+        <x:v>46115.7427043634</x:v>
       </x:c>
       <x:c r="B146" s="1" t="n">
         <x:v>35888</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="F146" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="G146" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H146" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="I146" s="1" t="n">
         <x:v>6</x:v>
@@ -11475,11 +11485,41 @@
       <x:c r="J146" s="1" t="n">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="K146" s="4">
+        <x:v>46115.6415685185</x:v>
+      </x:c>
       <x:c r="L146" s="4">
-        <x:v>46072.617799456</x:v>
+        <x:v>46115.7400868056</x:v>
       </x:c>
       <x:c r="M146" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="N146" s="4">
+        <x:v>46115.7400869213</x:v>
+      </x:c>
+      <x:c r="O146" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="P146" s="1" t="n">
+        <x:v>126.51</x:v>
+      </x:c>
+      <x:c r="Q146" s="1" t="n">
+        <x:v>759.06</x:v>
+      </x:c>
+      <x:c r="R146" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="S146" s="1" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="T146" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V146" s="1" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="W146" s="4">
+        <x:v>46122.1666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:29">
@@ -11496,16 +11536,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F147" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H147" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="I147" s="1" t="n">
         <x:v>12</x:v>
@@ -11520,7 +11560,7 @@
         <x:v>46086.6600798611</x:v>
       </x:c>
       <x:c r="M147" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="N147" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11538,7 +11578,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S147" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="T147" s="1" t="n">
         <x:v>23</x:v>
@@ -11567,16 +11607,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="F148" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H148" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="I148" s="1" t="n">
         <x:v>12</x:v>
@@ -11591,7 +11631,7 @@
         <x:v>46086.6600798611</x:v>
       </x:c>
       <x:c r="M148" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="N148" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11609,7 +11649,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S148" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="T148" s="1" t="n">
         <x:v>23</x:v>
@@ -11626,7 +11666,7 @@
     </x:row>
     <x:row r="149" spans="1:29">
       <x:c r="A149" s="4">
-        <x:v>46111.4966081019</x:v>
+        <x:v>46115.642734375</x:v>
       </x:c>
       <x:c r="B149" s="1" t="n">
         <x:v>35891</x:v>
@@ -11638,16 +11678,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="F149" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H149" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="I149" s="1" t="n">
         <x:v>1</x:v>
@@ -11659,12 +11699,15 @@
         <x:v>46072.617799456</x:v>
       </x:c>
       <x:c r="M149" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="T149" s="1" t="s">
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:29">
       <x:c r="A150" s="4">
-        <x:v>46111.4966081019</x:v>
+        <x:v>46115.6383925579</x:v>
       </x:c>
       <x:c r="B150" s="1" t="n">
         <x:v>35893</x:v>
@@ -11676,16 +11719,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F150" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H150" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="I150" s="1" t="n">
         <x:v>2</x:v>
@@ -11694,74 +11737,107 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="L150" s="4">
-        <x:v>46072.617799456</x:v>
+        <x:v>46115.6381272338</x:v>
       </x:c>
       <x:c r="M150" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>405</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:29">
       <x:c r="A151" s="4">
-        <x:v>46111.4595082523</x:v>
+        <x:v>46115.408791169</x:v>
       </x:c>
       <x:c r="B151" s="1" t="n">
-        <x:v>35894</x:v>
+        <x:v>35895</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
         <x:v>321</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="F151" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="G151" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H151" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="I151" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J151" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K151" s="4">
+        <x:v>46114.6190233796</x:v>
       </x:c>
       <x:c r="L151" s="4">
-        <x:v>46107.609743669</x:v>
+        <x:v>46115.403372338</x:v>
       </x:c>
       <x:c r="M151" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="N151" s="4">
+        <x:v>46115.4033724537</x:v>
+      </x:c>
+      <x:c r="O151" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="P151" s="1" t="n">
+        <x:v>3.38</x:v>
+      </x:c>
+      <x:c r="Q151" s="1" t="n">
+        <x:v>3.38</x:v>
+      </x:c>
+      <x:c r="R151" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S151" s="1" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="T151" s="1" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="U151" s="1" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="V151" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W151" s="4">
+        <x:v>46129.1666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:29">
       <x:c r="A152" s="4">
-        <x:v>46114.6190235764</x:v>
+        <x:v>46107.610496794</x:v>
       </x:c>
       <x:c r="B152" s="1" t="n">
-        <x:v>35895</x:v>
+        <x:v>35896</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
         <x:v>321</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F152" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H152" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="I152" s="1" t="n">
         <x:v>1</x:v>
@@ -11770,93 +11846,114 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K152" s="4">
-        <x:v>46114.6190233796</x:v>
+        <x:v>46098.4855049769</x:v>
       </x:c>
       <x:c r="L152" s="4">
-        <x:v>46114.6190234954</x:v>
+        <x:v>46107.6101008102</x:v>
       </x:c>
       <x:c r="M152" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="N152" s="4">
+        <x:v>46107.6101011227</x:v>
+      </x:c>
+      <x:c r="O152" s="1" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="P152" s="1" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="Q152" s="1" t="n">
+        <x:v>1318.185</x:v>
       </x:c>
       <x:c r="R152" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="S152" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="T152" s="1" t="n">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U152" s="1" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="V152" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W152" s="3">
+        <x:v>46115</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:29">
       <x:c r="A153" s="4">
-        <x:v>46107.610496794</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B153" s="1" t="n">
-        <x:v>35896</x:v>
+        <x:v>35897</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="D153" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F153" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H153" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="I153" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J153" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K153" s="4">
-        <x:v>46098.4855049769</x:v>
+        <x:v>46086.6518195255</x:v>
       </x:c>
       <x:c r="L153" s="4">
-        <x:v>46107.6101008102</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M153" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N153" s="4">
-        <x:v>46107.6101011227</x:v>
+        <x:v>46090.4456414005</x:v>
       </x:c>
       <x:c r="O153" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="P153" s="1" t="n">
-        <x:v>330</x:v>
+        <x:v>4.18</x:v>
       </x:c>
       <x:c r="Q153" s="1" t="n">
-        <x:v>1318.185</x:v>
+        <x:v>66.35332</x:v>
       </x:c>
       <x:c r="R153" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="S153" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T153" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="U153" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="V153" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W153" s="3">
-        <x:v>46115</x:v>
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:29">
@@ -11864,7 +11961,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B154" s="1" t="n">
-        <x:v>35897</x:v>
+        <x:v>35898</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
         <x:v>48</x:v>
@@ -11873,16 +11970,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F154" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H154" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="I154" s="1" t="n">
         <x:v>4</x:v>
@@ -11897,7 +11994,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M154" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N154" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11906,16 +12003,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P154" s="1" t="n">
-        <x:v>4.18</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="Q154" s="1" t="n">
-        <x:v>66.35332</x:v>
+        <x:v>80.9574</x:v>
       </x:c>
       <x:c r="R154" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S154" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T154" s="1" t="n">
         <x:v>10</x:v>
@@ -11935,7 +12032,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B155" s="1" t="n">
-        <x:v>35898</x:v>
+        <x:v>35899</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
         <x:v>48</x:v>
@@ -11944,16 +12041,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F155" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H155" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="I155" s="1" t="n">
         <x:v>4</x:v>
@@ -11968,7 +12065,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M155" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N155" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11977,16 +12074,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P155" s="1" t="n">
-        <x:v>5.1</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="Q155" s="1" t="n">
-        <x:v>80.9574</x:v>
+        <x:v>3.1748</x:v>
       </x:c>
       <x:c r="R155" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S155" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T155" s="1" t="n">
         <x:v>10</x:v>
@@ -12003,10 +12100,10 @@
     </x:row>
     <x:row r="156" spans="1:29">
       <x:c r="A156" s="4">
-        <x:v>46090.4467435532</x:v>
+        <x:v>46090.4485225694</x:v>
       </x:c>
       <x:c r="B156" s="1" t="n">
-        <x:v>35899</x:v>
+        <x:v>35900</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
         <x:v>48</x:v>
@@ -12015,69 +12112,69 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="F156" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H156" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="I156" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J156" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K156" s="4">
-        <x:v>46086.6518195255</x:v>
+        <x:v>46087.078303206</x:v>
       </x:c>
       <x:c r="L156" s="4">
-        <x:v>46086.6518199421</x:v>
+        <x:v>46087.0783034375</x:v>
       </x:c>
       <x:c r="M156" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="N156" s="4">
-        <x:v>46090.4456414005</x:v>
+        <x:v>46090.4474321412</x:v>
       </x:c>
       <x:c r="O156" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="P156" s="1" t="n">
-        <x:v>0.2</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="Q156" s="1" t="n">
-        <x:v>3.1748</x:v>
+        <x:v>202.3935</x:v>
       </x:c>
       <x:c r="R156" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="S156" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="T156" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U156" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="V156" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="W156" s="3">
-        <x:v>46095</x:v>
+        <x:v>46099</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:29">
       <x:c r="A157" s="4">
-        <x:v>46090.4485225694</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B157" s="1" t="n">
-        <x:v>35900</x:v>
+        <x:v>35901</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
         <x:v>48</x:v>
@@ -12086,87 +12183,87 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="F157" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H157" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="I157" s="1" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J157" s="1" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K157" s="4">
-        <x:v>46087.078303206</x:v>
+        <x:v>46086.6518195255</x:v>
       </x:c>
       <x:c r="L157" s="4">
-        <x:v>46087.0783034375</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M157" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N157" s="4">
-        <x:v>46090.4474321412</x:v>
+        <x:v>46090.4456414005</x:v>
       </x:c>
       <x:c r="O157" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="P157" s="1" t="n">
-        <x:v>8.5</x:v>
+        <x:v>35.63</x:v>
       </x:c>
       <x:c r="Q157" s="1" t="n">
-        <x:v>202.3935</x:v>
+        <x:v>282.79531</x:v>
       </x:c>
       <x:c r="R157" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="S157" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T157" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="U157" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="V157" s="1" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W157" s="3">
-        <x:v>46099</x:v>
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:29">
       <x:c r="A158" s="4">
-        <x:v>46090.4467435532</x:v>
+        <x:v>46086.6411116088</x:v>
       </x:c>
       <x:c r="B158" s="1" t="n">
-        <x:v>35901</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F158" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="G158" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H158" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="I158" s="1" t="n">
         <x:v>2</x:v>
@@ -12174,85 +12271,85 @@
       <x:c r="J158" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K158" s="4">
-        <x:v>46086.6518195255</x:v>
-      </x:c>
       <x:c r="L158" s="4">
-        <x:v>46086.6518199421</x:v>
+        <x:v>46076.6827676736</x:v>
       </x:c>
       <x:c r="M158" s="1" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="N158" s="4">
-        <x:v>46090.4456414005</x:v>
-      </x:c>
-      <x:c r="O158" s="1" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="P158" s="1" t="n">
-        <x:v>35.63</x:v>
-      </x:c>
-      <x:c r="Q158" s="1" t="n">
-        <x:v>282.79531</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="R158" s="1" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="S158" s="1" t="s">
-        <x:v>419</x:v>
-      </x:c>
-      <x:c r="T158" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="U158" s="1" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="V158" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="W158" s="3">
-        <x:v>46095</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:29">
       <x:c r="A159" s="4">
-        <x:v>46086.6411116088</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B159" s="1" t="n">
-        <x:v>35902</x:v>
+        <x:v>35903</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D159" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="I159" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J159" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K159" s="4">
+        <x:v>46086.6518195255</x:v>
       </x:c>
       <x:c r="L159" s="4">
-        <x:v>46076.6827676736</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M159" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="N159" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O159" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P159" s="1" t="n">
+        <x:v>10.11</x:v>
+      </x:c>
+      <x:c r="Q159" s="1" t="n">
+        <x:v>160.48614</x:v>
       </x:c>
       <x:c r="R159" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S159" s="1" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="T159" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U159" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V159" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W159" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:29">
@@ -12260,7 +12357,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B160" s="1" t="n">
-        <x:v>35903</x:v>
+        <x:v>35904</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
         <x:v>48</x:v>
@@ -12269,16 +12366,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="F160" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="I160" s="1" t="n">
         <x:v>4</x:v>
@@ -12293,7 +12390,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M160" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N160" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12302,16 +12399,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P160" s="1" t="n">
-        <x:v>10.11</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="Q160" s="1" t="n">
-        <x:v>160.48614</x:v>
+        <x:v>13.01668</x:v>
       </x:c>
       <x:c r="R160" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S160" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T160" s="1" t="n">
         <x:v>10</x:v>
@@ -12331,7 +12428,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B161" s="1" t="n">
-        <x:v>35904</x:v>
+        <x:v>35905</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
         <x:v>48</x:v>
@@ -12340,16 +12437,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="F161" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="I161" s="1" t="n">
         <x:v>4</x:v>
@@ -12364,7 +12461,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M161" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N161" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12373,16 +12470,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P161" s="1" t="n">
-        <x:v>0.82</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="Q161" s="1" t="n">
-        <x:v>13.01668</x:v>
+        <x:v>2.3811</x:v>
       </x:c>
       <x:c r="R161" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S161" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T161" s="1" t="n">
         <x:v>10</x:v>
@@ -12402,7 +12499,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B162" s="1" t="n">
-        <x:v>35905</x:v>
+        <x:v>35906</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
         <x:v>48</x:v>
@@ -12411,22 +12508,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F162" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="I162" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J162" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K162" s="4">
         <x:v>46086.6518195255</x:v>
@@ -12435,7 +12532,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M162" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N162" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12444,16 +12541,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P162" s="1" t="n">
-        <x:v>0.15</x:v>
+        <x:v>3.65</x:v>
       </x:c>
       <x:c r="Q162" s="1" t="n">
-        <x:v>2.3811</x:v>
+        <x:v>14.485025</x:v>
       </x:c>
       <x:c r="R162" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S162" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T162" s="1" t="n">
         <x:v>10</x:v>
@@ -12462,7 +12559,7 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="V162" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W162" s="3">
         <x:v>46095</x:v>
@@ -12473,7 +12570,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B163" s="1" t="n">
-        <x:v>35906</x:v>
+        <x:v>35907</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
         <x:v>48</x:v>
@@ -12482,22 +12579,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F163" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G163" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H163" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="I163" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J163" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K163" s="4">
         <x:v>46086.6518195255</x:v>
@@ -12506,7 +12603,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M163" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N163" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12515,16 +12612,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P163" s="1" t="n">
-        <x:v>3.65</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="Q163" s="1" t="n">
-        <x:v>14.485025</x:v>
+        <x:v>53.57475</x:v>
       </x:c>
       <x:c r="R163" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S163" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T163" s="1" t="n">
         <x:v>10</x:v>
@@ -12533,7 +12630,7 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="V163" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W163" s="3">
         <x:v>46095</x:v>
@@ -12544,7 +12641,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B164" s="1" t="n">
-        <x:v>35907</x:v>
+        <x:v>35908</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
         <x:v>48</x:v>
@@ -12553,22 +12650,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F164" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G164" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H164" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="I164" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J164" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K164" s="4">
         <x:v>46086.6518195255</x:v>
@@ -12577,7 +12674,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M164" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N164" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12586,16 +12683,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P164" s="1" t="n">
-        <x:v>6.75</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="Q164" s="1" t="n">
-        <x:v>53.57475</x:v>
+        <x:v>3.80976</x:v>
       </x:c>
       <x:c r="R164" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S164" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T164" s="1" t="n">
         <x:v>10</x:v>
@@ -12604,7 +12701,7 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="V164" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="W164" s="3">
         <x:v>46095</x:v>
@@ -12615,7 +12712,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B165" s="1" t="n">
-        <x:v>35908</x:v>
+        <x:v>35909</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
         <x:v>48</x:v>
@@ -12624,22 +12721,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F165" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G165" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="I165" s="1" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J165" s="1" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K165" s="4">
         <x:v>46086.6518195255</x:v>
@@ -12648,7 +12745,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M165" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N165" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12657,16 +12754,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P165" s="1" t="n">
-        <x:v>0.16</x:v>
+        <x:v>3.48</x:v>
       </x:c>
       <x:c r="Q165" s="1" t="n">
-        <x:v>3.80976</x:v>
+        <x:v>27.62076</x:v>
       </x:c>
       <x:c r="R165" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S165" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T165" s="1" t="n">
         <x:v>10</x:v>
@@ -12675,7 +12772,7 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="V165" s="1" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W165" s="3">
         <x:v>46095</x:v>
@@ -12683,10 +12780,10 @@
     </x:row>
     <x:row r="166" spans="1:29">
       <x:c r="A166" s="4">
-        <x:v>46090.4467435532</x:v>
+        <x:v>46090.4485225694</x:v>
       </x:c>
       <x:c r="B166" s="1" t="n">
-        <x:v>35909</x:v>
+        <x:v>35910</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
         <x:v>48</x:v>
@@ -12695,16 +12792,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="F166" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="G166" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="I166" s="1" t="n">
         <x:v>2</x:v>
@@ -12713,51 +12810,51 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K166" s="4">
-        <x:v>46086.6518195255</x:v>
+        <x:v>46087.078303206</x:v>
       </x:c>
       <x:c r="L166" s="4">
-        <x:v>46086.6518199421</x:v>
+        <x:v>46087.0783034375</x:v>
       </x:c>
       <x:c r="M166" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="N166" s="4">
-        <x:v>46090.4456414005</x:v>
+        <x:v>46090.4474321412</x:v>
       </x:c>
       <x:c r="O166" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="P166" s="1" t="n">
-        <x:v>3.48</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="Q166" s="1" t="n">
-        <x:v>27.62076</x:v>
+        <x:v>67.4645</x:v>
       </x:c>
       <x:c r="R166" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="S166" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="T166" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U166" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="V166" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="W166" s="3">
-        <x:v>46095</x:v>
+        <x:v>46099</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:29">
       <x:c r="A167" s="4">
-        <x:v>46090.4485225694</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B167" s="1" t="n">
-        <x:v>35910</x:v>
+        <x:v>35911</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
         <x:v>48</x:v>
@@ -12766,61 +12863,61 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="F167" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G167" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="I167" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J167" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K167" s="4">
-        <x:v>46087.078303206</x:v>
+        <x:v>46086.6518195255</x:v>
       </x:c>
       <x:c r="L167" s="4">
-        <x:v>46087.0783034375</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M167" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N167" s="4">
-        <x:v>46090.4474321412</x:v>
+        <x:v>46090.4456414005</x:v>
       </x:c>
       <x:c r="O167" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="P167" s="1" t="n">
-        <x:v>8.5</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="Q167" s="1" t="n">
-        <x:v>67.4645</x:v>
+        <x:v>20.00124</x:v>
       </x:c>
       <x:c r="R167" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="S167" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T167" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="U167" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="V167" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="W167" s="3">
-        <x:v>46099</x:v>
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:29">
@@ -12828,7 +12925,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B168" s="1" t="n">
-        <x:v>35911</x:v>
+        <x:v>35912</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
         <x:v>48</x:v>
@@ -12837,22 +12934,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F168" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G168" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="I168" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J168" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K168" s="4">
         <x:v>46086.6518195255</x:v>
@@ -12861,7 +12958,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M168" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N168" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12870,16 +12967,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P168" s="1" t="n">
-        <x:v>0.63</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="Q168" s="1" t="n">
-        <x:v>20.00124</x:v>
+        <x:v>13.88975</x:v>
       </x:c>
       <x:c r="R168" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S168" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T168" s="1" t="n">
         <x:v>10</x:v>
@@ -12888,7 +12985,7 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="V168" s="1" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W168" s="3">
         <x:v>46095</x:v>
@@ -12896,111 +12993,111 @@
     </x:row>
     <x:row r="169" spans="1:29">
       <x:c r="A169" s="4">
-        <x:v>46090.4467435532</x:v>
+        <x:v>46111.7199709144</x:v>
       </x:c>
       <x:c r="B169" s="1" t="n">
-        <x:v>35912</x:v>
+        <x:v>35913</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F169" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G169" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="I169" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J169" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K169" s="4">
-        <x:v>46086.6518195255</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L169" s="4">
-        <x:v>46086.6518199421</x:v>
+        <x:v>46111.7199707986</x:v>
       </x:c>
       <x:c r="M169" s="1" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="N169" s="4">
-        <x:v>46090.4456414005</x:v>
-      </x:c>
-      <x:c r="O169" s="1" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="P169" s="1" t="n">
-        <x:v>1.75</x:v>
-      </x:c>
-      <x:c r="Q169" s="1" t="n">
-        <x:v>13.88975</x:v>
-      </x:c>
-      <x:c r="R169" s="1" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="S169" s="1" t="s">
-        <x:v>419</x:v>
-      </x:c>
-      <x:c r="T169" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="U169" s="1" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="V169" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="W169" s="3">
-        <x:v>46095</x:v>
+        <x:v>458</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:29">
       <x:c r="A170" s="4">
-        <x:v>46111.7199709144</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B170" s="1" t="n">
-        <x:v>35913</x:v>
+        <x:v>35914</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D170" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F170" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G170" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H170" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="I170" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J170" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K170" s="4">
+        <x:v>46086.6518195255</x:v>
       </x:c>
       <x:c r="L170" s="4">
-        <x:v>46111.7199707986</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M170" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="N170" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O170" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P170" s="1" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="Q170" s="1" t="n">
+        <x:v>58.7338</x:v>
+      </x:c>
+      <x:c r="R170" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S170" s="1" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="T170" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U170" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V170" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="W170" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:29">
@@ -13008,7 +13105,7 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B171" s="1" t="n">
-        <x:v>35914</x:v>
+        <x:v>35915</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
         <x:v>48</x:v>
@@ -13017,22 +13114,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="F171" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="G171" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H171" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="I171" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J171" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K171" s="4">
         <x:v>46086.6518195255</x:v>
@@ -13041,7 +13138,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M171" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N171" s="4">
         <x:v>46090.4456414005</x:v>
@@ -13050,16 +13147,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P171" s="1" t="n">
-        <x:v>3.7</x:v>
+        <x:v>5.86</x:v>
       </x:c>
       <x:c r="Q171" s="1" t="n">
-        <x:v>58.7338</x:v>
+        <x:v>23.25541</x:v>
       </x:c>
       <x:c r="R171" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S171" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T171" s="1" t="n">
         <x:v>10</x:v>
@@ -13068,7 +13165,7 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="V171" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W171" s="3">
         <x:v>46095</x:v>
@@ -13076,10 +13173,10 @@
     </x:row>
     <x:row r="172" spans="1:29">
       <x:c r="A172" s="4">
-        <x:v>46090.4467435532</x:v>
+        <x:v>46090.447941169</x:v>
       </x:c>
       <x:c r="B172" s="1" t="n">
-        <x:v>35915</x:v>
+        <x:v>35916</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
         <x:v>48</x:v>
@@ -13088,16 +13185,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="F172" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="G172" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H172" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="I172" s="1" t="n">
         <x:v>1</x:v>
@@ -13106,182 +13203,182 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K172" s="4">
-        <x:v>46086.6518195255</x:v>
+        <x:v>46085.6136977199</x:v>
       </x:c>
       <x:c r="L172" s="4">
-        <x:v>46086.6518199421</x:v>
+        <x:v>46090.4477212616</x:v>
       </x:c>
       <x:c r="M172" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="N172" s="4">
-        <x:v>46090.4456414005</x:v>
+        <x:v>46090.447721412</x:v>
       </x:c>
       <x:c r="O172" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="P172" s="1" t="n">
-        <x:v>5.86</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="Q172" s="1" t="n">
-        <x:v>23.25541</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="R172" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="S172" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="T172" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U172" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="V172" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W172" s="3">
-        <x:v>46095</x:v>
+        <x:v>46113</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:29">
       <x:c r="A173" s="4">
-        <x:v>46090.447941169</x:v>
+        <x:v>46092.6276936343</x:v>
       </x:c>
       <x:c r="B173" s="1" t="n">
-        <x:v>35916</x:v>
+        <x:v>36010</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F173" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G173" s="1" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H173" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I173" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J173" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K173" s="4">
-        <x:v>46085.6136977199</x:v>
+        <x:v>46092.6231591088</x:v>
       </x:c>
       <x:c r="L173" s="4">
-        <x:v>46090.4477212616</x:v>
+        <x:v>46092.627584375</x:v>
       </x:c>
       <x:c r="M173" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="N173" s="4">
-        <x:v>46090.447721412</x:v>
+        <x:v>46092.6275845255</x:v>
       </x:c>
       <x:c r="O173" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="P173" s="1" t="n">
-        <x:v>885</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="Q173" s="1" t="n">
-        <x:v>885</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="R173" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="S173" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="T173" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U173" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="V173" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W173" s="3">
-        <x:v>46113</x:v>
+        <x:v>46094</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:29">
       <x:c r="A174" s="4">
-        <x:v>46092.6276936343</x:v>
+        <x:v>46107.6118467593</x:v>
       </x:c>
       <x:c r="B174" s="1" t="n">
-        <x:v>36010</x:v>
+        <x:v>36279</x:v>
       </x:c>
       <x:c r="C174" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F174" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="G174" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H174" s="1" t="s">
+        <x:v>476</x:v>
       </x:c>
       <x:c r="I174" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J174" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K174" s="4">
-        <x:v>46092.6231591088</x:v>
+        <x:v>46093.0045248843</x:v>
       </x:c>
       <x:c r="L174" s="4">
-        <x:v>46092.627584375</x:v>
+        <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M174" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="N174" s="4">
-        <x:v>46092.6275845255</x:v>
+        <x:v>46107.6111298611</x:v>
       </x:c>
       <x:c r="O174" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="P174" s="1" t="n">
-        <x:v>66</x:v>
+        <x:v>137.84</x:v>
       </x:c>
       <x:c r="Q174" s="1" t="n">
-        <x:v>132</x:v>
+        <x:v>137.84</x:v>
       </x:c>
       <x:c r="R174" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="S174" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="T174" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="U174" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="V174" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W174" s="3">
-        <x:v>46094</x:v>
+        <x:v>46115</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:29">
@@ -13289,7 +13386,7 @@
         <x:v>46107.6118467593</x:v>
       </x:c>
       <x:c r="B175" s="1" t="n">
-        <x:v>36279</x:v>
+        <x:v>36280</x:v>
       </x:c>
       <x:c r="C175" s="1" t="s">
         <x:v>48</x:v>
@@ -13298,22 +13395,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="F175" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="G175" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="I175" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J175" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K175" s="4">
         <x:v>46093.0045248843</x:v>
@@ -13322,34 +13419,34 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M175" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="N175" s="4">
         <x:v>46107.6111298611</x:v>
       </x:c>
       <x:c r="O175" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="P175" s="1" t="n">
-        <x:v>137.84</x:v>
+        <x:v>1.02</x:v>
       </x:c>
       <x:c r="Q175" s="1" t="n">
-        <x:v>137.84</x:v>
+        <x:v>4.08</x:v>
       </x:c>
       <x:c r="R175" s="1" t="s">
         <x:v>195</x:v>
       </x:c>
       <x:c r="S175" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="T175" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="U175" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="V175" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W175" s="3">
         <x:v>46115</x:v>
@@ -13360,7 +13457,7 @@
         <x:v>46107.6118467593</x:v>
       </x:c>
       <x:c r="B176" s="1" t="n">
-        <x:v>36280</x:v>
+        <x:v>36281</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
         <x:v>48</x:v>
@@ -13369,16 +13466,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="F176" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="G176" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H176" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="I176" s="1" t="n">
         <x:v>4</x:v>
@@ -13393,31 +13490,31 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M176" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="N176" s="4">
         <x:v>46107.6111298611</x:v>
       </x:c>
       <x:c r="O176" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="P176" s="1" t="n">
-        <x:v>1.02</x:v>
+        <x:v>2.37</x:v>
       </x:c>
       <x:c r="Q176" s="1" t="n">
-        <x:v>4.08</x:v>
+        <x:v>9.48</x:v>
       </x:c>
       <x:c r="R176" s="1" t="s">
         <x:v>195</x:v>
       </x:c>
       <x:c r="S176" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="T176" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="U176" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="V176" s="1" t="n">
         <x:v>4</x:v>
@@ -13428,181 +13525,145 @@
     </x:row>
     <x:row r="177" spans="1:29">
       <x:c r="A177" s="4">
-        <x:v>46107.6118467593</x:v>
+        <x:v>46097.6308056366</x:v>
       </x:c>
       <x:c r="B177" s="1" t="n">
-        <x:v>36281</x:v>
+        <x:v>36282</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F177" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="G177" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H177" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="I177" s="1" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J177" s="1" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K177" s="4">
-        <x:v>46093.0045248843</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L177" s="4">
-        <x:v>46093.0045250347</x:v>
+        <x:v>46093.0051497338</x:v>
       </x:c>
       <x:c r="M177" s="1" t="s">
-        <x:v>474</x:v>
-      </x:c>
-      <x:c r="N177" s="4">
-        <x:v>46107.6111298611</x:v>
-      </x:c>
-      <x:c r="O177" s="1" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="P177" s="1" t="n">
-        <x:v>2.37</x:v>
-      </x:c>
-      <x:c r="Q177" s="1" t="n">
-        <x:v>9.48</x:v>
-      </x:c>
-      <x:c r="R177" s="1" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="S177" s="1" t="s">
-        <x:v>476</x:v>
-      </x:c>
-      <x:c r="T177" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="U177" s="1" t="s">
-        <x:v>477</x:v>
-      </x:c>
-      <x:c r="V177" s="1" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="W177" s="3">
-        <x:v>46115</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:29">
       <x:c r="A178" s="4">
-        <x:v>46097.6308056366</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B178" s="1" t="n">
-        <x:v>36282</x:v>
+        <x:v>36360</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F178" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G178" s="1" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H178" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I178" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J178" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L178" s="4">
-        <x:v>46093.0051497338</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M178" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:29">
       <x:c r="A179" s="4">
-        <x:v>46085.4171919792</x:v>
+        <x:v>46085.4166482292</x:v>
       </x:c>
       <x:c r="B179" s="1" t="n">
-        <x:v>36360</x:v>
+        <x:v>36361</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="F179" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G179" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="I179" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J179" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L179" s="4">
-        <x:v>46085.4124951389</x:v>
+        <x:v>46085.4128305208</x:v>
       </x:c>
       <x:c r="M179" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:29">
       <x:c r="A180" s="4">
-        <x:v>46085.4166482292</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B180" s="1" t="n">
-        <x:v>36361</x:v>
+        <x:v>36362</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F180" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G180" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="I180" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J180" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L180" s="4">
-        <x:v>46085.4128305208</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M180" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:29">
@@ -13610,16 +13671,16 @@
         <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B181" s="1" t="n">
-        <x:v>36362</x:v>
+        <x:v>36363</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F181" s="1" t="s">
         <x:v>51</x:v>
@@ -13637,7 +13698,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M181" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:29">
@@ -13645,16 +13706,16 @@
         <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B182" s="1" t="n">
-        <x:v>36363</x:v>
+        <x:v>36364</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="F182" s="1" t="s">
         <x:v>51</x:v>
@@ -13663,16 +13724,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I182" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J182" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L182" s="4">
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M182" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:29">
@@ -13680,16 +13741,16 @@
         <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B183" s="1" t="n">
-        <x:v>36364</x:v>
+        <x:v>36365</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="F183" s="1" t="s">
         <x:v>51</x:v>
@@ -13698,16 +13759,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I183" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J183" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L183" s="4">
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M183" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:29">
@@ -13715,16 +13776,16 @@
         <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B184" s="1" t="n">
-        <x:v>36365</x:v>
+        <x:v>36366</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="F184" s="1" t="s">
         <x:v>51</x:v>
@@ -13742,7 +13803,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M184" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:29">
@@ -13750,16 +13811,16 @@
         <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B185" s="1" t="n">
-        <x:v>36366</x:v>
+        <x:v>36367</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="F185" s="1" t="s">
         <x:v>51</x:v>
@@ -13768,16 +13829,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I185" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J185" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L185" s="4">
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M185" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:29">
@@ -13785,16 +13846,16 @@
         <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B186" s="1" t="n">
-        <x:v>36367</x:v>
+        <x:v>36368</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E186" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="F186" s="1" t="s">
         <x:v>51</x:v>
@@ -13812,110 +13873,110 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M186" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:29">
       <x:c r="A187" s="4">
-        <x:v>46085.4171919792</x:v>
+        <x:v>46111.7202197917</x:v>
       </x:c>
       <x:c r="B187" s="1" t="n">
-        <x:v>36368</x:v>
+        <x:v>36369</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E187" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F187" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G187" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="I187" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J187" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K187" s="4">
+        <x:v>46111.6479773495</x:v>
       </x:c>
       <x:c r="L187" s="4">
-        <x:v>46085.4124951389</x:v>
+        <x:v>46111.7201420139</x:v>
       </x:c>
       <x:c r="M187" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="N187" s="4">
+        <x:v>46111.7201421644</x:v>
+      </x:c>
+      <x:c r="O187" s="1" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="P187" s="1" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q187" s="1" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="R187" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="S187" s="1" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="T187" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U187" s="1" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="V187" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W187" s="3">
+        <x:v>46126</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:29">
       <x:c r="A188" s="4">
-        <x:v>46111.7202197917</x:v>
+        <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B188" s="1" t="n">
-        <x:v>36369</x:v>
+        <x:v>36370</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F188" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G188" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="I188" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J188" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K188" s="4">
-        <x:v>46111.6479773495</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L188" s="4">
-        <x:v>46111.7201420139</x:v>
+        <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M188" s="1" t="s">
-        <x:v>498</x:v>
-      </x:c>
-      <x:c r="N188" s="4">
-        <x:v>46111.7201421644</x:v>
-      </x:c>
-      <x:c r="O188" s="1" t="s">
-        <x:v>499</x:v>
-      </x:c>
-      <x:c r="P188" s="1" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="Q188" s="1" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="R188" s="1" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="S188" s="1" t="s">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="T188" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U188" s="1" t="s">
-        <x:v>501</x:v>
-      </x:c>
-      <x:c r="V188" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="W188" s="3">
-        <x:v>46126</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:29">
@@ -13923,16 +13984,16 @@
         <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B189" s="1" t="n">
-        <x:v>36370</x:v>
+        <x:v>36371</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>502</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="F189" s="1" t="s">
         <x:v>51</x:v>
@@ -13941,16 +14002,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I189" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J189" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L189" s="4">
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M189" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:29">
@@ -13958,16 +14019,16 @@
         <x:v>46085.4171919792</x:v>
       </x:c>
       <x:c r="B190" s="1" t="n">
-        <x:v>36371</x:v>
+        <x:v>36372</x:v>
       </x:c>
       <x:c r="C190" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>503</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="F190" s="1" t="s">
         <x:v>51</x:v>
@@ -13985,30 +14046,33 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M190" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:29">
       <x:c r="A191" s="4">
-        <x:v>46085.4171919792</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B191" s="1" t="n">
-        <x:v>36372</x:v>
+        <x:v>36373</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>504</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="F191" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="G191" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H191" s="1" t="s">
+        <x:v>510</x:v>
       </x:c>
       <x:c r="I191" s="1" t="n">
         <x:v>2</x:v>
@@ -14016,11 +14080,44 @@
       <x:c r="J191" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K191" s="4">
+        <x:v>46086.7622765857</x:v>
+      </x:c>
       <x:c r="L191" s="4">
-        <x:v>46085.4124951389</x:v>
+        <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M191" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="N191" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O191" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P191" s="1" t="n">
+        <x:v>88.87</x:v>
+      </x:c>
+      <x:c r="Q191" s="1" t="n">
+        <x:v>705.36119</x:v>
+      </x:c>
+      <x:c r="R191" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S191" s="1" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="T191" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U191" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V191" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W191" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:29">
@@ -14028,25 +14125,25 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B192" s="1" t="n">
-        <x:v>36373</x:v>
+        <x:v>36374</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
-        <x:v>505</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="F192" s="1" t="s">
-        <x:v>506</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="G192" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H192" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="I192" s="1" t="n">
         <x:v>2</x:v>
@@ -14061,7 +14158,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M192" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="N192" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14070,16 +14167,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P192" s="1" t="n">
-        <x:v>88.87</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="Q192" s="1" t="n">
-        <x:v>705.36119</x:v>
+        <x:v>19.92187</x:v>
       </x:c>
       <x:c r="R192" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S192" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="T192" s="1" t="n">
         <x:v>1</x:v>
@@ -14099,25 +14196,25 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B193" s="1" t="n">
-        <x:v>36374</x:v>
+        <x:v>36375</x:v>
       </x:c>
       <x:c r="C193" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>510</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="F193" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G193" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H193" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="I193" s="1" t="n">
         <x:v>2</x:v>
@@ -14132,7 +14229,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M193" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="N193" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14141,16 +14238,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P193" s="1" t="n">
-        <x:v>2.51</x:v>
+        <x:v>5.72</x:v>
       </x:c>
       <x:c r="Q193" s="1" t="n">
-        <x:v>19.92187</x:v>
+        <x:v>45.39964</x:v>
       </x:c>
       <x:c r="R193" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S193" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="T193" s="1" t="n">
         <x:v>1</x:v>
@@ -14170,16 +14267,16 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B194" s="1" t="n">
-        <x:v>36375</x:v>
+        <x:v>36376</x:v>
       </x:c>
       <x:c r="C194" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
-        <x:v>513</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F194" s="1" t="s">
         <x:v>222</x:v>
@@ -14188,7 +14285,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H194" s="1" t="s">
-        <x:v>514</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="I194" s="1" t="n">
         <x:v>2</x:v>
@@ -14203,7 +14300,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M194" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="N194" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14212,16 +14309,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P194" s="1" t="n">
-        <x:v>5.72</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="Q194" s="1" t="n">
-        <x:v>45.39964</x:v>
+        <x:v>7.1433</x:v>
       </x:c>
       <x:c r="R194" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S194" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="T194" s="1" t="n">
         <x:v>1</x:v>
@@ -14241,40 +14338,28 @@
         <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B195" s="1" t="n">
-        <x:v>36376</x:v>
+        <x:v>36508</x:v>
       </x:c>
       <x:c r="C195" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D195" s="1" t="s">
-        <x:v>485</x:v>
-      </x:c>
       <x:c r="E195" s="1" t="s">
-        <x:v>515</x:v>
-      </x:c>
-      <x:c r="F195" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="G195" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="H195" s="1" t="s">
-        <x:v>516</x:v>
-      </x:c>
-      <x:c r="I195" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="J195" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K195" s="4">
-        <x:v>46086.7622765857</x:v>
+        <x:v>46086.6518195255</x:v>
       </x:c>
       <x:c r="L195" s="4">
-        <x:v>46086.7622771991</x:v>
+        <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M195" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N195" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14283,25 +14368,25 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="P195" s="1" t="n">
-        <x:v>0.9</x:v>
+        <x:v>52.64</x:v>
       </x:c>
       <x:c r="Q195" s="1" t="n">
-        <x:v>7.1433</x:v>
+        <x:v>208.90184</x:v>
       </x:c>
       <x:c r="R195" s="1" t="s">
         <x:v>226</x:v>
       </x:c>
       <x:c r="S195" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="T195" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="U195" s="1" t="s">
         <x:v>228</x:v>
       </x:c>
       <x:c r="V195" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W195" s="3">
         <x:v>46095</x:v>
@@ -14309,155 +14394,131 @@
     </x:row>
     <x:row r="196" spans="1:29">
       <x:c r="A196" s="4">
-        <x:v>46090.4467435532</x:v>
+        <x:v>46087.3857842245</x:v>
       </x:c>
       <x:c r="B196" s="1" t="n">
-        <x:v>36508</x:v>
+        <x:v>36516</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D196" s="1" t="s">
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="F196" s="1" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G196" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I196" s="1" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J196" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K196" s="4">
-        <x:v>46086.6518195255</x:v>
-      </x:c>
       <x:c r="L196" s="4">
-        <x:v>46086.6518199421</x:v>
+        <x:v>46086.7566555556</x:v>
       </x:c>
       <x:c r="M196" s="1" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="N196" s="4">
-        <x:v>46090.4456414005</x:v>
-      </x:c>
-      <x:c r="O196" s="1" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="P196" s="1" t="n">
-        <x:v>52.64</x:v>
-      </x:c>
-      <x:c r="Q196" s="1" t="n">
-        <x:v>208.90184</x:v>
-      </x:c>
-      <x:c r="R196" s="1" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="S196" s="1" t="s">
-        <x:v>419</x:v>
-      </x:c>
-      <x:c r="T196" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="U196" s="1" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="V196" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W196" s="3">
-        <x:v>46095</x:v>
+        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:29">
       <x:c r="A197" s="4">
-        <x:v>46087.3857842245</x:v>
+        <x:v>46090.4467435532</x:v>
       </x:c>
       <x:c r="B197" s="1" t="n">
-        <x:v>36516</x:v>
+        <x:v>36518</x:v>
       </x:c>
       <x:c r="C197" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D197" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E197" s="1" t="s">
-        <x:v>518</x:v>
-      </x:c>
-      <x:c r="F197" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="G197" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I197" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="J197" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K197" s="4">
+        <x:v>46086.7622765857</x:v>
+      </x:c>
       <x:c r="L197" s="4">
-        <x:v>46086.7566555556</x:v>
+        <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M197" s="1" t="s">
-        <x:v>519</x:v>
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="N197" s="4">
+        <x:v>46090.4456414005</x:v>
+      </x:c>
+      <x:c r="O197" s="1" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P197" s="1" t="n">
+        <x:v>92.08</x:v>
+      </x:c>
+      <x:c r="Q197" s="1" t="n">
+        <x:v>365.41948</x:v>
+      </x:c>
+      <x:c r="R197" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S197" s="1" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="T197" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U197" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="V197" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W197" s="3">
+        <x:v>46095</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:29">
       <x:c r="A198" s="4">
-        <x:v>46090.4467435532</x:v>
+        <x:v>46100.4842279745</x:v>
       </x:c>
       <x:c r="B198" s="1" t="n">
-        <x:v>36518</x:v>
+        <x:v>37261</x:v>
       </x:c>
       <x:c r="C198" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D198" s="1" t="s">
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E198" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="F198" s="1" t="s">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G198" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I198" s="1" t="n">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J198" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K198" s="4">
-        <x:v>46086.7622765857</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L198" s="4">
-        <x:v>46086.7622771991</x:v>
+        <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M198" s="1" t="s">
-        <x:v>508</x:v>
-      </x:c>
-      <x:c r="N198" s="4">
-        <x:v>46090.4456414005</x:v>
-      </x:c>
-      <x:c r="O198" s="1" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="P198" s="1" t="n">
-        <x:v>92.08</x:v>
-      </x:c>
-      <x:c r="Q198" s="1" t="n">
-        <x:v>365.41948</x:v>
-      </x:c>
-      <x:c r="R198" s="1" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="S198" s="1" t="s">
-        <x:v>509</x:v>
-      </x:c>
-      <x:c r="T198" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U198" s="1" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="V198" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W198" s="3">
-        <x:v>46095</x:v>
+        <x:v>526</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:29">
@@ -14465,16 +14526,16 @@
         <x:v>46100.4842279745</x:v>
       </x:c>
       <x:c r="B199" s="1" t="n">
-        <x:v>37261</x:v>
+        <x:v>37262</x:v>
       </x:c>
       <x:c r="C199" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D199" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E199" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="F199" s="1" t="s">
         <x:v>64</x:v>
@@ -14483,16 +14544,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I199" s="1" t="n">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J199" s="1" t="n">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L199" s="4">
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M199" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>526</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:29">
@@ -14500,16 +14561,16 @@
         <x:v>46100.4842279745</x:v>
       </x:c>
       <x:c r="B200" s="1" t="n">
-        <x:v>37262</x:v>
+        <x:v>37265</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E200" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="F200" s="1" t="s">
         <x:v>64</x:v>
@@ -14518,16 +14579,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I200" s="1" t="n">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J200" s="1" t="n">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L200" s="4">
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M200" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>526</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:29">
@@ -14535,16 +14596,16 @@
         <x:v>46100.4842279745</x:v>
       </x:c>
       <x:c r="B201" s="1" t="n">
-        <x:v>37265</x:v>
+        <x:v>37266</x:v>
       </x:c>
       <x:c r="C201" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F201" s="1" t="s">
         <x:v>64</x:v>
@@ -14562,42 +14623,42 @@
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M201" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>526</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:29">
       <x:c r="A202" s="4">
-        <x:v>46100.4842279745</x:v>
+        <x:v>46100.4847336806</x:v>
       </x:c>
       <x:c r="B202" s="1" t="n">
-        <x:v>37266</x:v>
+        <x:v>37412</x:v>
       </x:c>
       <x:c r="C202" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D202" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E202" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="F202" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G202" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="I202" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J202" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L202" s="4">
-        <x:v>46098.5238698727</x:v>
+        <x:v>46100.4729106481</x:v>
       </x:c>
       <x:c r="M202" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>531</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:29">
@@ -14605,16 +14666,16 @@
         <x:v>46100.4847336806</x:v>
       </x:c>
       <x:c r="B203" s="1" t="n">
-        <x:v>37412</x:v>
+        <x:v>37413</x:v>
       </x:c>
       <x:c r="C203" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="D203" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>527</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="F203" s="1" t="s">
         <x:v>51</x:v>
@@ -14623,51 +14684,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I203" s="1" t="n">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J203" s="1" t="n">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L203" s="4">
         <x:v>46100.4729106481</x:v>
       </x:c>
       <x:c r="M203" s="1" t="s">
-        <x:v>528</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" spans="1:29">
-      <x:c r="A204" s="4">
-        <x:v>46100.4847336806</x:v>
-      </x:c>
-      <x:c r="B204" s="1" t="n">
-        <x:v>37413</x:v>
-      </x:c>
-      <x:c r="C204" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D204" s="1" t="s">
-        <x:v>521</x:v>
-      </x:c>
-      <x:c r="E204" s="1" t="s">
-        <x:v>529</x:v>
-      </x:c>
-      <x:c r="F204" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G204" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I204" s="1" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J204" s="1" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="L204" s="4">
-        <x:v>46100.4729106481</x:v>
-      </x:c>
-      <x:c r="M204" s="1" t="s">
-        <x:v>528</x:v>
+        <x:v>531</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/bom.xlsx
+++ b/bom.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="533">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="568">
   <x:si>
     <x:t>Document No</x:t>
   </x:si>
@@ -884,6 +884,9 @@
     <x:t>PR5310321</x:t>
   </x:si>
   <x:si>
+    <x:t>Item Received</x:t>
+  </x:si>
+  <x:si>
     <x:t>Gear box</x:t>
   </x:si>
   <x:si>
@@ -1196,9 +1199,6 @@
     <x:t>OMR513-S1005A</x:t>
   </x:si>
   <x:si>
-    <x:t>PR Sent</x:t>
-  </x:si>
-  <x:si>
     <x:t>string wheel</x:t>
   </x:si>
   <x:si>
@@ -1216,6 +1216,9 @@
   <x:si>
     <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/47659
 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAPO26040057</x:t>
   </x:si>
   <x:si>
     <x:t>bearing</x:t>
@@ -1249,6 +1252,9 @@
 [TAS02-10]</x:t>
   </x:si>
   <x:si>
+    <x:t>PR Sent</x:t>
+  </x:si>
+  <x:si>
     <x:t>height sensor</x:t>
   </x:si>
   <x:si>
@@ -1261,6 +1267,16 @@
     <x:t>RFQ4129242</x:t>
   </x:si>
   <x:si>
+    <x:t>PR5338671</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Turck Banner Malaysia Sdn Bhd</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/48352
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>slipring</x:t>
   </x:si>
   <x:si>
@@ -1271,6 +1287,13 @@
   </x:si>
   <x:si>
     <x:t>RFQ4136261</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fulitech Technology Co. Limited</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/48029
+</x:t>
   </x:si>
   <x:si>
     <x:t>clamp plate</x:t>
@@ -1302,9 +1325,6 @@
   </x:si>
   <x:si>
     <x:t>PR5327031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fulitech Technology Co. Limited</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/46660
@@ -1462,6 +1482,13 @@
     <x:t>RFQ4130831</x:t>
   </x:si>
   <x:si>
+    <x:t>PR5338681</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/48197
+</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">E-CLBUS12-15-1.5
 【BKP11-d12-D15-L1.5】	
 </x:t>
@@ -1556,6 +1583,16 @@
     <x:t>RFQ4132491</x:t>
   </x:si>
   <x:si>
+    <x:t>PR5338661</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CHUNG MENG INDUSTRIAL SUPPLY SDN BHD </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/48597
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>Safety Guide</x:t>
   </x:si>
   <x:si>
@@ -1697,6 +1734,82 @@
   </x:si>
   <x:si>
     <x:t>OMR-2704A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR Approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Diverter Bearing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B6300ZZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4136331</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5335301</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/47996
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hoist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GearBox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Liming</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ST-RO-75-20/7MP62A-50-A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4136341</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5334971</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/47992
+https://internal.sophicauto.net/BOM/downloadFile/48027
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Right Angle Gear Reducer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYG17-G10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4137451</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Telescopic Motor + DDP Freight Charges</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4137461</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PR5335281</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://internal.sophicauto.net/BOM/downloadFile/48246
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rotary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A25.OMR.006.011.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RFQ4139541</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2085,7 +2198,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AC203"/>
+  <x:dimension ref="A1:AC208"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="30" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -7489,28 +7602,28 @@
     </x:row>
     <x:row r="84" spans="1:29">
       <x:c r="A84" s="4">
-        <x:v>46090.4481799421</x:v>
+        <x:v>46118.0053996181</x:v>
       </x:c>
       <x:c r="B84" s="1" t="n">
         <x:v>35728</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
         <x:v>272</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="I84" s="1" t="n">
         <x:v>1</x:v>
@@ -7525,13 +7638,13 @@
         <x:v>46090.4481129977</x:v>
       </x:c>
       <x:c r="M84" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="N84" s="4">
         <x:v>46090.4481131134</x:v>
       </x:c>
       <x:c r="O84" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="P84" s="1" t="n">
         <x:v>2100</x:v>
@@ -7540,22 +7653,28 @@
         <x:v>2100</x:v>
       </x:c>
       <x:c r="R84" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="S84" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="T84" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U84" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="V84" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W84" s="3">
         <x:v>46106</x:v>
+      </x:c>
+      <x:c r="Z84" s="3">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="AA84" s="1" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:29">
@@ -7572,7 +7691,7 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
         <x:v>191</x:v>
@@ -7581,7 +7700,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="I85" s="1" t="n">
         <x:v>4</x:v>
@@ -7602,7 +7721,7 @@
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O85" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P85" s="1" t="n">
         <x:v>24.84</x:v>
@@ -7620,7 +7739,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U85" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V85" s="1" t="n">
         <x:v>4</x:v>
@@ -7640,10 +7759,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
         <x:v>191</x:v>
@@ -7652,7 +7771,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="I86" s="1" t="n">
         <x:v>2</x:v>
@@ -7667,13 +7786,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M86" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N86" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O86" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P86" s="1" t="n">
         <x:v>23.97</x:v>
@@ -7685,13 +7804,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S86" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T86" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U86" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V86" s="1" t="n">
         <x:v>2</x:v>
@@ -7711,10 +7830,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
         <x:v>191</x:v>
@@ -7723,7 +7842,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="I87" s="1" t="n">
         <x:v>4</x:v>
@@ -7738,13 +7857,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M87" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N87" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O87" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P87" s="1" t="n">
         <x:v>62.66</x:v>
@@ -7756,13 +7875,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S87" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T87" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U87" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V87" s="1" t="n">
         <x:v>4</x:v>
@@ -7782,10 +7901,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
         <x:v>191</x:v>
@@ -7794,7 +7913,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="I88" s="1" t="n">
         <x:v>4</x:v>
@@ -7809,13 +7928,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M88" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N88" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O88" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P88" s="1" t="n">
         <x:v>46.38</x:v>
@@ -7827,13 +7946,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S88" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T88" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U88" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V88" s="1" t="n">
         <x:v>4</x:v>
@@ -7853,10 +7972,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
         <x:v>191</x:v>
@@ -7865,7 +7984,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="I89" s="1" t="n">
         <x:v>6</x:v>
@@ -7880,13 +7999,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M89" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N89" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O89" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P89" s="1" t="n">
         <x:v>309.14</x:v>
@@ -7898,13 +8017,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S89" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T89" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U89" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V89" s="1" t="n">
         <x:v>6</x:v>
@@ -7924,7 +8043,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
         <x:v>217</x:v>
@@ -7936,7 +8055,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="I90" s="1" t="n">
         <x:v>4</x:v>
@@ -7951,13 +8070,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M90" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N90" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O90" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P90" s="1" t="n">
         <x:v>12.4</x:v>
@@ -7969,13 +8088,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S90" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T90" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U90" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V90" s="1" t="n">
         <x:v>4</x:v>
@@ -7995,10 +8114,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
         <x:v>191</x:v>
@@ -8007,7 +8126,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="I91" s="1" t="n">
         <x:v>1</x:v>
@@ -8022,13 +8141,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M91" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N91" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O91" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P91" s="1" t="n">
         <x:v>16.6</x:v>
@@ -8040,13 +8159,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S91" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T91" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U91" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V91" s="1" t="n">
         <x:v>1</x:v>
@@ -8066,10 +8185,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
         <x:v>191</x:v>
@@ -8078,7 +8197,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="I92" s="1" t="n">
         <x:v>1</x:v>
@@ -8093,13 +8212,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M92" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N92" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O92" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P92" s="1" t="n">
         <x:v>32.03</x:v>
@@ -8111,13 +8230,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S92" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T92" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U92" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V92" s="1" t="n">
         <x:v>1</x:v>
@@ -8137,10 +8256,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
         <x:v>191</x:v>
@@ -8149,7 +8268,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="I93" s="1" t="n">
         <x:v>2</x:v>
@@ -8164,13 +8283,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M93" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N93" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O93" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P93" s="1" t="n">
         <x:v>73.31</x:v>
@@ -8182,13 +8301,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S93" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T93" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U93" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V93" s="1" t="n">
         <x:v>2</x:v>
@@ -8208,10 +8327,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
         <x:v>191</x:v>
@@ -8220,7 +8339,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="I94" s="1" t="n">
         <x:v>2</x:v>
@@ -8235,13 +8354,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M94" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N94" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O94" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P94" s="1" t="n">
         <x:v>56.66</x:v>
@@ -8253,13 +8372,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S94" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T94" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U94" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V94" s="1" t="n">
         <x:v>2</x:v>
@@ -8279,10 +8398,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
         <x:v>191</x:v>
@@ -8291,7 +8410,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="I95" s="1" t="n">
         <x:v>1</x:v>
@@ -8306,13 +8425,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M95" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N95" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O95" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P95" s="1" t="n">
         <x:v>62.1</x:v>
@@ -8324,13 +8443,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S95" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T95" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U95" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V95" s="1" t="n">
         <x:v>1</x:v>
@@ -8350,7 +8469,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>273</x:v>
@@ -8362,7 +8481,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="I96" s="1" t="n">
         <x:v>1</x:v>
@@ -8377,13 +8496,13 @@
         <x:v>46065.9676302431</x:v>
       </x:c>
       <x:c r="M96" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N96" s="4">
         <x:v>46066.6658176273</x:v>
       </x:c>
       <x:c r="O96" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="P96" s="1" t="n">
         <x:v>11.33</x:v>
@@ -8395,13 +8514,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S96" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="T96" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U96" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="V96" s="1" t="n">
         <x:v>1</x:v>
@@ -8421,7 +8540,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
         <x:v>234</x:v>
@@ -8433,7 +8552,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="I97" s="1" t="n">
         <x:v>3</x:v>
@@ -8448,13 +8567,13 @@
         <x:v>46079.4450462963</x:v>
       </x:c>
       <x:c r="M97" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="N97" s="4">
         <x:v>46079.445046412</x:v>
       </x:c>
       <x:c r="O97" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="P97" s="1" t="n">
         <x:v>25</x:v>
@@ -8466,13 +8585,13 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="S97" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="T97" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U97" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="V97" s="1" t="n">
         <x:v>3</x:v>
@@ -8492,10 +8611,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
         <x:v>51</x:v>
@@ -8513,7 +8632,7 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M98" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:29">
@@ -8527,10 +8646,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
         <x:v>51</x:v>
@@ -8548,7 +8667,7 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M99" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:29">
@@ -8562,10 +8681,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
         <x:v>51</x:v>
@@ -8583,7 +8702,7 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M100" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:29">
@@ -8597,10 +8716,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
         <x:v>51</x:v>
@@ -8618,7 +8737,7 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M101" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:29">
@@ -8632,10 +8751,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
         <x:v>51</x:v>
@@ -8653,24 +8772,24 @@
         <x:v>46065.6968415162</x:v>
       </x:c>
       <x:c r="M102" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:29">
       <x:c r="A103" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058697569</x:v>
       </x:c>
       <x:c r="B103" s="1" t="n">
         <x:v>35800</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
         <x:v>51</x:v>
@@ -8691,13 +8810,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M103" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N103" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O103" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P103" s="1" t="n">
         <x:v>70</x:v>
@@ -8709,13 +8828,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S103" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T103" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U103" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V103" s="1" t="n">
         <x:v>4</x:v>
@@ -8723,22 +8842,28 @@
       <x:c r="W103" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z103" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA103" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="104" spans="1:29">
       <x:c r="A104" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058699074</x:v>
       </x:c>
       <x:c r="B104" s="1" t="n">
         <x:v>35801</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
         <x:v>51</x:v>
@@ -8759,13 +8884,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M104" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N104" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O104" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P104" s="1" t="n">
         <x:v>35</x:v>
@@ -8777,13 +8902,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S104" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T104" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U104" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V104" s="1" t="n">
         <x:v>1</x:v>
@@ -8791,22 +8916,28 @@
       <x:c r="W104" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z104" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA104" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" spans="1:29">
       <x:c r="A105" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058699421</x:v>
       </x:c>
       <x:c r="B105" s="1" t="n">
         <x:v>35802</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
         <x:v>51</x:v>
@@ -8827,13 +8958,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M105" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N105" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O105" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P105" s="1" t="n">
         <x:v>85</x:v>
@@ -8845,13 +8976,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S105" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T105" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U105" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V105" s="1" t="n">
         <x:v>2</x:v>
@@ -8859,22 +8990,28 @@
       <x:c r="W105" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z105" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA105" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" spans="1:29">
       <x:c r="A106" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058700231</x:v>
       </x:c>
       <x:c r="B106" s="1" t="n">
         <x:v>35803</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
         <x:v>51</x:v>
@@ -8895,13 +9032,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M106" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N106" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O106" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P106" s="1" t="n">
         <x:v>275</x:v>
@@ -8913,13 +9050,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S106" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T106" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U106" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V106" s="1" t="n">
         <x:v>1</x:v>
@@ -8927,22 +9064,28 @@
       <x:c r="W106" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z106" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA106" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" spans="1:29">
       <x:c r="A107" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058702199</x:v>
       </x:c>
       <x:c r="B107" s="1" t="n">
         <x:v>35804</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
         <x:v>51</x:v>
@@ -8963,13 +9106,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M107" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N107" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O107" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P107" s="1" t="n">
         <x:v>50</x:v>
@@ -8981,13 +9124,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S107" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T107" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U107" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V107" s="1" t="n">
         <x:v>12</x:v>
@@ -8995,22 +9138,28 @@
       <x:c r="W107" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z107" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA107" s="1" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="108" spans="1:29">
       <x:c r="A108" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058702894</x:v>
       </x:c>
       <x:c r="B108" s="1" t="n">
         <x:v>35805</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
         <x:v>51</x:v>
@@ -9031,13 +9180,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M108" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N108" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O108" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P108" s="1" t="n">
         <x:v>25</x:v>
@@ -9049,13 +9198,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S108" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T108" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U108" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V108" s="1" t="n">
         <x:v>6</x:v>
@@ -9063,22 +9212,28 @@
       <x:c r="W108" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z108" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA108" s="1" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" spans="1:29">
       <x:c r="A109" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058703356</x:v>
       </x:c>
       <x:c r="B109" s="1" t="n">
         <x:v>35806</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
         <x:v>51</x:v>
@@ -9099,13 +9254,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M109" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N109" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O109" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P109" s="1" t="n">
         <x:v>100</x:v>
@@ -9117,13 +9272,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S109" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T109" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U109" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V109" s="1" t="n">
         <x:v>2</x:v>
@@ -9131,22 +9286,28 @@
       <x:c r="W109" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z109" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA109" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="110" spans="1:29">
       <x:c r="A110" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058704861</x:v>
       </x:c>
       <x:c r="B110" s="1" t="n">
         <x:v>35807</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F110" s="1" t="s">
         <x:v>51</x:v>
@@ -9167,13 +9328,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M110" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N110" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O110" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P110" s="1" t="n">
         <x:v>20</x:v>
@@ -9185,13 +9346,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S110" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T110" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U110" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V110" s="1" t="n">
         <x:v>12</x:v>
@@ -9199,22 +9360,28 @@
       <x:c r="W110" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z110" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA110" s="1" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="111" spans="1:29">
       <x:c r="A111" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058705671</x:v>
       </x:c>
       <x:c r="B111" s="1" t="n">
         <x:v>35808</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
         <x:v>51</x:v>
@@ -9235,13 +9402,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M111" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N111" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O111" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P111" s="1" t="n">
         <x:v>155</x:v>
@@ -9253,13 +9420,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S111" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T111" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U111" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V111" s="1" t="n">
         <x:v>1</x:v>
@@ -9267,22 +9434,28 @@
       <x:c r="W111" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z111" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA111" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="112" spans="1:29">
       <x:c r="A112" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058706019</x:v>
       </x:c>
       <x:c r="B112" s="1" t="n">
         <x:v>35809</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
         <x:v>51</x:v>
@@ -9303,13 +9476,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M112" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N112" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O112" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P112" s="1" t="n">
         <x:v>135</x:v>
@@ -9321,13 +9494,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S112" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T112" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U112" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V112" s="1" t="n">
         <x:v>4</x:v>
@@ -9335,22 +9508,28 @@
       <x:c r="W112" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z112" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA112" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="113" spans="1:29">
       <x:c r="A113" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058707523</x:v>
       </x:c>
       <x:c r="B113" s="1" t="n">
         <x:v>35810</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="F113" s="1" t="s">
         <x:v>51</x:v>
@@ -9371,13 +9550,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M113" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N113" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O113" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P113" s="1" t="n">
         <x:v>25</x:v>
@@ -9389,13 +9568,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S113" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T113" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U113" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V113" s="1" t="n">
         <x:v>2</x:v>
@@ -9403,22 +9582,28 @@
       <x:c r="W113" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z113" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA113" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="114" spans="1:29">
       <x:c r="A114" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058707986</x:v>
       </x:c>
       <x:c r="B114" s="1" t="n">
         <x:v>35811</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="F114" s="1" t="s">
         <x:v>51</x:v>
@@ -9439,13 +9624,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M114" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N114" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O114" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P114" s="1" t="n">
         <x:v>20</x:v>
@@ -9457,13 +9642,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S114" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T114" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U114" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V114" s="1" t="n">
         <x:v>2</x:v>
@@ -9471,22 +9656,28 @@
       <x:c r="W114" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z114" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA114" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="115" spans="1:29">
       <x:c r="A115" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058708681</x:v>
       </x:c>
       <x:c r="B115" s="1" t="n">
         <x:v>35812</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D115" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="F115" s="1" t="s">
         <x:v>51</x:v>
@@ -9507,13 +9698,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M115" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N115" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O115" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P115" s="1" t="n">
         <x:v>80</x:v>
@@ -9525,13 +9716,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S115" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T115" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U115" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V115" s="1" t="n">
         <x:v>2</x:v>
@@ -9539,22 +9730,28 @@
       <x:c r="W115" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z115" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA115" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="116" spans="1:29">
       <x:c r="A116" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058709838</x:v>
       </x:c>
       <x:c r="B116" s="1" t="n">
         <x:v>35813</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D116" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F116" s="1" t="s">
         <x:v>51</x:v>
@@ -9575,13 +9772,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M116" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N116" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O116" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P116" s="1" t="n">
         <x:v>15</x:v>
@@ -9593,13 +9790,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S116" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T116" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U116" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V116" s="1" t="n">
         <x:v>8</x:v>
@@ -9607,22 +9804,28 @@
       <x:c r="W116" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z116" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA116" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="117" spans="1:29">
       <x:c r="A117" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058711458</x:v>
       </x:c>
       <x:c r="B117" s="1" t="n">
         <x:v>35814</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D117" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="F117" s="1" t="s">
         <x:v>51</x:v>
@@ -9643,13 +9846,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M117" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N117" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O117" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P117" s="1" t="n">
         <x:v>18</x:v>
@@ -9661,13 +9864,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S117" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T117" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U117" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V117" s="1" t="n">
         <x:v>4</x:v>
@@ -9675,22 +9878,28 @@
       <x:c r="W117" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z117" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA117" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="118" spans="1:29">
       <x:c r="A118" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058711806</x:v>
       </x:c>
       <x:c r="B118" s="1" t="n">
         <x:v>35815</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D118" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F118" s="1" t="s">
         <x:v>51</x:v>
@@ -9711,13 +9920,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M118" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N118" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O118" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P118" s="1" t="n">
         <x:v>20</x:v>
@@ -9729,13 +9938,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S118" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T118" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U118" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V118" s="1" t="n">
         <x:v>2</x:v>
@@ -9743,22 +9952,28 @@
       <x:c r="W118" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z118" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA118" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="119" spans="1:29">
       <x:c r="A119" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058712963</x:v>
       </x:c>
       <x:c r="B119" s="1" t="n">
         <x:v>35816</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D119" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F119" s="1" t="s">
         <x:v>51</x:v>
@@ -9779,13 +9994,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M119" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N119" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O119" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P119" s="1" t="n">
         <x:v>20</x:v>
@@ -9797,13 +10012,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S119" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T119" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U119" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V119" s="1" t="n">
         <x:v>2</x:v>
@@ -9811,22 +10026,28 @@
       <x:c r="W119" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z119" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA119" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" spans="1:29">
       <x:c r="A120" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058713773</x:v>
       </x:c>
       <x:c r="B120" s="1" t="n">
         <x:v>35817</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D120" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F120" s="1" t="s">
         <x:v>51</x:v>
@@ -9847,13 +10068,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M120" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N120" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O120" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P120" s="1" t="n">
         <x:v>60</x:v>
@@ -9865,13 +10086,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S120" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T120" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U120" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V120" s="1" t="n">
         <x:v>4</x:v>
@@ -9879,22 +10100,28 @@
       <x:c r="W120" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z120" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA120" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="121" spans="1:29">
       <x:c r="A121" s="4">
-        <x:v>46093.456763044</x:v>
+        <x:v>46118.0058714468</x:v>
       </x:c>
       <x:c r="B121" s="1" t="n">
         <x:v>35818</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D121" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="F121" s="1" t="s">
         <x:v>51</x:v>
@@ -9915,13 +10142,13 @@
         <x:v>46093.4548872338</x:v>
       </x:c>
       <x:c r="M121" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="N121" s="4">
         <x:v>46093.4565539005</x:v>
       </x:c>
       <x:c r="O121" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="P121" s="1" t="n">
         <x:v>45</x:v>
@@ -9933,13 +10160,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S121" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="T121" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U121" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="V121" s="1" t="n">
         <x:v>4</x:v>
@@ -9947,22 +10174,28 @@
       <x:c r="W121" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z121" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA121" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="122" spans="1:29">
       <x:c r="A122" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058716782</x:v>
       </x:c>
       <x:c r="B122" s="1" t="n">
         <x:v>35823</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D122" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E122" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F122" s="1" t="s">
         <x:v>51</x:v>
@@ -9983,13 +10216,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M122" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N122" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O122" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P122" s="1" t="n">
         <x:v>25</x:v>
@@ -10001,13 +10234,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S122" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T122" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U122" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V122" s="1" t="n">
         <x:v>6</x:v>
@@ -10015,22 +10248,28 @@
       <x:c r="W122" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z122" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA122" s="1" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="123" spans="1:29">
       <x:c r="A123" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058717245</x:v>
       </x:c>
       <x:c r="B123" s="1" t="n">
         <x:v>35824</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D123" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="F123" s="1" t="s">
         <x:v>51</x:v>
@@ -10051,13 +10290,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M123" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N123" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O123" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P123" s="1" t="n">
         <x:v>70</x:v>
@@ -10069,13 +10308,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S123" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T123" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U123" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V123" s="1" t="n">
         <x:v>2</x:v>
@@ -10083,22 +10322,28 @@
       <x:c r="W123" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z123" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA123" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="124" spans="1:29">
       <x:c r="A124" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.005871794</x:v>
       </x:c>
       <x:c r="B124" s="1" t="n">
         <x:v>35825</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D124" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E124" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="F124" s="1" t="s">
         <x:v>51</x:v>
@@ -10119,13 +10364,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M124" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N124" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O124" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P124" s="1" t="n">
         <x:v>40</x:v>
@@ -10137,13 +10382,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S124" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T124" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U124" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V124" s="1" t="n">
         <x:v>4</x:v>
@@ -10151,22 +10396,28 @@
       <x:c r="W124" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z124" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA124" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="125" spans="1:29">
       <x:c r="A125" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058719907</x:v>
       </x:c>
       <x:c r="B125" s="1" t="n">
         <x:v>35826</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D125" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="F125" s="1" t="s">
         <x:v>51</x:v>
@@ -10187,13 +10438,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M125" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N125" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O125" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P125" s="1" t="n">
         <x:v>85</x:v>
@@ -10205,13 +10456,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S125" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T125" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U125" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V125" s="1" t="n">
         <x:v>2</x:v>
@@ -10219,22 +10470,28 @@
       <x:c r="W125" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z125" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA125" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" spans="1:29">
       <x:c r="A126" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058720255</x:v>
       </x:c>
       <x:c r="B126" s="1" t="n">
         <x:v>35827</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="F126" s="1" t="s">
         <x:v>51</x:v>
@@ -10255,13 +10512,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M126" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N126" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O126" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P126" s="1" t="n">
         <x:v>120</x:v>
@@ -10273,13 +10530,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S126" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T126" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U126" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V126" s="1" t="n">
         <x:v>4</x:v>
@@ -10287,22 +10544,28 @@
       <x:c r="W126" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z126" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA126" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="127" spans="1:29">
       <x:c r="A127" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058721065</x:v>
       </x:c>
       <x:c r="B127" s="1" t="n">
         <x:v>35828</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F127" s="1" t="s">
         <x:v>51</x:v>
@@ -10323,13 +10586,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M127" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N127" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O127" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P127" s="1" t="n">
         <x:v>40</x:v>
@@ -10341,13 +10604,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S127" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T127" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U127" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V127" s="1" t="n">
         <x:v>4</x:v>
@@ -10355,22 +10618,28 @@
       <x:c r="W127" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z127" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA127" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="128" spans="1:29">
       <x:c r="A128" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058722222</x:v>
       </x:c>
       <x:c r="B128" s="1" t="n">
         <x:v>35829</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="F128" s="1" t="s">
         <x:v>51</x:v>
@@ -10391,13 +10660,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M128" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N128" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O128" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P128" s="1" t="n">
         <x:v>100</x:v>
@@ -10409,13 +10678,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S128" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T128" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U128" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V128" s="1" t="n">
         <x:v>4</x:v>
@@ -10423,22 +10692,28 @@
       <x:c r="W128" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z128" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA128" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="129" spans="1:29">
       <x:c r="A129" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.005872338</x:v>
       </x:c>
       <x:c r="B129" s="1" t="n">
         <x:v>35830</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D129" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="F129" s="1" t="s">
         <x:v>51</x:v>
@@ -10459,13 +10734,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M129" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N129" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O129" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P129" s="1" t="n">
         <x:v>80</x:v>
@@ -10477,13 +10752,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S129" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T129" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U129" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V129" s="1" t="n">
         <x:v>4</x:v>
@@ -10491,22 +10766,28 @@
       <x:c r="W129" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z129" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA129" s="1" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" spans="1:29">
       <x:c r="A130" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.005872419</x:v>
       </x:c>
       <x:c r="B130" s="1" t="n">
         <x:v>35831</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D130" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="F130" s="1" t="s">
         <x:v>51</x:v>
@@ -10527,13 +10808,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M130" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N130" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O130" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P130" s="1" t="n">
         <x:v>25</x:v>
@@ -10545,13 +10826,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S130" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T130" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U130" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V130" s="1" t="n">
         <x:v>2</x:v>
@@ -10559,22 +10840,28 @@
       <x:c r="W130" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z130" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA130" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="131" spans="1:29">
       <x:c r="A131" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058725694</x:v>
       </x:c>
       <x:c r="B131" s="1" t="n">
         <x:v>35832</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D131" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="F131" s="1" t="s">
         <x:v>51</x:v>
@@ -10595,13 +10882,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M131" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N131" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O131" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P131" s="1" t="n">
         <x:v>50</x:v>
@@ -10613,13 +10900,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S131" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T131" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U131" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V131" s="1" t="n">
         <x:v>2</x:v>
@@ -10627,22 +10914,28 @@
       <x:c r="W131" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z131" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA131" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="132" spans="1:29">
       <x:c r="A132" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058726505</x:v>
       </x:c>
       <x:c r="B132" s="1" t="n">
         <x:v>35833</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D132" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="F132" s="1" t="s">
         <x:v>51</x:v>
@@ -10663,13 +10956,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M132" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N132" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O132" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P132" s="1" t="n">
         <x:v>40</x:v>
@@ -10681,13 +10974,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S132" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T132" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U132" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V132" s="1" t="n">
         <x:v>2</x:v>
@@ -10695,22 +10988,28 @@
       <x:c r="W132" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z132" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA132" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="133" spans="1:29">
       <x:c r="A133" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058726852</x:v>
       </x:c>
       <x:c r="B133" s="1" t="n">
         <x:v>35834</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D133" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="F133" s="1" t="s">
         <x:v>51</x:v>
@@ -10731,13 +11030,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M133" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N133" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O133" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P133" s="1" t="n">
         <x:v>65</x:v>
@@ -10749,13 +11048,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S133" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T133" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U133" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V133" s="1" t="n">
         <x:v>1</x:v>
@@ -10763,22 +11062,28 @@
       <x:c r="W133" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z133" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA133" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="134" spans="1:29">
       <x:c r="A134" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058727662</x:v>
       </x:c>
       <x:c r="B134" s="1" t="n">
         <x:v>35835</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D134" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="F134" s="1" t="s">
         <x:v>51</x:v>
@@ -10799,13 +11104,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M134" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N134" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O134" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P134" s="1" t="n">
         <x:v>45</x:v>
@@ -10817,13 +11122,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S134" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T134" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U134" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V134" s="1" t="n">
         <x:v>1</x:v>
@@ -10831,22 +11136,28 @@
       <x:c r="W134" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z134" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA134" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="135" spans="1:29">
       <x:c r="A135" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058729514</x:v>
       </x:c>
       <x:c r="B135" s="1" t="n">
         <x:v>35836</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D135" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F135" s="1" t="s">
         <x:v>51</x:v>
@@ -10867,13 +11178,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M135" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N135" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O135" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P135" s="1" t="n">
         <x:v>17</x:v>
@@ -10885,13 +11196,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S135" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T135" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U135" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V135" s="1" t="n">
         <x:v>1</x:v>
@@ -10899,22 +11210,28 @@
       <x:c r="W135" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z135" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA135" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="136" spans="1:29">
       <x:c r="A136" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058730324</x:v>
       </x:c>
       <x:c r="B136" s="1" t="n">
         <x:v>35837</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D136" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="F136" s="1" t="s">
         <x:v>51</x:v>
@@ -10935,13 +11252,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M136" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N136" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O136" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P136" s="1" t="n">
         <x:v>30</x:v>
@@ -10953,13 +11270,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S136" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T136" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U136" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V136" s="1" t="n">
         <x:v>2</x:v>
@@ -10967,22 +11284,28 @@
       <x:c r="W136" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z136" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA136" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="137" spans="1:29">
       <x:c r="A137" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058730671</x:v>
       </x:c>
       <x:c r="B137" s="1" t="n">
         <x:v>35838</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D137" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="F137" s="1" t="s">
         <x:v>51</x:v>
@@ -11003,13 +11326,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M137" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N137" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O137" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P137" s="1" t="n">
         <x:v>40</x:v>
@@ -11021,13 +11344,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S137" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T137" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U137" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V137" s="1" t="n">
         <x:v>1</x:v>
@@ -11035,22 +11358,28 @@
       <x:c r="W137" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z137" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA137" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="138" spans="1:29">
       <x:c r="A138" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058732986</x:v>
       </x:c>
       <x:c r="B138" s="1" t="n">
         <x:v>35839</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D138" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="F138" s="1" t="s">
         <x:v>51</x:v>
@@ -11071,13 +11400,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M138" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N138" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O138" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P138" s="1" t="n">
         <x:v>320</x:v>
@@ -11089,13 +11418,13 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S138" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T138" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U138" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V138" s="1" t="n">
         <x:v>1</x:v>
@@ -11103,22 +11432,28 @@
       <x:c r="W138" s="3">
         <x:v>46107</x:v>
       </x:c>
+      <x:c r="Z138" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA138" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="139" spans="1:29">
       <x:c r="A139" s="4">
-        <x:v>46092.8409738426</x:v>
+        <x:v>46118.0058733449</x:v>
       </x:c>
       <x:c r="B139" s="1" t="n">
         <x:v>35840</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D139" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F139" s="1" t="s">
         <x:v>51</x:v>
@@ -11139,13 +11474,13 @@
         <x:v>46092.8395457523</x:v>
       </x:c>
       <x:c r="M139" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="N139" s="4">
         <x:v>46092.8408331366</x:v>
       </x:c>
       <x:c r="O139" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="P139" s="1" t="n">
         <x:v>18</x:v>
@@ -11157,19 +11492,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S139" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="T139" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U139" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="V139" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W139" s="3">
         <x:v>46107</x:v>
+      </x:c>
+      <x:c r="Z139" s="3">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="AA139" s="1" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:29">
@@ -11180,13 +11521,13 @@
         <x:v>35841</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D140" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="F140" s="1" t="s">
         <x:v>158</x:v>
@@ -11207,13 +11548,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M140" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R140" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S140" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T140" s="1" t="n">
         <x:v>1</x:v>
@@ -11227,13 +11568,13 @@
         <x:v>35842</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D141" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F141" s="1" t="s">
         <x:v>158</x:v>
@@ -11254,13 +11595,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M141" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R141" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S141" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T141" s="1" t="n">
         <x:v>1</x:v>
@@ -11274,13 +11615,13 @@
         <x:v>35843</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D142" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F142" s="1" t="s">
         <x:v>158</x:v>
@@ -11301,13 +11642,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M142" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R142" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S142" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T142" s="1" t="n">
         <x:v>1</x:v>
@@ -11321,13 +11662,13 @@
         <x:v>35844</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D143" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="F143" s="1" t="s">
         <x:v>158</x:v>
@@ -11348,13 +11689,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M143" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R143" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S143" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T143" s="1" t="n">
         <x:v>1</x:v>
@@ -11368,13 +11709,13 @@
         <x:v>35845</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D144" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F144" s="1" t="s">
         <x:v>158</x:v>
@@ -11395,13 +11736,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M144" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R144" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S144" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T144" s="1" t="n">
         <x:v>1</x:v>
@@ -11415,13 +11756,13 @@
         <x:v>35846</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D145" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F145" s="1" t="s">
         <x:v>158</x:v>
@@ -11442,13 +11783,13 @@
         <x:v>46076.6465126505</x:v>
       </x:c>
       <x:c r="M145" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="R145" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
       <x:c r="S145" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="T145" s="1" t="n">
         <x:v>1</x:v>
@@ -11462,7 +11803,7 @@
         <x:v>35888</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D146" s="1" t="s">
         <x:v>124</x:v>
@@ -11515,11 +11856,14 @@
       <x:c r="T146" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="U146" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
       <x:c r="V146" s="1" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="W146" s="4">
-        <x:v>46122.1666666667</x:v>
+      <x:c r="W146" s="3">
+        <x:v>46125</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:29">
@@ -11536,16 +11880,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="F147" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="G147" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H147" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="I147" s="1" t="n">
         <x:v>12</x:v>
@@ -11560,7 +11904,7 @@
         <x:v>46086.6600798611</x:v>
       </x:c>
       <x:c r="M147" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="N147" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11578,7 +11922,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S147" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="T147" s="1" t="n">
         <x:v>23</x:v>
@@ -11607,16 +11951,16 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F148" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G148" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H148" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="I148" s="1" t="n">
         <x:v>12</x:v>
@@ -11631,7 +11975,7 @@
         <x:v>46086.6600798611</x:v>
       </x:c>
       <x:c r="M148" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="N148" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11649,7 +11993,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S148" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="T148" s="1" t="n">
         <x:v>23</x:v>
@@ -11666,28 +12010,28 @@
     </x:row>
     <x:row r="149" spans="1:29">
       <x:c r="A149" s="4">
-        <x:v>46115.642734375</x:v>
+        <x:v>46127.4680013079</x:v>
       </x:c>
       <x:c r="B149" s="1" t="n">
         <x:v>35891</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="D149" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="F149" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="G149" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H149" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="I149" s="1" t="n">
         <x:v>1</x:v>
@@ -11695,40 +12039,67 @@
       <x:c r="J149" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K149" s="4">
+        <x:v>46126.6494199074</x:v>
+      </x:c>
       <x:c r="L149" s="4">
-        <x:v>46072.617799456</x:v>
+        <x:v>46127.4679292824</x:v>
       </x:c>
       <x:c r="M149" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="N149" s="4">
+        <x:v>46127.4679293981</x:v>
+      </x:c>
+      <x:c r="O149" s="1" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="P149" s="1" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="Q149" s="1" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="R149" s="1" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="S149" s="1" t="s">
+        <x:v>406</x:v>
       </x:c>
       <x:c r="T149" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
+      <x:c r="V149" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W149" s="4">
+        <x:v>46141.1666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="150" spans="1:29">
       <x:c r="A150" s="4">
-        <x:v>46115.6383925579</x:v>
+        <x:v>46119.7364352199</x:v>
       </x:c>
       <x:c r="B150" s="1" t="n">
         <x:v>35893</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D150" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="F150" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="G150" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H150" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="I150" s="1" t="n">
         <x:v>2</x:v>
@@ -11736,11 +12107,23 @@
       <x:c r="J150" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="K150" s="4">
+        <x:v>46119.7364351852</x:v>
+      </x:c>
       <x:c r="L150" s="4">
-        <x:v>46115.6381272338</x:v>
+        <x:v>46119.7364350694</x:v>
       </x:c>
       <x:c r="M150" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="R150" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="S150" s="1" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="T150" s="1" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:29">
@@ -11754,10 +12137,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D151" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="F151" s="1" t="s">
         <x:v>385</x:v>
@@ -11766,7 +12149,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H151" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="I151" s="1" t="n">
         <x:v>1</x:v>
@@ -11781,13 +12164,13 @@
         <x:v>46115.403372338</x:v>
       </x:c>
       <x:c r="M151" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="N151" s="4">
         <x:v>46115.4033724537</x:v>
       </x:c>
       <x:c r="O151" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="P151" s="1" t="n">
         <x:v>3.38</x:v>
@@ -11799,13 +12182,13 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S151" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="T151" s="1" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="U151" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="V151" s="1" t="n">
         <x:v>1</x:v>
@@ -11816,28 +12199,28 @@
     </x:row>
     <x:row r="152" spans="1:29">
       <x:c r="A152" s="4">
-        <x:v>46107.610496794</x:v>
+        <x:v>46123.9395770833</x:v>
       </x:c>
       <x:c r="B152" s="1" t="n">
         <x:v>35896</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D152" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F152" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="G152" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H152" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="I152" s="1" t="n">
         <x:v>1</x:v>
@@ -11852,13 +12235,13 @@
         <x:v>46107.6101008102</x:v>
       </x:c>
       <x:c r="M152" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="N152" s="4">
         <x:v>46107.6101011227</x:v>
       </x:c>
       <x:c r="O152" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="P152" s="1" t="n">
         <x:v>330</x:v>
@@ -11867,22 +12250,28 @@
         <x:v>1318.185</x:v>
       </x:c>
       <x:c r="R152" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="S152" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="T152" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U152" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="V152" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="W152" s="3">
         <x:v>46115</x:v>
+      </x:c>
+      <x:c r="Z152" s="3">
+        <x:v>46119</x:v>
+      </x:c>
+      <x:c r="AA152" s="1" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:29">
@@ -11899,16 +12288,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="F153" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G153" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H153" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="I153" s="1" t="n">
         <x:v>4</x:v>
@@ -11923,7 +12312,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M153" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N153" s="4">
         <x:v>46090.4456414005</x:v>
@@ -11941,7 +12330,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S153" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T153" s="1" t="n">
         <x:v>10</x:v>
@@ -11970,16 +12359,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="F154" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G154" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H154" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="I154" s="1" t="n">
         <x:v>4</x:v>
@@ -11994,7 +12383,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M154" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N154" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12012,7 +12401,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S154" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T154" s="1" t="n">
         <x:v>10</x:v>
@@ -12041,16 +12430,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F155" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G155" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H155" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="I155" s="1" t="n">
         <x:v>4</x:v>
@@ -12065,7 +12454,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M155" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N155" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12083,7 +12472,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S155" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T155" s="1" t="n">
         <x:v>10</x:v>
@@ -12100,28 +12489,28 @@
     </x:row>
     <x:row r="156" spans="1:29">
       <x:c r="A156" s="4">
-        <x:v>46090.4485225694</x:v>
+        <x:v>46118.0058749653</x:v>
       </x:c>
       <x:c r="B156" s="1" t="n">
         <x:v>35900</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D156" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F156" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="G156" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H156" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="I156" s="1" t="n">
         <x:v>6</x:v>
@@ -12136,13 +12525,13 @@
         <x:v>46087.0783034375</x:v>
       </x:c>
       <x:c r="M156" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="N156" s="4">
         <x:v>46090.4474321412</x:v>
       </x:c>
       <x:c r="O156" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="P156" s="1" t="n">
         <x:v>8.5</x:v>
@@ -12151,22 +12540,28 @@
         <x:v>202.3935</x:v>
       </x:c>
       <x:c r="R156" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="S156" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="T156" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U156" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="V156" s="1" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="W156" s="3">
         <x:v>46099</x:v>
+      </x:c>
+      <x:c r="Z156" s="3">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="AA156" s="1" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:29">
@@ -12183,16 +12578,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="F157" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G157" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H157" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="I157" s="1" t="n">
         <x:v>2</x:v>
@@ -12207,7 +12602,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M157" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N157" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12225,7 +12620,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S157" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T157" s="1" t="n">
         <x:v>10</x:v>
@@ -12248,13 +12643,13 @@
         <x:v>35902</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="D158" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="F158" s="1" t="s">
         <x:v>385</x:v>
@@ -12263,7 +12658,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H158" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="I158" s="1" t="n">
         <x:v>2</x:v>
@@ -12275,7 +12670,7 @@
         <x:v>46076.6827676736</x:v>
       </x:c>
       <x:c r="M158" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="R158" s="1" t="s">
         <x:v>195</x:v>
@@ -12295,16 +12690,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G159" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="I159" s="1" t="n">
         <x:v>4</x:v>
@@ -12319,7 +12714,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M159" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N159" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12337,7 +12732,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S159" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T159" s="1" t="n">
         <x:v>10</x:v>
@@ -12366,16 +12761,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="F160" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G160" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="I160" s="1" t="n">
         <x:v>4</x:v>
@@ -12390,7 +12785,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M160" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N160" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12408,7 +12803,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S160" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T160" s="1" t="n">
         <x:v>10</x:v>
@@ -12437,16 +12832,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F161" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G161" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="I161" s="1" t="n">
         <x:v>4</x:v>
@@ -12461,7 +12856,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M161" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N161" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12479,7 +12874,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S161" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T161" s="1" t="n">
         <x:v>10</x:v>
@@ -12508,16 +12903,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="F162" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G162" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="I162" s="1" t="n">
         <x:v>1</x:v>
@@ -12532,7 +12927,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M162" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N162" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12550,7 +12945,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S162" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T162" s="1" t="n">
         <x:v>10</x:v>
@@ -12579,16 +12974,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="F163" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G163" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H163" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="I163" s="1" t="n">
         <x:v>2</x:v>
@@ -12603,7 +12998,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M163" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N163" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12621,7 +13016,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S163" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T163" s="1" t="n">
         <x:v>10</x:v>
@@ -12650,16 +13045,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="F164" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G164" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H164" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="I164" s="1" t="n">
         <x:v>6</x:v>
@@ -12674,7 +13069,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M164" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N164" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12692,7 +13087,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S164" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T164" s="1" t="n">
         <x:v>10</x:v>
@@ -12721,16 +13116,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F165" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G165" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="I165" s="1" t="n">
         <x:v>2</x:v>
@@ -12745,7 +13140,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M165" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N165" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12763,7 +13158,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S165" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T165" s="1" t="n">
         <x:v>10</x:v>
@@ -12780,28 +13175,28 @@
     </x:row>
     <x:row r="166" spans="1:29">
       <x:c r="A166" s="4">
-        <x:v>46090.4485225694</x:v>
+        <x:v>46118.005875</x:v>
       </x:c>
       <x:c r="B166" s="1" t="n">
         <x:v>35910</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D166" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="F166" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="G166" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="I166" s="1" t="n">
         <x:v>2</x:v>
@@ -12816,13 +13211,13 @@
         <x:v>46087.0783034375</x:v>
       </x:c>
       <x:c r="M166" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="N166" s="4">
         <x:v>46090.4474321412</x:v>
       </x:c>
       <x:c r="O166" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="P166" s="1" t="n">
         <x:v>8.5</x:v>
@@ -12831,22 +13226,28 @@
         <x:v>67.4645</x:v>
       </x:c>
       <x:c r="R166" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="S166" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="T166" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U166" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="V166" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="W166" s="3">
         <x:v>46099</x:v>
+      </x:c>
+      <x:c r="Z166" s="3">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="AA166" s="1" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:29">
@@ -12863,16 +13264,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E167" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="F167" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G167" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="I167" s="1" t="n">
         <x:v>8</x:v>
@@ -12887,7 +13288,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M167" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N167" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12905,7 +13306,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S167" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T167" s="1" t="n">
         <x:v>10</x:v>
@@ -12934,16 +13335,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E168" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="F168" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G168" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="I168" s="1" t="n">
         <x:v>2</x:v>
@@ -12958,7 +13359,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M168" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N168" s="4">
         <x:v>46090.4456414005</x:v>
@@ -12976,7 +13377,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S168" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T168" s="1" t="n">
         <x:v>10</x:v>
@@ -12993,28 +13394,28 @@
     </x:row>
     <x:row r="169" spans="1:29">
       <x:c r="A169" s="4">
-        <x:v>46111.7199709144</x:v>
+        <x:v>46127.4682006944</x:v>
       </x:c>
       <x:c r="B169" s="1" t="n">
         <x:v>35913</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="D169" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E169" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="F169" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="G169" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="I169" s="1" t="n">
         <x:v>1</x:v>
@@ -13022,11 +13423,41 @@
       <x:c r="J169" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K169" s="4">
+        <x:v>46126.6479112616</x:v>
+      </x:c>
       <x:c r="L169" s="4">
-        <x:v>46111.7199707986</x:v>
+        <x:v>46127.4680396991</x:v>
       </x:c>
       <x:c r="M169" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="N169" s="4">
+        <x:v>46127.4680398495</x:v>
+      </x:c>
+      <x:c r="O169" s="1" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="P169" s="1" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="Q169" s="1" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="R169" s="1" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="S169" s="1" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="T169" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V169" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W169" s="4">
+        <x:v>46134.1666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:29">
@@ -13043,16 +13474,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E170" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="F170" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G170" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H170" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="I170" s="1" t="n">
         <x:v>4</x:v>
@@ -13067,7 +13498,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M170" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N170" s="4">
         <x:v>46090.4456414005</x:v>
@@ -13085,7 +13516,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S170" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T170" s="1" t="n">
         <x:v>10</x:v>
@@ -13114,16 +13545,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E171" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="F171" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G171" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H171" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="I171" s="1" t="n">
         <x:v>1</x:v>
@@ -13138,7 +13569,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M171" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N171" s="4">
         <x:v>46090.4456414005</x:v>
@@ -13156,7 +13587,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S171" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T171" s="1" t="n">
         <x:v>10</x:v>
@@ -13173,28 +13604,28 @@
     </x:row>
     <x:row r="172" spans="1:29">
       <x:c r="A172" s="4">
-        <x:v>46090.447941169</x:v>
+        <x:v>46118.005874456</x:v>
       </x:c>
       <x:c r="B172" s="1" t="n">
         <x:v>35916</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D172" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E172" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F172" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G172" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H172" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="I172" s="1" t="n">
         <x:v>1</x:v>
@@ -13209,13 +13640,13 @@
         <x:v>46090.4477212616</x:v>
       </x:c>
       <x:c r="M172" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="N172" s="4">
         <x:v>46090.447721412</x:v>
       </x:c>
       <x:c r="O172" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="P172" s="1" t="n">
         <x:v>885</x:v>
@@ -13224,16 +13655,16 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="R172" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="S172" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="T172" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U172" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="V172" s="1" t="n">
         <x:v>1</x:v>
@@ -13241,22 +13672,28 @@
       <x:c r="W172" s="3">
         <x:v>46113</x:v>
       </x:c>
+      <x:c r="Z172" s="3">
+        <x:v>46108</x:v>
+      </x:c>
+      <x:c r="AA172" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="173" spans="1:29">
       <x:c r="A173" s="4">
-        <x:v>46092.6276936343</x:v>
+        <x:v>46118.0058641204</x:v>
       </x:c>
       <x:c r="B173" s="1" t="n">
         <x:v>36010</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="F173" s="1" t="s">
         <x:v>51</x:v>
@@ -13277,13 +13714,13 @@
         <x:v>46092.627584375</x:v>
       </x:c>
       <x:c r="M173" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="N173" s="4">
         <x:v>46092.6275845255</x:v>
       </x:c>
       <x:c r="O173" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="P173" s="1" t="n">
         <x:v>66</x:v>
@@ -13295,19 +13732,25 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="S173" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="T173" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U173" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="V173" s="1" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="W173" s="3">
         <x:v>46094</x:v>
+      </x:c>
+      <x:c r="Z173" s="3">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="AA173" s="1" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:29">
@@ -13324,16 +13767,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E174" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="F174" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="G174" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H174" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="I174" s="1" t="n">
         <x:v>1</x:v>
@@ -13348,13 +13791,13 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M174" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="N174" s="4">
         <x:v>46107.6111298611</x:v>
       </x:c>
       <x:c r="O174" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="P174" s="1" t="n">
         <x:v>137.84</x:v>
@@ -13366,13 +13809,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S174" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="T174" s="1" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="U174" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="V174" s="1" t="n">
         <x:v>1</x:v>
@@ -13395,16 +13838,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E175" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="F175" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="G175" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="I175" s="1" t="n">
         <x:v>4</x:v>
@@ -13419,13 +13862,13 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M175" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="N175" s="4">
         <x:v>46107.6111298611</x:v>
       </x:c>
       <x:c r="O175" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="P175" s="1" t="n">
         <x:v>1.02</x:v>
@@ -13437,13 +13880,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S175" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="T175" s="1" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="U175" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="V175" s="1" t="n">
         <x:v>4</x:v>
@@ -13466,16 +13909,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E176" s="1" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="F176" s="1" t="s">
         <x:v>483</x:v>
-      </x:c>
-      <x:c r="F176" s="1" t="s">
-        <x:v>475</x:v>
       </x:c>
       <x:c r="G176" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H176" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="I176" s="1" t="n">
         <x:v>4</x:v>
@@ -13490,13 +13933,13 @@
         <x:v>46093.0045250347</x:v>
       </x:c>
       <x:c r="M176" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="N176" s="4">
         <x:v>46107.6111298611</x:v>
       </x:c>
       <x:c r="O176" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="P176" s="1" t="n">
         <x:v>2.37</x:v>
@@ -13508,13 +13951,13 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="S176" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="T176" s="1" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="U176" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="V176" s="1" t="n">
         <x:v>4</x:v>
@@ -13525,28 +13968,28 @@
     </x:row>
     <x:row r="177" spans="1:29">
       <x:c r="A177" s="4">
-        <x:v>46097.6308056366</x:v>
+        <x:v>46127.4678774306</x:v>
       </x:c>
       <x:c r="B177" s="1" t="n">
         <x:v>36282</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E177" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="F177" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="G177" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H177" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="I177" s="1" t="n">
         <x:v>1</x:v>
@@ -13554,11 +13997,41 @@
       <x:c r="J177" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="K177" s="4">
+        <x:v>46126.6532908912</x:v>
+      </x:c>
       <x:c r="L177" s="4">
-        <x:v>46093.0051497338</x:v>
+        <x:v>46127.4676806366</x:v>
       </x:c>
       <x:c r="M177" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="N177" s="4">
+        <x:v>46127.467680787</x:v>
+      </x:c>
+      <x:c r="O177" s="1" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="P177" s="1" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="Q177" s="1" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="R177" s="1" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="S177" s="1" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="T177" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V177" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W177" s="4">
+        <x:v>46134.1666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:29">
@@ -13572,10 +14045,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E178" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F178" s="1" t="s">
         <x:v>51</x:v>
@@ -13593,7 +14066,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M178" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:29">
@@ -13607,10 +14080,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E179" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="F179" s="1" t="s">
         <x:v>64</x:v>
@@ -13628,7 +14101,7 @@
         <x:v>46085.4128305208</x:v>
       </x:c>
       <x:c r="M179" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>503</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:29">
@@ -13642,10 +14115,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D180" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E180" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="F180" s="1" t="s">
         <x:v>51</x:v>
@@ -13663,7 +14136,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M180" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:29">
@@ -13677,10 +14150,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D181" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E181" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="F181" s="1" t="s">
         <x:v>51</x:v>
@@ -13698,7 +14171,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M181" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:29">
@@ -13712,10 +14185,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D182" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E182" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="F182" s="1" t="s">
         <x:v>51</x:v>
@@ -13733,7 +14206,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M182" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:29">
@@ -13747,10 +14220,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D183" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="F183" s="1" t="s">
         <x:v>51</x:v>
@@ -13768,7 +14241,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M183" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:29">
@@ -13782,10 +14255,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D184" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E184" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="F184" s="1" t="s">
         <x:v>51</x:v>
@@ -13803,7 +14276,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M184" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:29">
@@ -13817,10 +14290,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D185" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="F185" s="1" t="s">
         <x:v>51</x:v>
@@ -13838,7 +14311,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M185" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:29">
@@ -13852,10 +14325,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D186" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E186" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="F186" s="1" t="s">
         <x:v>51</x:v>
@@ -13873,7 +14346,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M186" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:29">
@@ -13887,10 +14360,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E187" s="1" t="s">
-        <x:v>500</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="F187" s="1" t="s">
         <x:v>158</x:v>
@@ -13911,13 +14384,13 @@
         <x:v>46111.7201420139</x:v>
       </x:c>
       <x:c r="M187" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="N187" s="4">
         <x:v>46111.7201421644</x:v>
       </x:c>
       <x:c r="O187" s="1" t="s">
-        <x:v>502</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="P187" s="1" t="n">
         <x:v>50</x:v>
@@ -13929,13 +14402,13 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="S187" s="1" t="s">
-        <x:v>503</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="T187" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="U187" s="1" t="s">
-        <x:v>504</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="V187" s="1" t="n">
         <x:v>2</x:v>
@@ -13955,10 +14428,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D188" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E188" s="1" t="s">
-        <x:v>505</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="F188" s="1" t="s">
         <x:v>51</x:v>
@@ -13976,7 +14449,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M188" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:29">
@@ -13990,10 +14463,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D189" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>506</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F189" s="1" t="s">
         <x:v>51</x:v>
@@ -14011,7 +14484,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M189" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:29">
@@ -14025,10 +14498,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D190" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E190" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F190" s="1" t="s">
         <x:v>51</x:v>
@@ -14046,7 +14519,7 @@
         <x:v>46085.4124951389</x:v>
       </x:c>
       <x:c r="M190" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:29">
@@ -14060,19 +14533,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E191" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="F191" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="G191" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H191" s="1" t="s">
-        <x:v>510</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="I191" s="1" t="n">
         <x:v>2</x:v>
@@ -14087,7 +14560,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M191" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="N191" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14105,7 +14578,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S191" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="T191" s="1" t="n">
         <x:v>1</x:v>
@@ -14131,19 +14604,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D192" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E192" s="1" t="s">
-        <x:v>513</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="F192" s="1" t="s">
-        <x:v>514</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="G192" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="H192" s="1" t="s">
-        <x:v>515</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="I192" s="1" t="n">
         <x:v>2</x:v>
@@ -14158,7 +14631,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M192" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="N192" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14176,7 +14649,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S192" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="T192" s="1" t="n">
         <x:v>1</x:v>
@@ -14202,10 +14675,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D193" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="F193" s="1" t="s">
         <x:v>222</x:v>
@@ -14214,7 +14687,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H193" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="I193" s="1" t="n">
         <x:v>2</x:v>
@@ -14229,7 +14702,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M193" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="N193" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14247,7 +14720,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S193" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="T193" s="1" t="n">
         <x:v>1</x:v>
@@ -14273,10 +14746,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D194" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
-        <x:v>518</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F194" s="1" t="s">
         <x:v>222</x:v>
@@ -14285,7 +14758,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H194" s="1" t="s">
-        <x:v>519</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="I194" s="1" t="n">
         <x:v>2</x:v>
@@ -14300,7 +14773,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M194" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="N194" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14318,7 +14791,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S194" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="T194" s="1" t="n">
         <x:v>1</x:v>
@@ -14344,7 +14817,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E195" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="G195" s="1" t="s">
         <x:v>127</x:v>
@@ -14359,7 +14832,7 @@
         <x:v>46086.6518199421</x:v>
       </x:c>
       <x:c r="M195" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="N195" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14377,7 +14850,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S195" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="T195" s="1" t="n">
         <x:v>10</x:v>
@@ -14403,10 +14876,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D196" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="F196" s="1" t="s">
         <x:v>64</x:v>
@@ -14424,7 +14897,7 @@
         <x:v>46086.7566555556</x:v>
       </x:c>
       <x:c r="M196" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>533</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:29">
@@ -14438,7 +14911,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E197" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="G197" s="1" t="s">
         <x:v>127</x:v>
@@ -14453,7 +14926,7 @@
         <x:v>46086.7622771991</x:v>
       </x:c>
       <x:c r="M197" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="N197" s="4">
         <x:v>46090.4456414005</x:v>
@@ -14471,7 +14944,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="S197" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="T197" s="1" t="n">
         <x:v>1</x:v>
@@ -14497,10 +14970,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D198" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="E198" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="F198" s="1" t="s">
         <x:v>64</x:v>
@@ -14518,7 +14991,7 @@
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M198" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>537</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:29">
@@ -14532,10 +15005,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D199" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="E199" s="1" t="s">
-        <x:v>527</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="F199" s="1" t="s">
         <x:v>64</x:v>
@@ -14553,7 +15026,7 @@
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M199" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>537</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:29">
@@ -14567,10 +15040,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D200" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="E200" s="1" t="s">
-        <x:v>528</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="F200" s="1" t="s">
         <x:v>64</x:v>
@@ -14588,7 +15061,7 @@
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M200" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>537</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:29">
@@ -14602,10 +15075,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="E201" s="1" t="s">
-        <x:v>529</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="F201" s="1" t="s">
         <x:v>64</x:v>
@@ -14623,7 +15096,7 @@
         <x:v>46098.5238698727</x:v>
       </x:c>
       <x:c r="M201" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>537</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:29">
@@ -14637,10 +15110,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D202" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="E202" s="1" t="s">
-        <x:v>530</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="F202" s="1" t="s">
         <x:v>51</x:v>
@@ -14658,7 +15131,7 @@
         <x:v>46100.4729106481</x:v>
       </x:c>
       <x:c r="M202" s="1" t="s">
-        <x:v>531</x:v>
+        <x:v>542</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:29">
@@ -14672,10 +15145,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="D203" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>532</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="F203" s="1" t="s">
         <x:v>51</x:v>
@@ -14693,7 +15166,284 @@
         <x:v>46100.4729106481</x:v>
       </x:c>
       <x:c r="M203" s="1" t="s">
-        <x:v>531</x:v>
+        <x:v>542</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:29">
+      <x:c r="A204" s="4">
+        <x:v>46126.7262309838</x:v>
+      </x:c>
+      <x:c r="B204" s="1" t="n">
+        <x:v>38196</x:v>
+      </x:c>
+      <x:c r="C204" s="1" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="D204" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E204" s="1" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="F204" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G204" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H204" s="1" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="I204" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J204" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K204" s="4">
+        <x:v>46119.7327588773</x:v>
+      </x:c>
+      <x:c r="L204" s="4">
+        <x:v>46121.6969856134</x:v>
+      </x:c>
+      <x:c r="M204" s="1" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="N204" s="4">
+        <x:v>46121.6969857292</x:v>
+      </x:c>
+      <x:c r="O204" s="1" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="P204" s="1" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="Q204" s="1" t="n">
+        <x:v>1.88</x:v>
+      </x:c>
+      <x:c r="R204" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S204" s="1" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="T204" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V204" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W204" s="4">
+        <x:v>46122.1666666667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:29">
+      <x:c r="A205" s="4">
+        <x:v>46121.6802669329</x:v>
+      </x:c>
+      <x:c r="B205" s="1" t="n">
+        <x:v>38197</x:v>
+      </x:c>
+      <x:c r="C205" s="1" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="D205" s="1" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="E205" s="1" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="F205" s="1" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="G205" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H205" s="1" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="I205" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J205" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K205" s="4">
+        <x:v>46119.7316782407</x:v>
+      </x:c>
+      <x:c r="L205" s="4">
+        <x:v>46121.5722910532</x:v>
+      </x:c>
+      <x:c r="M205" s="1" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="N205" s="4">
+        <x:v>46121.572291169</x:v>
+      </x:c>
+      <x:c r="O205" s="1" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="P205" s="1" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q205" s="1" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R205" s="1" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="S205" s="1" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="T205" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V205" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W205" s="4">
+        <x:v>46135.1666666667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:29">
+      <x:c r="A206" s="4">
+        <x:v>46120.3992786227</x:v>
+      </x:c>
+      <x:c r="B206" s="1" t="n">
+        <x:v>38392</x:v>
+      </x:c>
+      <x:c r="C206" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D206" s="1" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="E206" s="1" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="F206" s="1" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="G206" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H206" s="1" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="I206" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J206" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L206" s="4">
+        <x:v>46119.7146954514</x:v>
+      </x:c>
+      <x:c r="M206" s="1" t="s">
+        <x:v>560</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:29">
+      <x:c r="A207" s="4">
+        <x:v>46126.7260145486</x:v>
+      </x:c>
+      <x:c r="B207" s="1" t="n">
+        <x:v>38393</x:v>
+      </x:c>
+      <x:c r="C207" s="1" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="D207" s="1" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="E207" s="1" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="F207" s="1" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="G207" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H207" s="1" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="I207" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J207" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K207" s="4">
+        <x:v>46121.610255706</x:v>
+      </x:c>
+      <x:c r="L207" s="4">
+        <x:v>46121.6950445949</x:v>
+      </x:c>
+      <x:c r="M207" s="1" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="N207" s="4">
+        <x:v>46121.6950447569</x:v>
+      </x:c>
+      <x:c r="O207" s="1" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="P207" s="1" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="Q207" s="1" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="R207" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="S207" s="1" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="T207" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V207" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W207" s="4">
+        <x:v>46151.1666666667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:29">
+      <x:c r="A208" s="4">
+        <x:v>46127.5161385417</x:v>
+      </x:c>
+      <x:c r="B208" s="1" t="n">
+        <x:v>38951</x:v>
+      </x:c>
+      <x:c r="C208" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D208" s="1" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="E208" s="1" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="F208" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G208" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I208" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J208" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L208" s="4">
+        <x:v>46127.5161385069</x:v>
+      </x:c>
+      <x:c r="M208" s="1" t="s">
+        <x:v>567</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
